--- a/Selva Viva/Selva Viva isotopos.xlsx
+++ b/Selva Viva/Selva Viva isotopos.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U224"/>
+  <dimension ref="A1:T224"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -476,55 +476,50 @@
       </c>
       <c r="K1" s="1" t="inlineStr">
         <is>
-          <t>Type 2</t>
+          <t>sample-ID</t>
         </is>
       </c>
       <c r="L1" s="1" t="inlineStr">
         <is>
-          <t>sample-ID</t>
+          <t>[N]</t>
         </is>
       </c>
       <c r="M1" s="1" t="inlineStr">
         <is>
-          <t>[N]</t>
+          <t>[C_b]%</t>
         </is>
       </c>
       <c r="N1" s="1" t="inlineStr">
         <is>
-          <t>[C_b]%</t>
+          <t>δ15N (‰ v.s. V-PDB)</t>
         </is>
       </c>
       <c r="O1" s="1" t="inlineStr">
         <is>
-          <t>δ15N (‰ v.s. V-PDB)</t>
+          <t>bulk_δ13C (‰ v.s.V-PDB)</t>
         </is>
       </c>
       <c r="P1" s="1" t="inlineStr">
         <is>
-          <t>bulk_δ13C (‰ v.s.V-PDB)</t>
+          <t>new_TreeID</t>
         </is>
       </c>
       <c r="Q1" s="1" t="inlineStr">
         <is>
-          <t>new_TreeID</t>
+          <t>family</t>
         </is>
       </c>
       <c r="R1" s="1" t="inlineStr">
         <is>
-          <t>family</t>
+          <t>JH herbarium collections</t>
         </is>
       </c>
       <c r="S1" s="1" t="inlineStr">
         <is>
-          <t>JH herbarium collections</t>
+          <t>genus</t>
         </is>
       </c>
       <c r="T1" s="1" t="inlineStr">
-        <is>
-          <t>genus</t>
-        </is>
-      </c>
-      <c r="U1" s="1" t="inlineStr">
         <is>
           <t>species</t>
         </is>
@@ -565,31 +560,26 @@
         </is>
       </c>
       <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="O2" t="inlineStr"/>
-      <c r="P2" t="inlineStr"/>
-      <c r="Q2" t="n">
+      <c r="P2" t="n">
         <v>3604</v>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="Q2" t="inlineStr">
         <is>
           <t>Meliaceae</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr"/>
-      <c r="T2" t="inlineStr">
+      <c r="R2" t="inlineStr"/>
+      <c r="S2" t="inlineStr">
         <is>
           <t>Guarea</t>
         </is>
       </c>
-      <c r="U2" t="inlineStr"/>
+      <c r="T2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="1" t="n">
@@ -631,22 +621,21 @@
       <c r="M3" t="inlineStr"/>
       <c r="N3" t="inlineStr"/>
       <c r="O3" t="inlineStr"/>
-      <c r="P3" t="inlineStr"/>
-      <c r="Q3" t="n">
+      <c r="P3" t="n">
         <v>3604</v>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="Q3" t="inlineStr">
         <is>
           <t>Meliaceae</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr">
+      <c r="R3" t="inlineStr"/>
+      <c r="S3" t="inlineStr">
         <is>
           <t>Guarea</t>
         </is>
       </c>
-      <c r="U3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="1" t="n">
@@ -690,26 +679,25 @@
       <c r="M4" t="inlineStr"/>
       <c r="N4" t="inlineStr"/>
       <c r="O4" t="inlineStr"/>
-      <c r="P4" t="inlineStr"/>
-      <c r="Q4" t="n">
+      <c r="P4" t="n">
         <v>3605</v>
       </c>
+      <c r="Q4" t="inlineStr">
+        <is>
+          <t>Moraceae</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>Moraceae</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>Ficus</t>
         </is>
       </c>
       <c r="T4" t="inlineStr">
-        <is>
-          <t>Ficus</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
         <is>
           <t>pulchella</t>
         </is>
@@ -746,43 +734,42 @@
       <c r="J5" t="n">
         <v>2171</v>
       </c>
-      <c r="K5" t="inlineStr"/>
-      <c r="L5" t="inlineStr">
+      <c r="K5" t="inlineStr">
         <is>
           <t>p69-3605</t>
         </is>
       </c>
+      <c r="L5" t="n">
+        <v>0.02213145516022583</v>
+      </c>
       <c r="M5" t="n">
-        <v>0.02213145516022583</v>
+        <v>0.4282614261488554</v>
       </c>
       <c r="N5" t="n">
-        <v>0.4282614261488554</v>
+        <v>0.46</v>
       </c>
       <c r="O5" t="n">
-        <v>0.46</v>
+        <v>-31.85</v>
       </c>
       <c r="P5" t="n">
-        <v>-31.85</v>
-      </c>
-      <c r="Q5" t="n">
         <v>3605</v>
       </c>
+      <c r="Q5" t="inlineStr">
+        <is>
+          <t>Moraceae</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>Moraceae</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>Ficus</t>
         </is>
       </c>
       <c r="T5" t="inlineStr">
-        <is>
-          <t>Ficus</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
         <is>
           <t>pulchella</t>
         </is>
@@ -819,43 +806,42 @@
       <c r="J6" t="n">
         <v>2171</v>
       </c>
-      <c r="K6" t="inlineStr"/>
-      <c r="L6" t="inlineStr">
+      <c r="K6" t="inlineStr">
         <is>
           <t>p69-3605</t>
         </is>
       </c>
+      <c r="L6" t="n">
+        <v>0.02213145516022583</v>
+      </c>
       <c r="M6" t="n">
-        <v>0.02213145516022583</v>
+        <v>0.4282614261488554</v>
       </c>
       <c r="N6" t="n">
-        <v>0.4282614261488554</v>
+        <v>0.46</v>
       </c>
       <c r="O6" t="n">
-        <v>0.46</v>
+        <v>-31.85</v>
       </c>
       <c r="P6" t="n">
-        <v>-31.85</v>
-      </c>
-      <c r="Q6" t="n">
         <v>3605</v>
       </c>
+      <c r="Q6" t="inlineStr">
+        <is>
+          <t>Moraceae</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>Moraceae</t>
+          <t>3841</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>Ficus</t>
         </is>
       </c>
       <c r="T6" t="inlineStr">
-        <is>
-          <t>Ficus</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
         <is>
           <t>pulchella</t>
         </is>
@@ -903,26 +889,25 @@
       <c r="M7" t="inlineStr"/>
       <c r="N7" t="inlineStr"/>
       <c r="O7" t="inlineStr"/>
-      <c r="P7" t="inlineStr"/>
-      <c r="Q7" t="n">
+      <c r="P7" t="n">
         <v>3606</v>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Moraceae</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>Moraceae</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>Batocarpus</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
-        <is>
-          <t>Batocarpus</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
         <is>
           <t>orinocensis</t>
         </is>
@@ -970,26 +955,25 @@
       <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="O8" t="inlineStr"/>
-      <c r="P8" t="inlineStr"/>
-      <c r="Q8" t="n">
+      <c r="P8" t="n">
         <v>3606</v>
       </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Moraceae</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
-          <t>Moraceae</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="S8" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>Batocarpus</t>
         </is>
       </c>
       <c r="T8" t="inlineStr">
-        <is>
-          <t>Batocarpus</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
         <is>
           <t>orinocensis</t>
         </is>
@@ -1026,43 +1010,42 @@
       <c r="J9" t="n">
         <v>2172</v>
       </c>
-      <c r="K9" t="inlineStr"/>
-      <c r="L9" t="inlineStr">
+      <c r="K9" t="inlineStr">
         <is>
           <t>p69-3606</t>
         </is>
       </c>
+      <c r="L9" t="n">
+        <v>0.02485796670088971</v>
+      </c>
       <c r="M9" t="n">
-        <v>0.02485796670088971</v>
+        <v>0.4378430142968719</v>
       </c>
       <c r="N9" t="n">
-        <v>0.4378430142968719</v>
+        <v>0.12</v>
       </c>
       <c r="O9" t="n">
-        <v>0.12</v>
+        <v>-31.98</v>
       </c>
       <c r="P9" t="n">
-        <v>-31.98</v>
-      </c>
-      <c r="Q9" t="n">
         <v>3606</v>
       </c>
+      <c r="Q9" t="inlineStr">
+        <is>
+          <t>Moraceae</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
-          <t>Moraceae</t>
+          <t>3842</t>
         </is>
       </c>
       <c r="S9" t="inlineStr">
         <is>
-          <t>3842</t>
+          <t>Batocarpus</t>
         </is>
       </c>
       <c r="T9" t="inlineStr">
-        <is>
-          <t>Batocarpus</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
         <is>
           <t>orinocensis</t>
         </is>
@@ -1108,18 +1091,17 @@
       <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="O10" t="inlineStr"/>
-      <c r="P10" t="inlineStr"/>
-      <c r="Q10" t="n">
+      <c r="P10" t="n">
         <v>3607</v>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="Q10" t="inlineStr">
         <is>
           <t>Indet</t>
         </is>
       </c>
+      <c r="R10" t="inlineStr"/>
       <c r="S10" t="inlineStr"/>
       <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n">
@@ -1156,27 +1138,22 @@
         </is>
       </c>
       <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
       <c r="M11" t="inlineStr"/>
       <c r="N11" t="inlineStr"/>
       <c r="O11" t="inlineStr"/>
-      <c r="P11" t="inlineStr"/>
-      <c r="Q11" t="n">
+      <c r="P11" t="n">
         <v>3607</v>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="Q11" t="inlineStr">
         <is>
           <t>Indet</t>
         </is>
       </c>
+      <c r="R11" t="inlineStr"/>
       <c r="S11" t="inlineStr"/>
       <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="1" t="n">
@@ -1220,26 +1197,25 @@
       <c r="M12" t="inlineStr"/>
       <c r="N12" t="inlineStr"/>
       <c r="O12" t="inlineStr"/>
-      <c r="P12" t="inlineStr"/>
-      <c r="Q12" t="n">
+      <c r="P12" t="n">
         <v>3608</v>
       </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>Meliaceae</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr">
         <is>
-          <t>Meliaceae</t>
+          <t>3840</t>
         </is>
       </c>
       <c r="S12" t="inlineStr">
         <is>
-          <t>3840</t>
+          <t>Guarea</t>
         </is>
       </c>
       <c r="T12" t="inlineStr">
-        <is>
-          <t>Guarea</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
         <is>
           <t>kunthiana</t>
         </is>
@@ -1276,39 +1252,38 @@
       <c r="J13" t="n">
         <v>2167</v>
       </c>
-      <c r="K13" t="inlineStr"/>
-      <c r="L13" t="inlineStr">
+      <c r="K13" t="inlineStr">
         <is>
           <t>p69-3609</t>
         </is>
       </c>
+      <c r="L13" t="n">
+        <v>0.02341087029895825</v>
+      </c>
       <c r="M13" t="n">
-        <v>0.02341087029895825</v>
+        <v>0.433943697942952</v>
       </c>
       <c r="N13" t="n">
-        <v>0.433943697942952</v>
+        <v>-0.63</v>
       </c>
       <c r="O13" t="n">
-        <v>-0.63</v>
+        <v>-32.26</v>
       </c>
       <c r="P13" t="n">
-        <v>-32.26</v>
-      </c>
-      <c r="Q13" t="n">
         <v>3609</v>
       </c>
-      <c r="R13" t="inlineStr">
+      <c r="Q13" t="inlineStr">
         <is>
           <t>Euphorbiaceae</t>
         </is>
       </c>
-      <c r="S13" t="inlineStr"/>
+      <c r="R13" t="inlineStr"/>
+      <c r="S13" t="inlineStr">
+        <is>
+          <t>Pseudosenefeldera</t>
+        </is>
+      </c>
       <c r="T13" t="inlineStr">
-        <is>
-          <t>Pseudosenefeldera</t>
-        </is>
-      </c>
-      <c r="U13" t="inlineStr">
         <is>
           <t>inclinata</t>
         </is>
@@ -1356,22 +1331,21 @@
       <c r="M14" t="inlineStr"/>
       <c r="N14" t="inlineStr"/>
       <c r="O14" t="inlineStr"/>
-      <c r="P14" t="inlineStr"/>
-      <c r="Q14" t="n">
+      <c r="P14" t="n">
         <v>3610</v>
       </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Indet</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
-          <t>Indet</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
           <t>3838</t>
         </is>
       </c>
+      <c r="S14" t="inlineStr"/>
       <c r="T14" t="inlineStr"/>
-      <c r="U14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="1" t="n">
@@ -1404,39 +1378,38 @@
       <c r="J15" t="n">
         <v>2180</v>
       </c>
-      <c r="K15" t="inlineStr"/>
-      <c r="L15" t="inlineStr">
+      <c r="K15" t="inlineStr">
         <is>
           <t>p69-3612</t>
         </is>
       </c>
+      <c r="L15" t="n">
+        <v>0.0144700480896215</v>
+      </c>
       <c r="M15" t="n">
-        <v>0.0144700480896215</v>
+        <v>0.4792818843283498</v>
       </c>
       <c r="N15" t="n">
-        <v>0.4792818843283498</v>
+        <v>-0.86</v>
       </c>
       <c r="O15" t="n">
-        <v>-0.86</v>
+        <v>-31.62</v>
       </c>
       <c r="P15" t="n">
-        <v>-31.62</v>
-      </c>
-      <c r="Q15" t="n">
         <v>3612</v>
       </c>
-      <c r="R15" t="inlineStr">
+      <c r="Q15" t="inlineStr">
         <is>
           <t>Myristicaceae</t>
         </is>
       </c>
-      <c r="S15" t="inlineStr"/>
+      <c r="R15" t="inlineStr"/>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>Otoba</t>
+        </is>
+      </c>
       <c r="T15" t="inlineStr">
-        <is>
-          <t>Otoba</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
         <is>
           <t>parvifolia</t>
         </is>
@@ -1482,22 +1455,21 @@
       <c r="M16" t="inlineStr"/>
       <c r="N16" t="inlineStr"/>
       <c r="O16" t="inlineStr"/>
-      <c r="P16" t="inlineStr"/>
-      <c r="Q16" t="n">
+      <c r="P16" t="n">
         <v>3613</v>
       </c>
-      <c r="R16" t="inlineStr">
+      <c r="Q16" t="inlineStr">
         <is>
           <t>Euphorbiaceae</t>
         </is>
       </c>
-      <c r="S16" t="inlineStr"/>
+      <c r="R16" t="inlineStr"/>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>Pseudosenefeldera</t>
+        </is>
+      </c>
       <c r="T16" t="inlineStr">
-        <is>
-          <t>Pseudosenefeldera</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
         <is>
           <t>inclinata</t>
         </is>
@@ -1538,31 +1510,26 @@
         </is>
       </c>
       <c r="J17" t="inlineStr"/>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K17" t="inlineStr"/>
       <c r="L17" t="inlineStr"/>
       <c r="M17" t="inlineStr"/>
       <c r="N17" t="inlineStr"/>
       <c r="O17" t="inlineStr"/>
-      <c r="P17" t="inlineStr"/>
-      <c r="Q17" t="n">
+      <c r="P17" t="n">
         <v>3613</v>
       </c>
-      <c r="R17" t="inlineStr">
+      <c r="Q17" t="inlineStr">
         <is>
           <t>Euphorbiaceae</t>
         </is>
       </c>
-      <c r="S17" t="inlineStr"/>
+      <c r="R17" t="inlineStr"/>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>Pseudosenefeldera</t>
+        </is>
+      </c>
       <c r="T17" t="inlineStr">
-        <is>
-          <t>Pseudosenefeldera</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
         <is>
           <t>inclinata</t>
         </is>
@@ -1610,26 +1577,25 @@
       <c r="M18" t="inlineStr"/>
       <c r="N18" t="inlineStr"/>
       <c r="O18" t="inlineStr"/>
-      <c r="P18" t="inlineStr"/>
-      <c r="Q18" t="n">
+      <c r="P18" t="n">
         <v>3617</v>
       </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>Fabaceae</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr">
         <is>
-          <t>Fabaceae</t>
+          <t>3844</t>
         </is>
       </c>
       <c r="S18" t="inlineStr">
         <is>
-          <t>3844</t>
+          <t>Browneopsis</t>
         </is>
       </c>
       <c r="T18" t="inlineStr">
-        <is>
-          <t>Browneopsis</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
         <is>
           <t>ucayalina</t>
         </is>
@@ -1666,39 +1632,38 @@
       <c r="J19" t="n">
         <v>2179</v>
       </c>
-      <c r="K19" t="inlineStr"/>
-      <c r="L19" t="inlineStr">
+      <c r="K19" t="inlineStr">
         <is>
           <t>p69-3619</t>
         </is>
       </c>
+      <c r="L19" t="n">
+        <v>0.01915534221097701</v>
+      </c>
       <c r="M19" t="n">
-        <v>0.01915534221097701</v>
+        <v>0.4350616092673997</v>
       </c>
       <c r="N19" t="n">
-        <v>0.4350616092673997</v>
+        <v>-0.12</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.12</v>
+        <v>-34.07</v>
       </c>
       <c r="P19" t="n">
-        <v>-34.07</v>
-      </c>
-      <c r="Q19" t="n">
         <v>3619</v>
       </c>
-      <c r="R19" t="inlineStr">
+      <c r="Q19" t="inlineStr">
         <is>
           <t>Salicaceae</t>
         </is>
       </c>
-      <c r="S19" t="inlineStr"/>
+      <c r="R19" t="inlineStr"/>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>Tetrathylacium</t>
+        </is>
+      </c>
       <c r="T19" t="inlineStr">
-        <is>
-          <t>Tetrathylacium</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
         <is>
           <t>macrophyllum</t>
         </is>
@@ -1746,24 +1711,23 @@
       <c r="M20" t="inlineStr"/>
       <c r="N20" t="inlineStr"/>
       <c r="O20" t="inlineStr"/>
-      <c r="P20" t="inlineStr"/>
-      <c r="Q20" t="n">
+      <c r="P20" t="n">
         <v>3622</v>
       </c>
-      <c r="R20" t="inlineStr">
+      <c r="Q20" t="inlineStr">
         <is>
           <t>Clusiaceae</t>
         </is>
       </c>
-      <c r="S20" t="n">
+      <c r="R20" t="n">
         <v>3892</v>
       </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>Chrysochlamys</t>
+        </is>
+      </c>
       <c r="T20" t="inlineStr">
-        <is>
-          <t>Chrysochlamys</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
         <is>
           <t>membranacea</t>
         </is>
@@ -1800,41 +1764,40 @@
       <c r="J21" t="n">
         <v>2220</v>
       </c>
-      <c r="K21" t="inlineStr"/>
-      <c r="L21" t="inlineStr">
+      <c r="K21" t="inlineStr">
         <is>
           <t>p70-3622</t>
         </is>
       </c>
+      <c r="L21" t="n">
+        <v>0.01468680313508528</v>
+      </c>
       <c r="M21" t="n">
-        <v>0.01468680313508528</v>
+        <v>0.4178782536686835</v>
       </c>
       <c r="N21" t="n">
-        <v>0.4178782536686835</v>
+        <v>1.41</v>
       </c>
       <c r="O21" t="n">
-        <v>1.41</v>
+        <v>-33.8</v>
       </c>
       <c r="P21" t="n">
-        <v>-33.8</v>
-      </c>
-      <c r="Q21" t="n">
         <v>3622</v>
       </c>
-      <c r="R21" t="inlineStr">
+      <c r="Q21" t="inlineStr">
         <is>
           <t>Clusiaceae</t>
         </is>
       </c>
-      <c r="S21" t="n">
+      <c r="R21" t="n">
         <v>3892</v>
       </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>Chrysochlamys</t>
+        </is>
+      </c>
       <c r="T21" t="inlineStr">
-        <is>
-          <t>Chrysochlamys</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
         <is>
           <t>membranacea</t>
         </is>
@@ -1871,41 +1834,40 @@
       <c r="J22" t="n">
         <v>2218</v>
       </c>
-      <c r="K22" t="inlineStr"/>
-      <c r="L22" t="inlineStr">
+      <c r="K22" t="inlineStr">
         <is>
           <t>p70-3623</t>
         </is>
       </c>
+      <c r="L22" t="n">
+        <v>0.02344245815416083</v>
+      </c>
       <c r="M22" t="n">
-        <v>0.02344245815416083</v>
+        <v>0.4632356375118532</v>
       </c>
       <c r="N22" t="n">
-        <v>0.4632356375118532</v>
+        <v>1.86</v>
       </c>
       <c r="O22" t="n">
-        <v>1.86</v>
+        <v>-33.18</v>
       </c>
       <c r="P22" t="n">
-        <v>-33.18</v>
-      </c>
-      <c r="Q22" t="n">
         <v>3623</v>
       </c>
-      <c r="R22" t="inlineStr">
+      <c r="Q22" t="inlineStr">
         <is>
           <t>Melastomataceae</t>
         </is>
       </c>
-      <c r="S22" t="n">
+      <c r="R22" t="n">
         <v>3882</v>
       </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>Miconia</t>
+        </is>
+      </c>
       <c r="T22" t="inlineStr">
-        <is>
-          <t>Miconia</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
         <is>
           <t>elata</t>
         </is>
@@ -1953,24 +1915,23 @@
       <c r="M23" t="inlineStr"/>
       <c r="N23" t="inlineStr"/>
       <c r="O23" t="inlineStr"/>
-      <c r="P23" t="inlineStr"/>
-      <c r="Q23" t="n">
+      <c r="P23" t="n">
         <v>3623</v>
       </c>
-      <c r="R23" t="inlineStr">
+      <c r="Q23" t="inlineStr">
         <is>
           <t>Melastomataceae</t>
         </is>
       </c>
-      <c r="S23" t="n">
+      <c r="R23" t="n">
         <v>3882</v>
       </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>Miconia</t>
+        </is>
+      </c>
       <c r="T23" t="inlineStr">
-        <is>
-          <t>Miconia</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
         <is>
           <t>elata</t>
         </is>
@@ -2018,24 +1979,23 @@
       <c r="M24" t="inlineStr"/>
       <c r="N24" t="inlineStr"/>
       <c r="O24" t="inlineStr"/>
-      <c r="P24" t="inlineStr"/>
-      <c r="Q24" t="n">
+      <c r="P24" t="n">
         <v>3624</v>
       </c>
-      <c r="R24" t="inlineStr">
+      <c r="Q24" t="inlineStr">
         <is>
           <t>Myristicaceae</t>
         </is>
       </c>
-      <c r="S24" t="n">
+      <c r="R24" t="n">
         <v>3881</v>
       </c>
+      <c r="S24" t="inlineStr">
+        <is>
+          <t>Virola</t>
+        </is>
+      </c>
       <c r="T24" t="inlineStr">
-        <is>
-          <t>Virola</t>
-        </is>
-      </c>
-      <c r="U24" t="inlineStr">
         <is>
           <t>flexuosa</t>
         </is>
@@ -2079,24 +2039,23 @@
       <c r="M25" t="inlineStr"/>
       <c r="N25" t="inlineStr"/>
       <c r="O25" t="inlineStr"/>
-      <c r="P25" t="inlineStr"/>
-      <c r="Q25" t="n">
+      <c r="P25" t="n">
         <v>3624</v>
       </c>
-      <c r="R25" t="inlineStr">
+      <c r="Q25" t="inlineStr">
         <is>
           <t>Myristicaceae</t>
         </is>
       </c>
-      <c r="S25" t="n">
+      <c r="R25" t="n">
         <v>3881</v>
       </c>
+      <c r="S25" t="inlineStr">
+        <is>
+          <t>Virola</t>
+        </is>
+      </c>
       <c r="T25" t="inlineStr">
-        <is>
-          <t>Virola</t>
-        </is>
-      </c>
-      <c r="U25" t="inlineStr">
         <is>
           <t>flexuosa</t>
         </is>
@@ -2137,27 +2096,22 @@
         </is>
       </c>
       <c r="J26" t="inlineStr"/>
-      <c r="K26" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K26" t="inlineStr"/>
       <c r="L26" t="inlineStr"/>
       <c r="M26" t="inlineStr"/>
       <c r="N26" t="inlineStr"/>
       <c r="O26" t="inlineStr"/>
-      <c r="P26" t="inlineStr"/>
-      <c r="Q26" t="n">
+      <c r="P26" t="n">
         <v>3625</v>
       </c>
-      <c r="R26" t="inlineStr">
+      <c r="Q26" t="inlineStr">
         <is>
           <t>indet</t>
         </is>
       </c>
+      <c r="R26" t="inlineStr"/>
       <c r="S26" t="inlineStr"/>
       <c r="T26" t="inlineStr"/>
-      <c r="U26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="1" t="n">
@@ -2199,18 +2153,17 @@
       <c r="M27" t="inlineStr"/>
       <c r="N27" t="inlineStr"/>
       <c r="O27" t="inlineStr"/>
-      <c r="P27" t="inlineStr"/>
-      <c r="Q27" t="n">
+      <c r="P27" t="n">
         <v>3625</v>
       </c>
-      <c r="R27" t="inlineStr">
+      <c r="Q27" t="inlineStr">
         <is>
           <t>indet</t>
         </is>
       </c>
+      <c r="R27" t="inlineStr"/>
       <c r="S27" t="inlineStr"/>
       <c r="T27" t="inlineStr"/>
-      <c r="U27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="1" t="n">
@@ -2247,27 +2200,22 @@
         </is>
       </c>
       <c r="J28" t="inlineStr"/>
-      <c r="K28" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K28" t="inlineStr"/>
       <c r="L28" t="inlineStr"/>
       <c r="M28" t="inlineStr"/>
       <c r="N28" t="inlineStr"/>
       <c r="O28" t="inlineStr"/>
-      <c r="P28" t="inlineStr"/>
-      <c r="Q28" t="n">
+      <c r="P28" t="n">
         <v>3626</v>
       </c>
-      <c r="R28" t="inlineStr">
+      <c r="Q28" t="inlineStr">
         <is>
           <t>Lauraceae</t>
         </is>
       </c>
+      <c r="R28" t="inlineStr"/>
       <c r="S28" t="inlineStr"/>
       <c r="T28" t="inlineStr"/>
-      <c r="U28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="1" t="n">
@@ -2309,18 +2257,17 @@
       <c r="M29" t="inlineStr"/>
       <c r="N29" t="inlineStr"/>
       <c r="O29" t="inlineStr"/>
-      <c r="P29" t="inlineStr"/>
-      <c r="Q29" t="n">
+      <c r="P29" t="n">
         <v>3626</v>
       </c>
-      <c r="R29" t="inlineStr">
+      <c r="Q29" t="inlineStr">
         <is>
           <t>Lauraceae</t>
         </is>
       </c>
+      <c r="R29" t="inlineStr"/>
       <c r="S29" t="inlineStr"/>
       <c r="T29" t="inlineStr"/>
-      <c r="U29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="1" t="n">
@@ -2362,22 +2309,21 @@
       <c r="M30" t="inlineStr"/>
       <c r="N30" t="inlineStr"/>
       <c r="O30" t="inlineStr"/>
-      <c r="P30" t="inlineStr"/>
-      <c r="Q30" t="n">
+      <c r="P30" t="n">
         <v>3627</v>
       </c>
-      <c r="R30" t="inlineStr">
+      <c r="Q30" t="inlineStr">
         <is>
           <t>Meliaceae</t>
         </is>
       </c>
-      <c r="S30" t="inlineStr"/>
-      <c r="T30" t="inlineStr">
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr">
         <is>
           <t>Guarea</t>
         </is>
       </c>
-      <c r="U30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="1" t="n">
@@ -2414,31 +2360,26 @@
         </is>
       </c>
       <c r="J31" t="inlineStr"/>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K31" t="inlineStr"/>
       <c r="L31" t="inlineStr"/>
       <c r="M31" t="inlineStr"/>
       <c r="N31" t="inlineStr"/>
       <c r="O31" t="inlineStr"/>
-      <c r="P31" t="inlineStr"/>
-      <c r="Q31" t="n">
+      <c r="P31" t="n">
         <v>3627</v>
       </c>
-      <c r="R31" t="inlineStr">
+      <c r="Q31" t="inlineStr">
         <is>
           <t>Meliaceae</t>
         </is>
       </c>
-      <c r="S31" t="inlineStr"/>
-      <c r="T31" t="inlineStr">
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr">
         <is>
           <t>Guarea</t>
         </is>
       </c>
-      <c r="U31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="1" t="n">
@@ -2477,33 +2418,28 @@
       <c r="J32" t="n">
         <v>2223</v>
       </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K32" t="inlineStr"/>
       <c r="L32" t="inlineStr"/>
       <c r="M32" t="inlineStr"/>
       <c r="N32" t="inlineStr"/>
       <c r="O32" t="inlineStr"/>
-      <c r="P32" t="inlineStr"/>
-      <c r="Q32" t="n">
+      <c r="P32" t="n">
         <v>3628</v>
       </c>
-      <c r="R32" t="inlineStr">
+      <c r="Q32" t="inlineStr">
         <is>
           <t>Myristicaceae</t>
         </is>
       </c>
-      <c r="S32" t="n">
+      <c r="R32" t="n">
         <v>3893</v>
       </c>
+      <c r="S32" t="inlineStr">
+        <is>
+          <t>Otoba</t>
+        </is>
+      </c>
       <c r="T32" t="inlineStr">
-        <is>
-          <t>Otoba</t>
-        </is>
-      </c>
-      <c r="U32" t="inlineStr">
         <is>
           <t>parvifolia</t>
         </is>
@@ -2551,24 +2487,23 @@
       <c r="M33" t="inlineStr"/>
       <c r="N33" t="inlineStr"/>
       <c r="O33" t="inlineStr"/>
-      <c r="P33" t="inlineStr"/>
-      <c r="Q33" t="n">
+      <c r="P33" t="n">
         <v>3628</v>
       </c>
-      <c r="R33" t="inlineStr">
+      <c r="Q33" t="inlineStr">
         <is>
           <t>Myristicaceae</t>
         </is>
       </c>
-      <c r="S33" t="n">
+      <c r="R33" t="n">
         <v>3893</v>
       </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Otoba</t>
+        </is>
+      </c>
       <c r="T33" t="inlineStr">
-        <is>
-          <t>Otoba</t>
-        </is>
-      </c>
-      <c r="U33" t="inlineStr">
         <is>
           <t>parvifolia</t>
         </is>
@@ -2605,41 +2540,40 @@
       <c r="J34" t="n">
         <v>2224</v>
       </c>
-      <c r="K34" t="inlineStr"/>
-      <c r="L34" t="inlineStr">
+      <c r="K34" t="inlineStr">
         <is>
           <t>p70-3629</t>
         </is>
       </c>
+      <c r="L34" t="n">
+        <v>0.03545007406100038</v>
+      </c>
       <c r="M34" t="n">
-        <v>0.03545007406100038</v>
+        <v>0.4812524582095935</v>
       </c>
       <c r="N34" t="n">
-        <v>0.4812524582095935</v>
+        <v>1.94</v>
       </c>
       <c r="O34" t="n">
-        <v>1.94</v>
+        <v>-32.25</v>
       </c>
       <c r="P34" t="n">
-        <v>-32.25</v>
-      </c>
-      <c r="Q34" t="n">
         <v>3629</v>
       </c>
-      <c r="R34" t="inlineStr">
+      <c r="Q34" t="inlineStr">
         <is>
           <t>Meliaceae</t>
         </is>
       </c>
-      <c r="S34" t="n">
+      <c r="R34" t="n">
         <v>3885</v>
       </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Trichilia</t>
+        </is>
+      </c>
       <c r="T34" t="inlineStr">
-        <is>
-          <t>Trichilia</t>
-        </is>
-      </c>
-      <c r="U34" t="inlineStr">
         <is>
           <t>septentrionalis</t>
         </is>
@@ -2683,24 +2617,23 @@
       <c r="M35" t="inlineStr"/>
       <c r="N35" t="inlineStr"/>
       <c r="O35" t="inlineStr"/>
-      <c r="P35" t="inlineStr"/>
-      <c r="Q35" t="n">
+      <c r="P35" t="n">
         <v>3631</v>
       </c>
-      <c r="R35" t="inlineStr">
+      <c r="Q35" t="inlineStr">
         <is>
           <t>Lauraceae</t>
         </is>
       </c>
-      <c r="S35" t="n">
+      <c r="R35" t="n">
         <v>3903</v>
       </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Mespilodaphne</t>
+        </is>
+      </c>
       <c r="T35" t="inlineStr">
-        <is>
-          <t>Mespilodaphne</t>
-        </is>
-      </c>
-      <c r="U35" t="inlineStr">
         <is>
           <t>quixos</t>
         </is>
@@ -2743,33 +2676,28 @@
       <c r="J36" t="n">
         <v>2246</v>
       </c>
-      <c r="K36" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K36" t="inlineStr"/>
       <c r="L36" t="inlineStr"/>
       <c r="M36" t="inlineStr"/>
       <c r="N36" t="inlineStr"/>
       <c r="O36" t="inlineStr"/>
-      <c r="P36" t="inlineStr"/>
-      <c r="Q36" t="n">
+      <c r="P36" t="n">
         <v>3631</v>
       </c>
-      <c r="R36" t="inlineStr">
+      <c r="Q36" t="inlineStr">
         <is>
           <t>Lauraceae</t>
         </is>
       </c>
-      <c r="S36" t="n">
+      <c r="R36" t="n">
         <v>3903</v>
       </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Mespilodaphne</t>
+        </is>
+      </c>
       <c r="T36" t="inlineStr">
-        <is>
-          <t>Mespilodaphne</t>
-        </is>
-      </c>
-      <c r="U36" t="inlineStr">
         <is>
           <t>quixos</t>
         </is>
@@ -2810,31 +2738,26 @@
         </is>
       </c>
       <c r="J37" t="inlineStr"/>
-      <c r="K37" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K37" t="inlineStr"/>
       <c r="L37" t="inlineStr"/>
       <c r="M37" t="inlineStr"/>
       <c r="N37" t="inlineStr"/>
       <c r="O37" t="inlineStr"/>
-      <c r="P37" t="inlineStr"/>
-      <c r="Q37" t="n">
+      <c r="P37" t="n">
         <v>3632</v>
       </c>
-      <c r="R37" t="inlineStr">
+      <c r="Q37" t="inlineStr">
         <is>
           <t>Moraceae</t>
         </is>
       </c>
-      <c r="S37" t="inlineStr"/>
+      <c r="R37" t="inlineStr"/>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Pseudolmedia</t>
+        </is>
+      </c>
       <c r="T37" t="inlineStr">
-        <is>
-          <t>Pseudolmedia</t>
-        </is>
-      </c>
-      <c r="U37" t="inlineStr">
         <is>
           <t>laevigata</t>
         </is>
@@ -2880,22 +2803,21 @@
       <c r="M38" t="inlineStr"/>
       <c r="N38" t="inlineStr"/>
       <c r="O38" t="inlineStr"/>
-      <c r="P38" t="inlineStr"/>
-      <c r="Q38" t="n">
+      <c r="P38" t="n">
         <v>3632</v>
       </c>
-      <c r="R38" t="inlineStr">
+      <c r="Q38" t="inlineStr">
         <is>
           <t>Moraceae</t>
         </is>
       </c>
-      <c r="S38" t="inlineStr"/>
+      <c r="R38" t="inlineStr"/>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Pseudolmedia</t>
+        </is>
+      </c>
       <c r="T38" t="inlineStr">
-        <is>
-          <t>Pseudolmedia</t>
-        </is>
-      </c>
-      <c r="U38" t="inlineStr">
         <is>
           <t>laevigata</t>
         </is>
@@ -2938,33 +2860,28 @@
       <c r="J39" t="n">
         <v>2245</v>
       </c>
-      <c r="K39" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K39" t="inlineStr"/>
       <c r="L39" t="inlineStr"/>
       <c r="M39" t="inlineStr"/>
       <c r="N39" t="inlineStr"/>
       <c r="O39" t="inlineStr"/>
-      <c r="P39" t="inlineStr"/>
-      <c r="Q39" t="n">
+      <c r="P39" t="n">
         <v>3634</v>
       </c>
-      <c r="R39" t="inlineStr">
+      <c r="Q39" t="inlineStr">
         <is>
           <t>Annonaceae</t>
         </is>
       </c>
-      <c r="S39" t="n">
+      <c r="R39" t="n">
         <v>3902</v>
       </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Guatteria</t>
+        </is>
+      </c>
       <c r="T39" t="inlineStr">
-        <is>
-          <t>Guatteria</t>
-        </is>
-      </c>
-      <c r="U39" t="inlineStr">
         <is>
           <t>cf multivenia</t>
         </is>
@@ -3001,41 +2918,40 @@
       <c r="J40" t="n">
         <v>2245</v>
       </c>
-      <c r="K40" t="inlineStr"/>
-      <c r="L40" t="inlineStr">
+      <c r="K40" t="inlineStr">
         <is>
           <t>p70-3634</t>
         </is>
       </c>
+      <c r="L40" t="n">
+        <v>0.01173829239074074</v>
+      </c>
       <c r="M40" t="n">
-        <v>0.01173829239074074</v>
+        <v>0.4273580210356233</v>
       </c>
       <c r="N40" t="n">
-        <v>0.4273580210356233</v>
+        <v>0.86</v>
       </c>
       <c r="O40" t="n">
-        <v>0.86</v>
+        <v>-35.61</v>
       </c>
       <c r="P40" t="n">
-        <v>-35.61</v>
-      </c>
-      <c r="Q40" t="n">
         <v>3634</v>
       </c>
-      <c r="R40" t="inlineStr">
+      <c r="Q40" t="inlineStr">
         <is>
           <t>Annonaceae</t>
         </is>
       </c>
-      <c r="S40" t="n">
+      <c r="R40" t="n">
         <v>3902</v>
       </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Guatteria</t>
+        </is>
+      </c>
       <c r="T40" t="inlineStr">
-        <is>
-          <t>Guatteria</t>
-        </is>
-      </c>
-      <c r="U40" t="inlineStr">
         <is>
           <t>cf multivenia</t>
         </is>
@@ -3083,24 +2999,23 @@
       <c r="M41" t="inlineStr"/>
       <c r="N41" t="inlineStr"/>
       <c r="O41" t="inlineStr"/>
-      <c r="P41" t="inlineStr"/>
-      <c r="Q41" t="n">
+      <c r="P41" t="n">
         <v>3635</v>
       </c>
-      <c r="R41" t="inlineStr">
+      <c r="Q41" t="inlineStr">
         <is>
           <t>Annonaceae</t>
         </is>
       </c>
-      <c r="S41" t="n">
+      <c r="R41" t="n">
         <v>3889</v>
       </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Annona</t>
+        </is>
+      </c>
       <c r="T41" t="inlineStr">
-        <is>
-          <t>Annona</t>
-        </is>
-      </c>
-      <c r="U41" t="inlineStr">
         <is>
           <t>helosioides</t>
         </is>
@@ -3137,41 +3052,40 @@
       <c r="J42" t="n">
         <v>2238</v>
       </c>
-      <c r="K42" t="inlineStr"/>
-      <c r="L42" t="inlineStr">
+      <c r="K42" t="inlineStr">
         <is>
           <t>p70-3635</t>
         </is>
       </c>
+      <c r="L42" t="n">
+        <v>0.02329030068816614</v>
+      </c>
       <c r="M42" t="n">
-        <v>0.02329030068816614</v>
+        <v>0.4286406242211068</v>
       </c>
       <c r="N42" t="n">
-        <v>0.4286406242211068</v>
+        <v>0.67</v>
       </c>
       <c r="O42" t="n">
-        <v>0.67</v>
+        <v>-34.74</v>
       </c>
       <c r="P42" t="n">
-        <v>-34.74</v>
-      </c>
-      <c r="Q42" t="n">
         <v>3635</v>
       </c>
-      <c r="R42" t="inlineStr">
+      <c r="Q42" t="inlineStr">
         <is>
           <t>Annonaceae</t>
         </is>
       </c>
-      <c r="S42" t="n">
+      <c r="R42" t="n">
         <v>3889</v>
       </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Annona</t>
+        </is>
+      </c>
       <c r="T42" t="inlineStr">
-        <is>
-          <t>Annona</t>
-        </is>
-      </c>
-      <c r="U42" t="inlineStr">
         <is>
           <t>helosioides</t>
         </is>
@@ -3219,24 +3133,23 @@
       <c r="M43" t="inlineStr"/>
       <c r="N43" t="inlineStr"/>
       <c r="O43" t="inlineStr"/>
-      <c r="P43" t="inlineStr"/>
-      <c r="Q43" t="n">
+      <c r="P43" t="n">
         <v>3637</v>
       </c>
-      <c r="R43" t="inlineStr">
+      <c r="Q43" t="inlineStr">
         <is>
           <t>Sapotaceae</t>
         </is>
       </c>
-      <c r="S43" t="n">
+      <c r="R43" t="n">
         <v>3888</v>
       </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Pouteria</t>
+        </is>
+      </c>
       <c r="T43" t="inlineStr">
-        <is>
-          <t>Pouteria</t>
-        </is>
-      </c>
-      <c r="U43" t="inlineStr">
         <is>
           <t>torta</t>
         </is>
@@ -3277,31 +3190,26 @@
         </is>
       </c>
       <c r="J44" t="inlineStr"/>
-      <c r="K44" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K44" t="inlineStr"/>
       <c r="L44" t="inlineStr"/>
       <c r="M44" t="inlineStr"/>
       <c r="N44" t="inlineStr"/>
       <c r="O44" t="inlineStr"/>
-      <c r="P44" t="inlineStr"/>
-      <c r="Q44" t="n">
+      <c r="P44" t="n">
         <v>3639</v>
       </c>
-      <c r="R44" t="inlineStr">
+      <c r="Q44" t="inlineStr">
         <is>
           <t>Euphorbiaceae</t>
         </is>
       </c>
-      <c r="S44" t="inlineStr"/>
-      <c r="T44" t="inlineStr">
+      <c r="R44" t="inlineStr"/>
+      <c r="S44" t="inlineStr">
         <is>
           <t xml:space="preserve">Alchornea </t>
         </is>
       </c>
-      <c r="U44" t="inlineStr"/>
+      <c r="T44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="1" t="n">
@@ -3343,22 +3251,21 @@
       <c r="M45" t="inlineStr"/>
       <c r="N45" t="inlineStr"/>
       <c r="O45" t="inlineStr"/>
-      <c r="P45" t="inlineStr"/>
-      <c r="Q45" t="n">
+      <c r="P45" t="n">
         <v>3639</v>
       </c>
-      <c r="R45" t="inlineStr">
+      <c r="Q45" t="inlineStr">
         <is>
           <t>Euphorbiaceae</t>
         </is>
       </c>
-      <c r="S45" t="inlineStr"/>
-      <c r="T45" t="inlineStr">
+      <c r="R45" t="inlineStr"/>
+      <c r="S45" t="inlineStr">
         <is>
           <t xml:space="preserve">Alchornea </t>
         </is>
       </c>
-      <c r="U45" t="inlineStr"/>
+      <c r="T45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="1" t="n">
@@ -3400,22 +3307,21 @@
       <c r="M46" t="inlineStr"/>
       <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
-      <c r="P46" t="inlineStr"/>
-      <c r="Q46" t="n">
+      <c r="P46" t="n">
         <v>3640</v>
       </c>
-      <c r="R46" t="inlineStr">
+      <c r="Q46" t="inlineStr">
         <is>
           <t>Salicaceae</t>
         </is>
       </c>
-      <c r="S46" t="inlineStr"/>
+      <c r="R46" t="inlineStr"/>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Banara</t>
+        </is>
+      </c>
       <c r="T46" t="inlineStr">
-        <is>
-          <t>Banara</t>
-        </is>
-      </c>
-      <c r="U46" t="inlineStr">
         <is>
           <t>nitida</t>
         </is>
@@ -3456,31 +3362,26 @@
         </is>
       </c>
       <c r="J47" t="inlineStr"/>
-      <c r="K47" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K47" t="inlineStr"/>
       <c r="L47" t="inlineStr"/>
       <c r="M47" t="inlineStr"/>
       <c r="N47" t="inlineStr"/>
       <c r="O47" t="inlineStr"/>
-      <c r="P47" t="inlineStr"/>
-      <c r="Q47" t="n">
+      <c r="P47" t="n">
         <v>3640</v>
       </c>
-      <c r="R47" t="inlineStr">
+      <c r="Q47" t="inlineStr">
         <is>
           <t>Salicaceae</t>
         </is>
       </c>
-      <c r="S47" t="inlineStr"/>
+      <c r="R47" t="inlineStr"/>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Banara</t>
+        </is>
+      </c>
       <c r="T47" t="inlineStr">
-        <is>
-          <t>Banara</t>
-        </is>
-      </c>
-      <c r="U47" t="inlineStr">
         <is>
           <t>nitida</t>
         </is>
@@ -3526,18 +3427,17 @@
       <c r="M48" t="inlineStr"/>
       <c r="N48" t="inlineStr"/>
       <c r="O48" t="inlineStr"/>
-      <c r="P48" t="inlineStr"/>
-      <c r="Q48" t="n">
+      <c r="P48" t="n">
         <v>3641</v>
       </c>
-      <c r="R48" t="inlineStr">
+      <c r="Q48" t="inlineStr">
         <is>
           <t>indet</t>
         </is>
       </c>
+      <c r="R48" t="inlineStr"/>
       <c r="S48" t="inlineStr"/>
       <c r="T48" t="inlineStr"/>
-      <c r="U48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="1" t="n">
@@ -3574,27 +3474,22 @@
         </is>
       </c>
       <c r="J49" t="inlineStr"/>
-      <c r="K49" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K49" t="inlineStr"/>
       <c r="L49" t="inlineStr"/>
       <c r="M49" t="inlineStr"/>
       <c r="N49" t="inlineStr"/>
       <c r="O49" t="inlineStr"/>
-      <c r="P49" t="inlineStr"/>
-      <c r="Q49" t="n">
+      <c r="P49" t="n">
         <v>3641</v>
       </c>
-      <c r="R49" t="inlineStr">
+      <c r="Q49" t="inlineStr">
         <is>
           <t>indet</t>
         </is>
       </c>
+      <c r="R49" t="inlineStr"/>
       <c r="S49" t="inlineStr"/>
       <c r="T49" t="inlineStr"/>
-      <c r="U49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="1" t="n">
@@ -3638,24 +3533,23 @@
       <c r="M50" t="inlineStr"/>
       <c r="N50" t="inlineStr"/>
       <c r="O50" t="inlineStr"/>
-      <c r="P50" t="inlineStr"/>
-      <c r="Q50" t="n">
+      <c r="P50" t="n">
         <v>3642</v>
       </c>
-      <c r="R50" t="inlineStr">
+      <c r="Q50" t="inlineStr">
         <is>
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="S50" t="n">
+      <c r="R50" t="n">
         <v>3897</v>
       </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Chimarrhis</t>
+        </is>
+      </c>
       <c r="T50" t="inlineStr">
-        <is>
-          <t>Chimarrhis</t>
-        </is>
-      </c>
-      <c r="U50" t="inlineStr">
         <is>
           <t>cf glabriflora</t>
         </is>
@@ -3703,24 +3597,23 @@
       <c r="M51" t="inlineStr"/>
       <c r="N51" t="inlineStr"/>
       <c r="O51" t="inlineStr"/>
-      <c r="P51" t="inlineStr"/>
-      <c r="Q51" t="n">
+      <c r="P51" t="n">
         <v>3642</v>
       </c>
-      <c r="R51" t="inlineStr">
+      <c r="Q51" t="inlineStr">
         <is>
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="S51" t="n">
+      <c r="R51" t="n">
         <v>3897</v>
       </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Chimarrhis</t>
+        </is>
+      </c>
       <c r="T51" t="inlineStr">
-        <is>
-          <t>Chimarrhis</t>
-        </is>
-      </c>
-      <c r="U51" t="inlineStr">
         <is>
           <t>cf glabriflora</t>
         </is>
@@ -3757,41 +3650,40 @@
       <c r="J52" t="n">
         <v>2233</v>
       </c>
-      <c r="K52" t="inlineStr"/>
-      <c r="L52" t="inlineStr">
+      <c r="K52" t="inlineStr">
         <is>
           <t>p70-3642</t>
         </is>
       </c>
+      <c r="L52" t="n">
+        <v>0.01994461056810911</v>
+      </c>
       <c r="M52" t="n">
-        <v>0.01994461056810911</v>
+        <v>0.4625106483743614</v>
       </c>
       <c r="N52" t="n">
-        <v>0.4625106483743614</v>
+        <v>1.91</v>
       </c>
       <c r="O52" t="n">
-        <v>1.91</v>
+        <v>-31.42</v>
       </c>
       <c r="P52" t="n">
-        <v>-31.42</v>
-      </c>
-      <c r="Q52" t="n">
         <v>3642</v>
       </c>
-      <c r="R52" t="inlineStr">
+      <c r="Q52" t="inlineStr">
         <is>
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="S52" t="n">
+      <c r="R52" t="n">
         <v>3897</v>
       </c>
+      <c r="S52" t="inlineStr">
+        <is>
+          <t>Chimarrhis</t>
+        </is>
+      </c>
       <c r="T52" t="inlineStr">
-        <is>
-          <t>Chimarrhis</t>
-        </is>
-      </c>
-      <c r="U52" t="inlineStr">
         <is>
           <t>cf glabriflora</t>
         </is>
@@ -3834,33 +3726,28 @@
       <c r="J53" t="n">
         <v>2239</v>
       </c>
-      <c r="K53" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K53" t="inlineStr"/>
       <c r="L53" t="inlineStr"/>
       <c r="M53" t="inlineStr"/>
       <c r="N53" t="inlineStr"/>
       <c r="O53" t="inlineStr"/>
-      <c r="P53" t="inlineStr"/>
-      <c r="Q53" t="n">
+      <c r="P53" t="n">
         <v>3643</v>
       </c>
-      <c r="R53" t="inlineStr">
+      <c r="Q53" t="inlineStr">
         <is>
           <t>Melastomataceae</t>
         </is>
       </c>
-      <c r="S53" t="n">
+      <c r="R53" t="n">
         <v>3899</v>
       </c>
-      <c r="T53" t="inlineStr">
+      <c r="S53" t="inlineStr">
         <is>
           <t>Miconia</t>
         </is>
       </c>
-      <c r="U53" t="inlineStr"/>
+      <c r="T53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="n">
@@ -3900,24 +3787,23 @@
       <c r="M54" t="inlineStr"/>
       <c r="N54" t="inlineStr"/>
       <c r="O54" t="inlineStr"/>
-      <c r="P54" t="inlineStr"/>
-      <c r="Q54" t="n">
+      <c r="P54" t="n">
         <v>3643</v>
       </c>
-      <c r="R54" t="inlineStr">
+      <c r="Q54" t="inlineStr">
         <is>
           <t>Melastomataceae</t>
         </is>
       </c>
-      <c r="S54" t="n">
+      <c r="R54" t="n">
         <v>3899</v>
       </c>
-      <c r="T54" t="inlineStr">
+      <c r="S54" t="inlineStr">
         <is>
           <t>Miconia</t>
         </is>
       </c>
-      <c r="U54" t="inlineStr"/>
+      <c r="T54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="1" t="n">
@@ -3961,24 +3847,23 @@
       <c r="M55" t="inlineStr"/>
       <c r="N55" t="inlineStr"/>
       <c r="O55" t="inlineStr"/>
-      <c r="P55" t="inlineStr"/>
-      <c r="Q55" t="n">
+      <c r="P55" t="n">
         <v>3643</v>
       </c>
-      <c r="R55" t="inlineStr">
+      <c r="Q55" t="inlineStr">
         <is>
           <t>Melastomataceae</t>
         </is>
       </c>
-      <c r="S55" t="n">
+      <c r="R55" t="n">
         <v>3899</v>
       </c>
-      <c r="T55" t="inlineStr">
+      <c r="S55" t="inlineStr">
         <is>
           <t>Miconia</t>
         </is>
       </c>
-      <c r="U55" t="inlineStr"/>
+      <c r="T55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="1" t="n">
@@ -4015,31 +3900,26 @@
         </is>
       </c>
       <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
       <c r="M56" t="inlineStr"/>
       <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
-      <c r="P56" t="inlineStr"/>
-      <c r="Q56" t="n">
+      <c r="P56" t="n">
         <v>3644</v>
       </c>
-      <c r="R56" t="inlineStr">
+      <c r="Q56" t="inlineStr">
         <is>
           <t>Salicacia</t>
         </is>
       </c>
-      <c r="S56" t="inlineStr"/>
-      <c r="T56" t="inlineStr">
+      <c r="R56" t="inlineStr"/>
+      <c r="S56" t="inlineStr">
         <is>
           <t>Laetia</t>
         </is>
       </c>
-      <c r="U56" t="inlineStr"/>
+      <c r="T56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="1" t="n">
@@ -4081,22 +3961,21 @@
       <c r="M57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="O57" t="inlineStr"/>
-      <c r="P57" t="inlineStr"/>
-      <c r="Q57" t="n">
+      <c r="P57" t="n">
         <v>3644</v>
       </c>
-      <c r="R57" t="inlineStr">
+      <c r="Q57" t="inlineStr">
         <is>
           <t>Salicacia</t>
         </is>
       </c>
-      <c r="S57" t="inlineStr"/>
-      <c r="T57" t="inlineStr">
+      <c r="R57" t="inlineStr"/>
+      <c r="S57" t="inlineStr">
         <is>
           <t>Laetia</t>
         </is>
       </c>
-      <c r="U57" t="inlineStr"/>
+      <c r="T57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="1" t="n">
@@ -4133,31 +4012,26 @@
         </is>
       </c>
       <c r="J58" t="inlineStr"/>
-      <c r="K58" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
       <c r="M58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="O58" t="inlineStr"/>
-      <c r="P58" t="inlineStr"/>
-      <c r="Q58" t="n">
+      <c r="P58" t="n">
         <v>3645</v>
       </c>
-      <c r="R58" t="inlineStr">
+      <c r="Q58" t="inlineStr">
         <is>
           <t>Salicacia</t>
         </is>
       </c>
-      <c r="S58" t="inlineStr"/>
-      <c r="T58" t="inlineStr">
+      <c r="R58" t="inlineStr"/>
+      <c r="S58" t="inlineStr">
         <is>
           <t>Laetia</t>
         </is>
       </c>
-      <c r="U58" t="inlineStr"/>
+      <c r="T58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="1" t="n">
@@ -4193,22 +4067,21 @@
       <c r="M59" t="inlineStr"/>
       <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
-      <c r="P59" t="inlineStr"/>
-      <c r="Q59" t="n">
+      <c r="P59" t="n">
         <v>3645</v>
       </c>
-      <c r="R59" t="inlineStr">
+      <c r="Q59" t="inlineStr">
         <is>
           <t>Salicacia</t>
         </is>
       </c>
-      <c r="S59" t="inlineStr"/>
-      <c r="T59" t="inlineStr">
+      <c r="R59" t="inlineStr"/>
+      <c r="S59" t="inlineStr">
         <is>
           <t>Laetia</t>
         </is>
       </c>
-      <c r="U59" t="inlineStr"/>
+      <c r="T59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="1" t="n">
@@ -4250,22 +4123,21 @@
       <c r="M60" t="inlineStr"/>
       <c r="N60" t="inlineStr"/>
       <c r="O60" t="inlineStr"/>
-      <c r="P60" t="inlineStr"/>
-      <c r="Q60" t="n">
+      <c r="P60" t="n">
         <v>3645</v>
       </c>
-      <c r="R60" t="inlineStr">
+      <c r="Q60" t="inlineStr">
         <is>
           <t>Salicacia</t>
         </is>
       </c>
-      <c r="S60" t="inlineStr"/>
-      <c r="T60" t="inlineStr">
+      <c r="R60" t="inlineStr"/>
+      <c r="S60" t="inlineStr">
         <is>
           <t>Laetia</t>
         </is>
       </c>
-      <c r="U60" t="inlineStr"/>
+      <c r="T60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="1" t="n">
@@ -4309,24 +4181,23 @@
       <c r="M61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="O61" t="inlineStr"/>
-      <c r="P61" t="inlineStr"/>
-      <c r="Q61" t="n">
+      <c r="P61" t="n">
         <v>3647</v>
       </c>
-      <c r="R61" t="inlineStr">
+      <c r="Q61" t="inlineStr">
         <is>
           <t>Moraceae</t>
         </is>
       </c>
-      <c r="S61" t="n">
+      <c r="R61" t="n">
         <v>3877</v>
       </c>
+      <c r="S61" t="inlineStr">
+        <is>
+          <t>Maclura</t>
+        </is>
+      </c>
       <c r="T61" t="inlineStr">
-        <is>
-          <t>Maclura</t>
-        </is>
-      </c>
-      <c r="U61" t="inlineStr">
         <is>
           <t>tinctoria</t>
         </is>
@@ -4374,22 +4245,21 @@
       <c r="M62" t="inlineStr"/>
       <c r="N62" t="inlineStr"/>
       <c r="O62" t="inlineStr"/>
-      <c r="P62" t="inlineStr"/>
-      <c r="Q62" t="n">
+      <c r="P62" t="n">
         <v>3648</v>
       </c>
-      <c r="R62" t="inlineStr">
+      <c r="Q62" t="inlineStr">
         <is>
           <t>Burseraceae</t>
         </is>
       </c>
-      <c r="S62" t="inlineStr"/>
-      <c r="T62" t="inlineStr">
+      <c r="R62" t="inlineStr"/>
+      <c r="S62" t="inlineStr">
         <is>
           <t>Protium</t>
         </is>
       </c>
-      <c r="U62" t="inlineStr"/>
+      <c r="T62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="1" t="n">
@@ -4422,41 +4292,40 @@
       <c r="J63" t="n">
         <v>2210</v>
       </c>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr">
+      <c r="K63" t="inlineStr">
         <is>
           <t>p70-3649</t>
         </is>
       </c>
+      <c r="L63" t="n">
+        <v>0.021352396</v>
+      </c>
       <c r="M63" t="n">
-        <v>0.021352396</v>
+        <v>0.483725522</v>
       </c>
       <c r="N63" t="n">
-        <v>0.483725522</v>
+        <v>2.737714646464645</v>
       </c>
       <c r="O63" t="n">
-        <v>2.737714646464645</v>
+        <v>-31.18964284199364</v>
       </c>
       <c r="P63" t="n">
-        <v>-31.18964284199364</v>
-      </c>
-      <c r="Q63" t="n">
         <v>3649</v>
       </c>
-      <c r="R63" t="inlineStr">
+      <c r="Q63" t="inlineStr">
         <is>
           <t>Sapotaceae</t>
         </is>
       </c>
-      <c r="S63" t="n">
+      <c r="R63" t="n">
         <v>3878</v>
       </c>
+      <c r="S63" t="inlineStr">
+        <is>
+          <t>Micropholis</t>
+        </is>
+      </c>
       <c r="T63" t="inlineStr">
-        <is>
-          <t>Micropholis</t>
-        </is>
-      </c>
-      <c r="U63" t="inlineStr">
         <is>
           <t>guyanensis</t>
         </is>
@@ -4496,18 +4365,17 @@
       <c r="M64" t="inlineStr"/>
       <c r="N64" t="inlineStr"/>
       <c r="O64" t="inlineStr"/>
-      <c r="P64" t="inlineStr"/>
-      <c r="Q64" t="n">
+      <c r="P64" t="n">
         <v>3650</v>
       </c>
-      <c r="R64" t="inlineStr">
+      <c r="Q64" t="inlineStr">
         <is>
           <t>indet</t>
         </is>
       </c>
+      <c r="R64" t="inlineStr"/>
       <c r="S64" t="inlineStr"/>
       <c r="T64" t="inlineStr"/>
-      <c r="U64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="1" t="n">
@@ -4544,27 +4412,22 @@
         </is>
       </c>
       <c r="J65" t="inlineStr"/>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
       <c r="M65" t="inlineStr"/>
       <c r="N65" t="inlineStr"/>
       <c r="O65" t="inlineStr"/>
-      <c r="P65" t="inlineStr"/>
-      <c r="Q65" t="n">
+      <c r="P65" t="n">
         <v>3650</v>
       </c>
-      <c r="R65" t="inlineStr">
+      <c r="Q65" t="inlineStr">
         <is>
           <t>indet</t>
         </is>
       </c>
+      <c r="R65" t="inlineStr"/>
       <c r="S65" t="inlineStr"/>
       <c r="T65" t="inlineStr"/>
-      <c r="U65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="1" t="n">
@@ -4606,18 +4469,17 @@
       <c r="M66" t="inlineStr"/>
       <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
-      <c r="P66" t="inlineStr"/>
-      <c r="Q66" t="n">
+      <c r="P66" t="n">
         <v>3650</v>
       </c>
-      <c r="R66" t="inlineStr">
+      <c r="Q66" t="inlineStr">
         <is>
           <t>indet</t>
         </is>
       </c>
+      <c r="R66" t="inlineStr"/>
       <c r="S66" t="inlineStr"/>
       <c r="T66" t="inlineStr"/>
-      <c r="U66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="1" t="n">
@@ -4659,22 +4521,21 @@
       <c r="M67" t="inlineStr"/>
       <c r="N67" t="inlineStr"/>
       <c r="O67" t="inlineStr"/>
-      <c r="P67" t="inlineStr"/>
-      <c r="Q67" t="n">
+      <c r="P67" t="n">
         <v>3652</v>
       </c>
-      <c r="R67" t="inlineStr">
+      <c r="Q67" t="inlineStr">
         <is>
           <t>Meliaceae</t>
         </is>
       </c>
-      <c r="S67" t="inlineStr"/>
-      <c r="T67" t="inlineStr">
+      <c r="R67" t="inlineStr"/>
+      <c r="S67" t="inlineStr">
         <is>
           <t>Guarea</t>
         </is>
       </c>
-      <c r="U67" t="inlineStr"/>
+      <c r="T67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="1" t="n">
@@ -4711,31 +4572,26 @@
         </is>
       </c>
       <c r="J68" t="inlineStr"/>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="M68" t="inlineStr"/>
       <c r="N68" t="inlineStr"/>
       <c r="O68" t="inlineStr"/>
-      <c r="P68" t="inlineStr"/>
-      <c r="Q68" t="n">
+      <c r="P68" t="n">
         <v>3652</v>
       </c>
-      <c r="R68" t="inlineStr">
+      <c r="Q68" t="inlineStr">
         <is>
           <t>Meliaceae</t>
         </is>
       </c>
-      <c r="S68" t="inlineStr"/>
-      <c r="T68" t="inlineStr">
+      <c r="R68" t="inlineStr"/>
+      <c r="S68" t="inlineStr">
         <is>
           <t>Guarea</t>
         </is>
       </c>
-      <c r="U68" t="inlineStr"/>
+      <c r="T68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="1" t="n">
@@ -4779,26 +4635,25 @@
       <c r="M69" t="inlineStr"/>
       <c r="N69" t="inlineStr"/>
       <c r="O69" t="inlineStr"/>
-      <c r="P69" t="inlineStr"/>
-      <c r="Q69" t="n">
+      <c r="P69" t="n">
         <v>3654</v>
       </c>
+      <c r="Q69" t="inlineStr">
+        <is>
+          <t>Rubiaceae</t>
+        </is>
+      </c>
       <c r="R69" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="S69" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>Faramea</t>
         </is>
       </c>
       <c r="T69" t="inlineStr">
-        <is>
-          <t>Faramea</t>
-        </is>
-      </c>
-      <c r="U69" t="inlineStr">
         <is>
           <t>parvibractea</t>
         </is>
@@ -4846,24 +4701,23 @@
       <c r="M70" t="inlineStr"/>
       <c r="N70" t="inlineStr"/>
       <c r="O70" t="inlineStr"/>
-      <c r="P70" t="inlineStr"/>
-      <c r="Q70" t="n">
+      <c r="P70" t="n">
         <v>3654</v>
       </c>
-      <c r="R70" t="inlineStr">
+      <c r="Q70" t="inlineStr">
         <is>
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="S70" t="n">
+      <c r="R70" t="n">
         <v>3876</v>
       </c>
+      <c r="S70" t="inlineStr">
+        <is>
+          <t>Faramea</t>
+        </is>
+      </c>
       <c r="T70" t="inlineStr">
-        <is>
-          <t>Faramea</t>
-        </is>
-      </c>
-      <c r="U70" t="inlineStr">
         <is>
           <t>parvibractea</t>
         </is>
@@ -4900,41 +4754,40 @@
       <c r="J71" t="n">
         <v>2205</v>
       </c>
-      <c r="K71" t="inlineStr"/>
-      <c r="L71" t="inlineStr">
+      <c r="K71" t="inlineStr">
         <is>
           <t>p70-3654</t>
         </is>
       </c>
+      <c r="L71" t="n">
+        <v>0.02201823142746578</v>
+      </c>
       <c r="M71" t="n">
-        <v>0.02201823142746578</v>
+        <v>0.3956347601824302</v>
       </c>
       <c r="N71" t="n">
-        <v>0.3956347601824302</v>
+        <v>1.86</v>
       </c>
       <c r="O71" t="n">
-        <v>1.86</v>
+        <v>-33.86</v>
       </c>
       <c r="P71" t="n">
-        <v>-33.86</v>
-      </c>
-      <c r="Q71" t="n">
         <v>3654</v>
       </c>
-      <c r="R71" t="inlineStr">
+      <c r="Q71" t="inlineStr">
         <is>
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="S71" t="n">
+      <c r="R71" t="n">
         <v>3876</v>
       </c>
+      <c r="S71" t="inlineStr">
+        <is>
+          <t>Faramea</t>
+        </is>
+      </c>
       <c r="T71" t="inlineStr">
-        <is>
-          <t>Faramea</t>
-        </is>
-      </c>
-      <c r="U71" t="inlineStr">
         <is>
           <t>parvibractea</t>
         </is>
@@ -4971,43 +4824,42 @@
       <c r="J72" t="n">
         <v>2205</v>
       </c>
-      <c r="K72" t="inlineStr"/>
-      <c r="L72" t="inlineStr">
+      <c r="K72" t="inlineStr">
         <is>
           <t>p70-3654</t>
         </is>
       </c>
+      <c r="L72" t="n">
+        <v>0.02201823142746578</v>
+      </c>
       <c r="M72" t="n">
-        <v>0.02201823142746578</v>
+        <v>0.3956347601824302</v>
       </c>
       <c r="N72" t="n">
-        <v>0.3956347601824302</v>
+        <v>1.86</v>
       </c>
       <c r="O72" t="n">
-        <v>1.86</v>
+        <v>-33.86</v>
       </c>
       <c r="P72" t="n">
-        <v>-33.86</v>
-      </c>
-      <c r="Q72" t="n">
         <v>3654</v>
       </c>
+      <c r="Q72" t="inlineStr">
+        <is>
+          <t>Rubiaceae</t>
+        </is>
+      </c>
       <c r="R72" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
+          <t>3876</t>
         </is>
       </c>
       <c r="S72" t="inlineStr">
         <is>
-          <t>3876</t>
+          <t>Faramea</t>
         </is>
       </c>
       <c r="T72" t="inlineStr">
-        <is>
-          <t>Faramea</t>
-        </is>
-      </c>
-      <c r="U72" t="inlineStr">
         <is>
           <t>parvibractea</t>
         </is>
@@ -5050,33 +4902,28 @@
       <c r="J73" t="n">
         <v>2230</v>
       </c>
-      <c r="K73" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K73" t="inlineStr"/>
       <c r="L73" t="inlineStr"/>
       <c r="M73" t="inlineStr"/>
       <c r="N73" t="inlineStr"/>
       <c r="O73" t="inlineStr"/>
-      <c r="P73" t="inlineStr"/>
-      <c r="Q73" t="n">
+      <c r="P73" t="n">
         <v>3655</v>
       </c>
-      <c r="R73" t="inlineStr">
+      <c r="Q73" t="inlineStr">
         <is>
           <t>Bignoniaceae</t>
         </is>
       </c>
-      <c r="S73" t="n">
+      <c r="R73" t="n">
         <v>3887</v>
       </c>
+      <c r="S73" t="inlineStr">
+        <is>
+          <t>Jacaranda</t>
+        </is>
+      </c>
       <c r="T73" t="inlineStr">
-        <is>
-          <t>Jacaranda</t>
-        </is>
-      </c>
-      <c r="U73" t="inlineStr">
         <is>
           <t>copaia</t>
         </is>
@@ -5117,27 +4964,22 @@
         </is>
       </c>
       <c r="J74" t="inlineStr"/>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="M74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
       <c r="O74" t="inlineStr"/>
-      <c r="P74" t="inlineStr"/>
-      <c r="Q74" t="n">
+      <c r="P74" t="n">
         <v>3656</v>
       </c>
-      <c r="R74" t="inlineStr">
+      <c r="Q74" t="inlineStr">
         <is>
           <t>indet</t>
         </is>
       </c>
+      <c r="R74" t="inlineStr"/>
       <c r="S74" t="inlineStr"/>
       <c r="T74" t="inlineStr"/>
-      <c r="U74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="1" t="n">
@@ -5179,18 +5021,17 @@
       <c r="M75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
       <c r="O75" t="inlineStr"/>
-      <c r="P75" t="inlineStr"/>
-      <c r="Q75" t="n">
+      <c r="P75" t="n">
         <v>3656</v>
       </c>
-      <c r="R75" t="inlineStr">
+      <c r="Q75" t="inlineStr">
         <is>
           <t>indet</t>
         </is>
       </c>
+      <c r="R75" t="inlineStr"/>
       <c r="S75" t="inlineStr"/>
       <c r="T75" t="inlineStr"/>
-      <c r="U75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="1" t="n">
@@ -5225,41 +5066,40 @@
       <c r="J76" t="n">
         <v>2202</v>
       </c>
-      <c r="K76" t="inlineStr"/>
-      <c r="L76" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>p70-3658</t>
         </is>
       </c>
+      <c r="L76" t="n">
+        <v>0.022130638</v>
+      </c>
       <c r="M76" t="n">
-        <v>0.022130638</v>
+        <v>0.436691485</v>
       </c>
       <c r="N76" t="n">
-        <v>0.436691485</v>
+        <v>2.122085858585857</v>
       </c>
       <c r="O76" t="n">
-        <v>2.122085858585857</v>
+        <v>-33.32435503711559</v>
       </c>
       <c r="P76" t="n">
-        <v>-33.32435503711559</v>
-      </c>
-      <c r="Q76" t="n">
         <v>3658</v>
       </c>
-      <c r="R76" t="inlineStr">
+      <c r="Q76" t="inlineStr">
         <is>
           <t>Achariaceae</t>
         </is>
       </c>
-      <c r="S76" t="n">
+      <c r="R76" t="n">
         <v>3873</v>
       </c>
+      <c r="S76" t="inlineStr">
+        <is>
+          <t>Lindackeria</t>
+        </is>
+      </c>
       <c r="T76" t="inlineStr">
-        <is>
-          <t>Lindackeria</t>
-        </is>
-      </c>
-      <c r="U76" t="inlineStr">
         <is>
           <t>paludosa</t>
         </is>
@@ -5296,41 +5136,40 @@
       <c r="J77" t="n">
         <v>2202</v>
       </c>
-      <c r="K77" t="inlineStr"/>
-      <c r="L77" t="inlineStr">
+      <c r="K77" t="inlineStr">
         <is>
           <t>p70-3658</t>
         </is>
       </c>
+      <c r="L77" t="n">
+        <v>0.022130638</v>
+      </c>
       <c r="M77" t="n">
-        <v>0.022130638</v>
+        <v>0.436691485</v>
       </c>
       <c r="N77" t="n">
-        <v>0.436691485</v>
+        <v>2.122085858585857</v>
       </c>
       <c r="O77" t="n">
-        <v>2.122085858585857</v>
+        <v>-33.32435503711559</v>
       </c>
       <c r="P77" t="n">
-        <v>-33.32435503711559</v>
-      </c>
-      <c r="Q77" t="n">
         <v>3658</v>
       </c>
-      <c r="R77" t="inlineStr">
+      <c r="Q77" t="inlineStr">
         <is>
           <t>Achariaceae</t>
         </is>
       </c>
-      <c r="S77" t="n">
+      <c r="R77" t="n">
         <v>3873</v>
       </c>
+      <c r="S77" t="inlineStr">
+        <is>
+          <t>Lindackeria</t>
+        </is>
+      </c>
       <c r="T77" t="inlineStr">
-        <is>
-          <t>Lindackeria</t>
-        </is>
-      </c>
-      <c r="U77" t="inlineStr">
         <is>
           <t>paludosa</t>
         </is>
@@ -5371,31 +5210,26 @@
         </is>
       </c>
       <c r="J78" t="inlineStr"/>
-      <c r="K78" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K78" t="inlineStr"/>
       <c r="L78" t="inlineStr"/>
       <c r="M78" t="inlineStr"/>
       <c r="N78" t="inlineStr"/>
       <c r="O78" t="inlineStr"/>
-      <c r="P78" t="inlineStr"/>
-      <c r="Q78" t="n">
+      <c r="P78" t="n">
         <v>3659</v>
       </c>
-      <c r="R78" t="inlineStr">
+      <c r="Q78" t="inlineStr">
         <is>
           <t>Meliaceae</t>
         </is>
       </c>
-      <c r="S78" t="inlineStr"/>
+      <c r="R78" t="inlineStr"/>
+      <c r="S78" t="inlineStr">
+        <is>
+          <t>Guarea</t>
+        </is>
+      </c>
       <c r="T78" t="inlineStr">
-        <is>
-          <t>Guarea</t>
-        </is>
-      </c>
-      <c r="U78" t="inlineStr">
         <is>
           <t>pterorhachis</t>
         </is>
@@ -5441,22 +5275,21 @@
       <c r="M79" t="inlineStr"/>
       <c r="N79" t="inlineStr"/>
       <c r="O79" t="inlineStr"/>
-      <c r="P79" t="inlineStr"/>
-      <c r="Q79" t="n">
+      <c r="P79" t="n">
         <v>3659</v>
       </c>
-      <c r="R79" t="inlineStr">
+      <c r="Q79" t="inlineStr">
         <is>
           <t>Meliaceae</t>
         </is>
       </c>
-      <c r="S79" t="inlineStr"/>
+      <c r="R79" t="inlineStr"/>
+      <c r="S79" t="inlineStr">
+        <is>
+          <t>Guarea</t>
+        </is>
+      </c>
       <c r="T79" t="inlineStr">
-        <is>
-          <t>Guarea</t>
-        </is>
-      </c>
-      <c r="U79" t="inlineStr">
         <is>
           <t>pterorhachis</t>
         </is>
@@ -5491,31 +5324,30 @@
       <c r="H80" t="inlineStr"/>
       <c r="I80" t="inlineStr"/>
       <c r="J80" t="inlineStr"/>
-      <c r="K80" t="inlineStr"/>
-      <c r="L80" t="inlineStr">
+      <c r="K80" t="inlineStr">
         <is>
           <t>p69-8617</t>
         </is>
       </c>
+      <c r="L80" t="n">
+        <v>0.01853964833900083</v>
+      </c>
       <c r="M80" t="n">
-        <v>0.01853964833900083</v>
+        <v>0.4430114955907127</v>
       </c>
       <c r="N80" t="n">
-        <v>0.4430114955907127</v>
+        <v>2.34</v>
       </c>
       <c r="O80" t="n">
-        <v>2.34</v>
+        <v>-32.61</v>
       </c>
       <c r="P80" t="n">
-        <v>-32.61</v>
-      </c>
-      <c r="Q80" t="n">
         <v>8617</v>
       </c>
+      <c r="Q80" t="inlineStr"/>
       <c r="R80" t="inlineStr"/>
       <c r="S80" t="inlineStr"/>
       <c r="T80" t="inlineStr"/>
-      <c r="U80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="1" t="n">
@@ -5553,14 +5385,13 @@
       <c r="M81" t="inlineStr"/>
       <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
-      <c r="P81" t="inlineStr"/>
-      <c r="Q81" t="n">
+      <c r="P81" t="n">
         <v>8640</v>
       </c>
+      <c r="Q81" t="inlineStr"/>
       <c r="R81" t="inlineStr"/>
       <c r="S81" t="inlineStr"/>
       <c r="T81" t="inlineStr"/>
-      <c r="U81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="1" t="n">
@@ -5597,31 +5428,26 @@
         </is>
       </c>
       <c r="J82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
       <c r="M82" t="inlineStr"/>
       <c r="N82" t="inlineStr"/>
       <c r="O82" t="inlineStr"/>
-      <c r="P82" t="inlineStr"/>
-      <c r="Q82" t="n">
+      <c r="P82" t="n">
         <v>8688</v>
       </c>
-      <c r="R82" t="inlineStr">
+      <c r="Q82" t="inlineStr">
         <is>
           <t>Meliaceae</t>
         </is>
       </c>
-      <c r="S82" t="inlineStr"/>
+      <c r="R82" t="inlineStr"/>
+      <c r="S82" t="inlineStr">
+        <is>
+          <t>Guarea</t>
+        </is>
+      </c>
       <c r="T82" t="inlineStr">
-        <is>
-          <t>Guarea</t>
-        </is>
-      </c>
-      <c r="U82" t="inlineStr">
         <is>
           <t>sp.</t>
         </is>
@@ -5667,22 +5493,21 @@
       <c r="M83" t="inlineStr"/>
       <c r="N83" t="inlineStr"/>
       <c r="O83" t="inlineStr"/>
-      <c r="P83" t="inlineStr"/>
-      <c r="Q83" t="n">
+      <c r="P83" t="n">
         <v>8688</v>
       </c>
-      <c r="R83" t="inlineStr">
+      <c r="Q83" t="inlineStr">
         <is>
           <t>Meliaceae</t>
         </is>
       </c>
-      <c r="S83" t="inlineStr"/>
+      <c r="R83" t="inlineStr"/>
+      <c r="S83" t="inlineStr">
+        <is>
+          <t>Guarea</t>
+        </is>
+      </c>
       <c r="T83" t="inlineStr">
-        <is>
-          <t>Guarea</t>
-        </is>
-      </c>
-      <c r="U83" t="inlineStr">
         <is>
           <t>sp.</t>
         </is>
@@ -5717,39 +5542,38 @@
       <c r="H84" t="inlineStr"/>
       <c r="I84" t="inlineStr"/>
       <c r="J84" t="inlineStr"/>
-      <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr">
+      <c r="K84" t="inlineStr">
         <is>
           <t>p72-8688</t>
         </is>
       </c>
+      <c r="L84" t="n">
+        <v>0.026106295</v>
+      </c>
       <c r="M84" t="n">
-        <v>0.026106295</v>
+        <v>0.456459654</v>
       </c>
       <c r="N84" t="n">
-        <v>0.456459654</v>
+        <v>2.867320707070705</v>
       </c>
       <c r="O84" t="n">
-        <v>2.867320707070705</v>
+        <v>-30.49869734888653</v>
       </c>
       <c r="P84" t="n">
-        <v>-30.49869734888653</v>
-      </c>
-      <c r="Q84" t="n">
         <v>8688</v>
       </c>
-      <c r="R84" t="inlineStr">
+      <c r="Q84" t="inlineStr">
         <is>
           <t>Meliaceae</t>
         </is>
       </c>
-      <c r="S84" t="inlineStr"/>
+      <c r="R84" t="inlineStr"/>
+      <c r="S84" t="inlineStr">
+        <is>
+          <t>Guarea</t>
+        </is>
+      </c>
       <c r="T84" t="inlineStr">
-        <is>
-          <t>Guarea</t>
-        </is>
-      </c>
-      <c r="U84" t="inlineStr">
         <is>
           <t>sp.</t>
         </is>
@@ -5786,41 +5610,40 @@
       <c r="J85" t="n">
         <v>2310</v>
       </c>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr">
+      <c r="K85" t="inlineStr">
         <is>
           <t>p72-8689</t>
         </is>
       </c>
+      <c r="L85" t="n">
+        <v>0.015163699</v>
+      </c>
       <c r="M85" t="n">
-        <v>0.015163699</v>
+        <v>0.468505884</v>
       </c>
       <c r="N85" t="n">
-        <v>0.468505884</v>
+        <v>2.74851515151515</v>
       </c>
       <c r="O85" t="n">
-        <v>2.74851515151515</v>
+        <v>-32.67466002120891</v>
       </c>
       <c r="P85" t="n">
-        <v>-32.67466002120891</v>
-      </c>
-      <c r="Q85" t="n">
         <v>8689</v>
       </c>
-      <c r="R85" t="inlineStr">
+      <c r="Q85" t="inlineStr">
         <is>
           <t>Myristicaceae</t>
         </is>
       </c>
-      <c r="S85" t="n">
+      <c r="R85" t="n">
         <v>3213</v>
       </c>
+      <c r="S85" t="inlineStr">
+        <is>
+          <t>Virola</t>
+        </is>
+      </c>
       <c r="T85" t="inlineStr">
-        <is>
-          <t>Virola</t>
-        </is>
-      </c>
-      <c r="U85" t="inlineStr">
         <is>
           <t>dixonii</t>
         </is>
@@ -5868,24 +5691,23 @@
       <c r="M86" t="inlineStr"/>
       <c r="N86" t="inlineStr"/>
       <c r="O86" t="inlineStr"/>
-      <c r="P86" t="inlineStr"/>
-      <c r="Q86" t="n">
+      <c r="P86" t="n">
         <v>8689</v>
       </c>
-      <c r="R86" t="inlineStr">
+      <c r="Q86" t="inlineStr">
         <is>
           <t>Myristicaceae</t>
         </is>
       </c>
-      <c r="S86" t="n">
+      <c r="R86" t="n">
         <v>3213</v>
       </c>
+      <c r="S86" t="inlineStr">
+        <is>
+          <t>Virola</t>
+        </is>
+      </c>
       <c r="T86" t="inlineStr">
-        <is>
-          <t>Virola</t>
-        </is>
-      </c>
-      <c r="U86" t="inlineStr">
         <is>
           <t>dixonii</t>
         </is>
@@ -5922,41 +5744,40 @@
       <c r="J87" t="n">
         <v>2309</v>
       </c>
-      <c r="K87" t="inlineStr"/>
-      <c r="L87" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>p72-8690</t>
         </is>
       </c>
+      <c r="L87" t="n">
+        <v>0.039906421</v>
+      </c>
       <c r="M87" t="n">
-        <v>0.039906421</v>
+        <v>0.432175376</v>
       </c>
       <c r="N87" t="n">
-        <v>0.432175376</v>
+        <v>2.370497474747473</v>
       </c>
       <c r="O87" t="n">
-        <v>2.370497474747473</v>
+        <v>-29.56024899257688</v>
       </c>
       <c r="P87" t="n">
-        <v>-29.56024899257688</v>
-      </c>
-      <c r="Q87" t="n">
         <v>8690</v>
       </c>
-      <c r="R87" t="inlineStr">
+      <c r="Q87" t="inlineStr">
         <is>
           <t>Myrtaceae</t>
         </is>
       </c>
-      <c r="S87" t="n">
+      <c r="R87" t="n">
         <v>3209</v>
       </c>
-      <c r="T87" t="inlineStr">
+      <c r="S87" t="inlineStr">
         <is>
           <t>Eugenia</t>
         </is>
       </c>
-      <c r="U87" t="inlineStr"/>
+      <c r="T87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" s="1" t="n">
@@ -5996,24 +5817,23 @@
       <c r="M88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="O88" t="inlineStr"/>
-      <c r="P88" t="inlineStr"/>
-      <c r="Q88" t="n">
+      <c r="P88" t="n">
         <v>8693</v>
       </c>
-      <c r="R88" t="inlineStr">
+      <c r="Q88" t="inlineStr">
         <is>
           <t>Fabaceae</t>
         </is>
       </c>
-      <c r="S88" t="n">
+      <c r="R88" t="n">
         <v>3198</v>
       </c>
+      <c r="S88" t="inlineStr">
+        <is>
+          <t>Inga</t>
+        </is>
+      </c>
       <c r="T88" t="inlineStr">
-        <is>
-          <t>Inga</t>
-        </is>
-      </c>
-      <c r="U88" t="inlineStr">
         <is>
           <t>multinervis</t>
         </is>
@@ -6061,24 +5881,23 @@
       <c r="M89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="O89" t="inlineStr"/>
-      <c r="P89" t="inlineStr"/>
-      <c r="Q89" t="n">
+      <c r="P89" t="n">
         <v>8693</v>
       </c>
-      <c r="R89" t="inlineStr">
+      <c r="Q89" t="inlineStr">
         <is>
           <t>Fabaceae</t>
         </is>
       </c>
-      <c r="S89" t="n">
+      <c r="R89" t="n">
         <v>3198</v>
       </c>
+      <c r="S89" t="inlineStr">
+        <is>
+          <t>Inga</t>
+        </is>
+      </c>
       <c r="T89" t="inlineStr">
-        <is>
-          <t>Inga</t>
-        </is>
-      </c>
-      <c r="U89" t="inlineStr">
         <is>
           <t>multinervis</t>
         </is>
@@ -6126,24 +5945,23 @@
       <c r="M90" t="inlineStr"/>
       <c r="N90" t="inlineStr"/>
       <c r="O90" t="inlineStr"/>
-      <c r="P90" t="inlineStr"/>
-      <c r="Q90" t="n">
+      <c r="P90" t="n">
         <v>8695</v>
       </c>
-      <c r="R90" t="inlineStr">
+      <c r="Q90" t="inlineStr">
         <is>
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="S90" t="n">
+      <c r="R90" t="n">
         <v>3214</v>
       </c>
+      <c r="S90" t="inlineStr">
+        <is>
+          <t>Pentagonia</t>
+        </is>
+      </c>
       <c r="T90" t="inlineStr">
-        <is>
-          <t>Pentagonia</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
         <is>
           <t>amazonica</t>
         </is>
@@ -6186,33 +6004,28 @@
       <c r="J91" t="n">
         <v>2303</v>
       </c>
-      <c r="K91" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K91" t="inlineStr"/>
       <c r="L91" t="inlineStr"/>
       <c r="M91" t="inlineStr"/>
       <c r="N91" t="inlineStr"/>
       <c r="O91" t="inlineStr"/>
-      <c r="P91" t="inlineStr"/>
-      <c r="Q91" t="n">
+      <c r="P91" t="n">
         <v>8695</v>
       </c>
-      <c r="R91" t="inlineStr">
+      <c r="Q91" t="inlineStr">
         <is>
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="S91" t="n">
+      <c r="R91" t="n">
         <v>3214</v>
       </c>
+      <c r="S91" t="inlineStr">
+        <is>
+          <t>Pentagonia</t>
+        </is>
+      </c>
       <c r="T91" t="inlineStr">
-        <is>
-          <t>Pentagonia</t>
-        </is>
-      </c>
-      <c r="U91" t="inlineStr">
         <is>
           <t>amazonica</t>
         </is>
@@ -6249,41 +6062,40 @@
       <c r="J92" t="n">
         <v>2303</v>
       </c>
-      <c r="K92" t="inlineStr"/>
-      <c r="L92" t="inlineStr">
+      <c r="K92" t="inlineStr">
         <is>
           <t>p72-8695</t>
         </is>
       </c>
+      <c r="L92" t="n">
+        <v>0.019071872</v>
+      </c>
       <c r="M92" t="n">
-        <v>0.019071872</v>
+        <v>0.460067295</v>
       </c>
       <c r="N92" t="n">
-        <v>0.460067295</v>
+        <v>2.867320707070705</v>
       </c>
       <c r="O92" t="n">
-        <v>2.867320707070705</v>
+        <v>-33.52029480381761</v>
       </c>
       <c r="P92" t="n">
-        <v>-33.52029480381761</v>
-      </c>
-      <c r="Q92" t="n">
         <v>8695</v>
       </c>
-      <c r="R92" t="inlineStr">
+      <c r="Q92" t="inlineStr">
         <is>
           <t>Rubiaceae</t>
         </is>
       </c>
-      <c r="S92" t="n">
+      <c r="R92" t="n">
         <v>3214</v>
       </c>
+      <c r="S92" t="inlineStr">
+        <is>
+          <t>Pentagonia</t>
+        </is>
+      </c>
       <c r="T92" t="inlineStr">
-        <is>
-          <t>Pentagonia</t>
-        </is>
-      </c>
-      <c r="U92" t="inlineStr">
         <is>
           <t>amazonica</t>
         </is>
@@ -6331,24 +6143,23 @@
       <c r="M93" t="inlineStr"/>
       <c r="N93" t="inlineStr"/>
       <c r="O93" t="inlineStr"/>
-      <c r="P93" t="inlineStr"/>
-      <c r="Q93" t="n">
+      <c r="P93" t="n">
         <v>8697</v>
       </c>
-      <c r="R93" t="inlineStr">
+      <c r="Q93" t="inlineStr">
         <is>
           <t>Myristicaceae</t>
         </is>
       </c>
-      <c r="S93" t="n">
+      <c r="R93" t="n">
         <v>3200</v>
       </c>
+      <c r="S93" t="inlineStr">
+        <is>
+          <t>Otoba</t>
+        </is>
+      </c>
       <c r="T93" t="inlineStr">
-        <is>
-          <t>Otoba</t>
-        </is>
-      </c>
-      <c r="U93" t="inlineStr">
         <is>
           <t>parvifolia</t>
         </is>
@@ -6385,41 +6196,40 @@
       <c r="J94" t="n">
         <v>2315</v>
       </c>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr">
+      <c r="K94" t="inlineStr">
         <is>
           <t>p72-8697</t>
         </is>
       </c>
+      <c r="L94" t="n">
+        <v>0.01496271</v>
+      </c>
       <c r="M94" t="n">
-        <v>0.01496271</v>
+        <v>0.480305405</v>
       </c>
       <c r="N94" t="n">
-        <v>0.480305405</v>
+        <v>1.290446969696968</v>
       </c>
       <c r="O94" t="n">
-        <v>1.290446969696968</v>
+        <v>-30.84932640509014</v>
       </c>
       <c r="P94" t="n">
-        <v>-30.84932640509014</v>
-      </c>
-      <c r="Q94" t="n">
         <v>8697</v>
       </c>
-      <c r="R94" t="inlineStr">
+      <c r="Q94" t="inlineStr">
         <is>
           <t>Myristicaceae</t>
         </is>
       </c>
-      <c r="S94" t="n">
+      <c r="R94" t="n">
         <v>3200</v>
       </c>
+      <c r="S94" t="inlineStr">
+        <is>
+          <t>Otoba</t>
+        </is>
+      </c>
       <c r="T94" t="inlineStr">
-        <is>
-          <t>Otoba</t>
-        </is>
-      </c>
-      <c r="U94" t="inlineStr">
         <is>
           <t>parvifolia</t>
         </is>
@@ -6460,31 +6270,26 @@
         </is>
       </c>
       <c r="J95" t="inlineStr"/>
-      <c r="K95" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
       <c r="M95" t="inlineStr"/>
       <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
-      <c r="P95" t="inlineStr"/>
-      <c r="Q95" t="n">
+      <c r="P95" t="n">
         <v>8698</v>
       </c>
-      <c r="R95" t="inlineStr">
+      <c r="Q95" t="inlineStr">
         <is>
           <t xml:space="preserve"> Chrysobalanaceae</t>
         </is>
       </c>
-      <c r="S95" t="inlineStr"/>
-      <c r="T95" t="inlineStr">
+      <c r="R95" t="inlineStr"/>
+      <c r="S95" t="inlineStr">
         <is>
           <t>Hirtella</t>
         </is>
       </c>
-      <c r="U95" t="inlineStr"/>
+      <c r="T95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" s="1" t="n">
@@ -6526,22 +6331,21 @@
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="O96" t="inlineStr"/>
-      <c r="P96" t="inlineStr"/>
-      <c r="Q96" t="n">
+      <c r="P96" t="n">
         <v>8698</v>
       </c>
-      <c r="R96" t="inlineStr">
+      <c r="Q96" t="inlineStr">
         <is>
           <t xml:space="preserve"> Chrysobalanaceae</t>
         </is>
       </c>
-      <c r="S96" t="inlineStr"/>
-      <c r="T96" t="inlineStr">
+      <c r="R96" t="inlineStr"/>
+      <c r="S96" t="inlineStr">
         <is>
           <t>Hirtella</t>
         </is>
       </c>
-      <c r="U96" t="inlineStr"/>
+      <c r="T96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" s="1" t="n">
@@ -6585,24 +6389,23 @@
       <c r="M97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="O97" t="inlineStr"/>
-      <c r="P97" t="inlineStr"/>
-      <c r="Q97" t="n">
+      <c r="P97" t="n">
         <v>8699</v>
       </c>
-      <c r="R97" t="inlineStr">
+      <c r="Q97" t="inlineStr">
         <is>
           <t>Rutaceae</t>
         </is>
       </c>
-      <c r="S97" t="n">
+      <c r="R97" t="n">
         <v>3197</v>
       </c>
+      <c r="S97" t="inlineStr">
+        <is>
+          <t>Amyris</t>
+        </is>
+      </c>
       <c r="T97" t="inlineStr">
-        <is>
-          <t>Amyris</t>
-        </is>
-      </c>
-      <c r="U97" t="inlineStr">
         <is>
           <t>macrocarpa</t>
         </is>
@@ -6639,41 +6442,40 @@
       <c r="J98" t="n">
         <v>2319</v>
       </c>
-      <c r="K98" t="inlineStr"/>
-      <c r="L98" t="inlineStr">
+      <c r="K98" t="inlineStr">
         <is>
           <t>p72-8699</t>
         </is>
       </c>
+      <c r="L98" t="n">
+        <v>0.019942396</v>
+      </c>
       <c r="M98" t="n">
-        <v>0.019942396</v>
+        <v>0.460964682</v>
       </c>
       <c r="N98" t="n">
-        <v>0.460964682</v>
+        <v>1.160840909090907</v>
       </c>
       <c r="O98" t="n">
-        <v>1.160840909090907</v>
+        <v>-34.56186935312832</v>
       </c>
       <c r="P98" t="n">
-        <v>-34.56186935312832</v>
-      </c>
-      <c r="Q98" t="n">
         <v>8699</v>
       </c>
-      <c r="R98" t="inlineStr">
+      <c r="Q98" t="inlineStr">
         <is>
           <t>Rutaceae</t>
         </is>
       </c>
-      <c r="S98" t="n">
+      <c r="R98" t="n">
         <v>3197</v>
       </c>
+      <c r="S98" t="inlineStr">
+        <is>
+          <t>Amyris</t>
+        </is>
+      </c>
       <c r="T98" t="inlineStr">
-        <is>
-          <t>Amyris</t>
-        </is>
-      </c>
-      <c r="U98" t="inlineStr">
         <is>
           <t>macrocarpa</t>
         </is>
@@ -6719,22 +6521,21 @@
       <c r="M99" t="inlineStr"/>
       <c r="N99" t="inlineStr"/>
       <c r="O99" t="inlineStr"/>
-      <c r="P99" t="inlineStr"/>
-      <c r="Q99" t="n">
+      <c r="P99" t="n">
         <v>8802</v>
       </c>
-      <c r="R99" t="inlineStr">
+      <c r="Q99" t="inlineStr">
         <is>
           <t>Lauraceae</t>
         </is>
       </c>
-      <c r="S99" t="inlineStr"/>
+      <c r="R99" t="inlineStr"/>
+      <c r="S99" t="inlineStr">
+        <is>
+          <t>Ocotea</t>
+        </is>
+      </c>
       <c r="T99" t="inlineStr">
-        <is>
-          <t>Ocotea</t>
-        </is>
-      </c>
-      <c r="U99" t="inlineStr">
         <is>
           <t>oblonga</t>
         </is>
@@ -6775,31 +6576,26 @@
         </is>
       </c>
       <c r="J100" t="inlineStr"/>
-      <c r="K100" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K100" t="inlineStr"/>
       <c r="L100" t="inlineStr"/>
       <c r="M100" t="inlineStr"/>
       <c r="N100" t="inlineStr"/>
       <c r="O100" t="inlineStr"/>
-      <c r="P100" t="inlineStr"/>
-      <c r="Q100" t="n">
+      <c r="P100" t="n">
         <v>8802</v>
       </c>
-      <c r="R100" t="inlineStr">
+      <c r="Q100" t="inlineStr">
         <is>
           <t>Lauraceae</t>
         </is>
       </c>
-      <c r="S100" t="inlineStr"/>
+      <c r="R100" t="inlineStr"/>
+      <c r="S100" t="inlineStr">
+        <is>
+          <t>Ocotea</t>
+        </is>
+      </c>
       <c r="T100" t="inlineStr">
-        <is>
-          <t>Ocotea</t>
-        </is>
-      </c>
-      <c r="U100" t="inlineStr">
         <is>
           <t>oblonga</t>
         </is>
@@ -6836,41 +6632,40 @@
       <c r="J101" t="n">
         <v>2288</v>
       </c>
-      <c r="K101" t="inlineStr"/>
-      <c r="L101" t="inlineStr">
+      <c r="K101" t="inlineStr">
         <is>
           <t>p72-8803</t>
         </is>
       </c>
+      <c r="L101" t="n">
+        <v>0.013534934</v>
+      </c>
       <c r="M101" t="n">
-        <v>0.013534934</v>
+        <v>0.4586319</v>
       </c>
       <c r="N101" t="n">
-        <v>0.4586319</v>
+        <v>2.284093434343433</v>
       </c>
       <c r="O101" t="n">
-        <v>2.284093434343433</v>
+        <v>-32.93247550371157</v>
       </c>
       <c r="P101" t="n">
-        <v>-32.93247550371157</v>
-      </c>
-      <c r="Q101" t="n">
         <v>8803</v>
       </c>
-      <c r="R101" t="inlineStr">
+      <c r="Q101" t="inlineStr">
         <is>
           <t>Lecythidaceae</t>
         </is>
       </c>
-      <c r="S101" t="n">
+      <c r="R101" t="n">
         <v>3196</v>
       </c>
-      <c r="T101" t="inlineStr">
+      <c r="S101" t="inlineStr">
         <is>
           <t>Eschweilera</t>
         </is>
       </c>
-      <c r="U101" t="inlineStr"/>
+      <c r="T101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" s="1" t="n">
@@ -6914,24 +6709,23 @@
       <c r="M102" t="inlineStr"/>
       <c r="N102" t="inlineStr"/>
       <c r="O102" t="inlineStr"/>
-      <c r="P102" t="inlineStr"/>
-      <c r="Q102" t="n">
+      <c r="P102" t="n">
         <v>8803</v>
       </c>
-      <c r="R102" t="inlineStr">
+      <c r="Q102" t="inlineStr">
         <is>
           <t>Lecythidaceae</t>
         </is>
       </c>
-      <c r="S102" t="n">
+      <c r="R102" t="n">
         <v>3196</v>
       </c>
-      <c r="T102" t="inlineStr">
+      <c r="S102" t="inlineStr">
         <is>
           <t>Eschweilera</t>
         </is>
       </c>
-      <c r="U102" t="inlineStr"/>
+      <c r="T102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" s="1" t="n">
@@ -6964,41 +6758,40 @@
       <c r="J103" t="n">
         <v>2289</v>
       </c>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr">
+      <c r="K103" t="inlineStr">
         <is>
           <t>p72-8804</t>
         </is>
       </c>
+      <c r="L103" t="n">
+        <v>0.016758675</v>
+      </c>
       <c r="M103" t="n">
-        <v>0.016758675</v>
+        <v>0.473760231</v>
       </c>
       <c r="N103" t="n">
-        <v>0.473760231</v>
+        <v>1.76566919191919</v>
       </c>
       <c r="O103" t="n">
-        <v>1.76566919191919</v>
+        <v>-34.8712479321315</v>
       </c>
       <c r="P103" t="n">
-        <v>-34.8712479321315</v>
-      </c>
-      <c r="Q103" t="n">
         <v>8804</v>
       </c>
-      <c r="R103" t="inlineStr">
+      <c r="Q103" t="inlineStr">
         <is>
           <t>Sapotaceae</t>
         </is>
       </c>
-      <c r="S103" t="n">
+      <c r="R103" t="n">
         <v>3206</v>
       </c>
+      <c r="S103" t="inlineStr">
+        <is>
+          <t>Pouteria</t>
+        </is>
+      </c>
       <c r="T103" t="inlineStr">
-        <is>
-          <t>Pouteria</t>
-        </is>
-      </c>
-      <c r="U103" t="inlineStr">
         <is>
           <t>guianensis</t>
         </is>
@@ -7046,24 +6839,23 @@
       <c r="M104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="O104" t="inlineStr"/>
-      <c r="P104" t="inlineStr"/>
-      <c r="Q104" t="n">
+      <c r="P104" t="n">
         <v>8804</v>
       </c>
-      <c r="R104" t="inlineStr">
+      <c r="Q104" t="inlineStr">
         <is>
           <t>Sapotaceae</t>
         </is>
       </c>
-      <c r="S104" t="n">
+      <c r="R104" t="n">
         <v>3206</v>
       </c>
+      <c r="S104" t="inlineStr">
+        <is>
+          <t>Pouteria</t>
+        </is>
+      </c>
       <c r="T104" t="inlineStr">
-        <is>
-          <t>Pouteria</t>
-        </is>
-      </c>
-      <c r="U104" t="inlineStr">
         <is>
           <t>guianensis</t>
         </is>
@@ -7111,24 +6903,23 @@
       <c r="M105" t="inlineStr"/>
       <c r="N105" t="inlineStr"/>
       <c r="O105" t="inlineStr"/>
-      <c r="P105" t="inlineStr"/>
-      <c r="Q105" t="n">
+      <c r="P105" t="n">
         <v>8807</v>
       </c>
-      <c r="R105" t="inlineStr">
+      <c r="Q105" t="inlineStr">
         <is>
           <t>Fabaceae</t>
         </is>
       </c>
-      <c r="S105" t="n">
+      <c r="R105" t="n">
         <v>3199</v>
       </c>
+      <c r="S105" t="inlineStr">
+        <is>
+          <t>Browneopsis</t>
+        </is>
+      </c>
       <c r="T105" t="inlineStr">
-        <is>
-          <t>Browneopsis</t>
-        </is>
-      </c>
-      <c r="U105" t="inlineStr">
         <is>
           <t>ucayalina</t>
         </is>
@@ -7174,18 +6965,17 @@
       <c r="M106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="O106" t="inlineStr"/>
-      <c r="P106" t="inlineStr"/>
-      <c r="Q106" t="n">
+      <c r="P106" t="n">
         <v>8808</v>
       </c>
-      <c r="R106" t="inlineStr">
+      <c r="Q106" t="inlineStr">
         <is>
           <t>Melastomatacea</t>
         </is>
       </c>
+      <c r="R106" t="inlineStr"/>
       <c r="S106" t="inlineStr"/>
       <c r="T106" t="inlineStr"/>
-      <c r="U106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" s="1" t="n">
@@ -7222,27 +7012,22 @@
         </is>
       </c>
       <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
       <c r="M107" t="inlineStr"/>
       <c r="N107" t="inlineStr"/>
       <c r="O107" t="inlineStr"/>
-      <c r="P107" t="inlineStr"/>
-      <c r="Q107" t="n">
+      <c r="P107" t="n">
         <v>8808</v>
       </c>
-      <c r="R107" t="inlineStr">
+      <c r="Q107" t="inlineStr">
         <is>
           <t>Melastomatacea</t>
         </is>
       </c>
+      <c r="R107" t="inlineStr"/>
       <c r="S107" t="inlineStr"/>
       <c r="T107" t="inlineStr"/>
-      <c r="U107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" s="1" t="n">
@@ -7284,22 +7069,21 @@
       <c r="M108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="O108" t="inlineStr"/>
-      <c r="P108" t="inlineStr"/>
-      <c r="Q108" t="n">
+      <c r="P108" t="n">
         <v>8810</v>
       </c>
-      <c r="R108" t="inlineStr">
+      <c r="Q108" t="inlineStr">
         <is>
           <t>Euphorbiaceae</t>
         </is>
       </c>
-      <c r="S108" t="inlineStr"/>
+      <c r="R108" t="inlineStr"/>
+      <c r="S108" t="inlineStr">
+        <is>
+          <t>Pseudosenefeldera</t>
+        </is>
+      </c>
       <c r="T108" t="inlineStr">
-        <is>
-          <t>Pseudosenefeldera</t>
-        </is>
-      </c>
-      <c r="U108" t="inlineStr">
         <is>
           <t>inclinata</t>
         </is>
@@ -7340,31 +7124,26 @@
         </is>
       </c>
       <c r="J109" t="inlineStr"/>
-      <c r="K109" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
       <c r="M109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="O109" t="inlineStr"/>
-      <c r="P109" t="inlineStr"/>
-      <c r="Q109" t="n">
+      <c r="P109" t="n">
         <v>8810</v>
       </c>
-      <c r="R109" t="inlineStr">
+      <c r="Q109" t="inlineStr">
         <is>
           <t>Euphorbiaceae</t>
         </is>
       </c>
-      <c r="S109" t="inlineStr"/>
+      <c r="R109" t="inlineStr"/>
+      <c r="S109" t="inlineStr">
+        <is>
+          <t>Pseudosenefeldera</t>
+        </is>
+      </c>
       <c r="T109" t="inlineStr">
-        <is>
-          <t>Pseudosenefeldera</t>
-        </is>
-      </c>
-      <c r="U109" t="inlineStr">
         <is>
           <t>inclinata</t>
         </is>
@@ -7412,24 +7191,23 @@
       <c r="M110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="O110" t="inlineStr"/>
-      <c r="P110" t="inlineStr"/>
-      <c r="Q110" t="n">
+      <c r="P110" t="n">
         <v>8811</v>
       </c>
-      <c r="R110" t="inlineStr">
+      <c r="Q110" t="inlineStr">
         <is>
           <t>Moraceae</t>
         </is>
       </c>
-      <c r="S110" t="n">
+      <c r="R110" t="n">
         <v>3195</v>
       </c>
+      <c r="S110" t="inlineStr">
+        <is>
+          <t>Sorocea</t>
+        </is>
+      </c>
       <c r="T110" t="inlineStr">
-        <is>
-          <t>Sorocea</t>
-        </is>
-      </c>
-      <c r="U110" t="inlineStr">
         <is>
           <t>steinbachii</t>
         </is>
@@ -7466,41 +7244,40 @@
       <c r="J111" t="n">
         <v>2292</v>
       </c>
-      <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr">
+      <c r="K111" t="inlineStr">
         <is>
           <t>p72-8811</t>
         </is>
       </c>
+      <c r="L111" t="n">
+        <v>0.021918119</v>
+      </c>
       <c r="M111" t="n">
-        <v>0.021918119</v>
+        <v>0.409271254</v>
       </c>
       <c r="N111" t="n">
-        <v>0.409271254</v>
+        <v>1.970878787878786</v>
       </c>
       <c r="O111" t="n">
-        <v>1.970878787878786</v>
+        <v>-33.44810646871687</v>
       </c>
       <c r="P111" t="n">
-        <v>-33.44810646871687</v>
-      </c>
-      <c r="Q111" t="n">
         <v>8811</v>
       </c>
-      <c r="R111" t="inlineStr">
+      <c r="Q111" t="inlineStr">
         <is>
           <t>Moraceae</t>
         </is>
       </c>
-      <c r="S111" t="n">
+      <c r="R111" t="n">
         <v>3195</v>
       </c>
+      <c r="S111" t="inlineStr">
+        <is>
+          <t>Sorocea</t>
+        </is>
+      </c>
       <c r="T111" t="inlineStr">
-        <is>
-          <t>Sorocea</t>
-        </is>
-      </c>
-      <c r="U111" t="inlineStr">
         <is>
           <t>steinbachii</t>
         </is>
@@ -7546,22 +7323,21 @@
       <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="O112" t="inlineStr"/>
-      <c r="P112" t="inlineStr"/>
-      <c r="Q112" t="n">
+      <c r="P112" t="n">
         <v>8812</v>
       </c>
-      <c r="R112" t="inlineStr">
+      <c r="Q112" t="inlineStr">
         <is>
           <t>Sapotaceae</t>
         </is>
       </c>
-      <c r="S112" t="inlineStr"/>
-      <c r="T112" t="inlineStr">
+      <c r="R112" t="inlineStr"/>
+      <c r="S112" t="inlineStr">
         <is>
           <t>Pouteria</t>
         </is>
       </c>
-      <c r="U112" t="inlineStr"/>
+      <c r="T112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" s="1" t="n">
@@ -7598,31 +7374,26 @@
         </is>
       </c>
       <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K113" t="inlineStr"/>
       <c r="L113" t="inlineStr"/>
       <c r="M113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="O113" t="inlineStr"/>
-      <c r="P113" t="inlineStr"/>
-      <c r="Q113" t="n">
+      <c r="P113" t="n">
         <v>8812</v>
       </c>
-      <c r="R113" t="inlineStr">
+      <c r="Q113" t="inlineStr">
         <is>
           <t>Sapotaceae</t>
         </is>
       </c>
-      <c r="S113" t="inlineStr"/>
-      <c r="T113" t="inlineStr">
+      <c r="R113" t="inlineStr"/>
+      <c r="S113" t="inlineStr">
         <is>
           <t>Pouteria</t>
         </is>
       </c>
-      <c r="U113" t="inlineStr"/>
+      <c r="T113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" s="1" t="n">
@@ -7664,22 +7435,21 @@
       <c r="M114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="O114" t="inlineStr"/>
-      <c r="P114" t="inlineStr"/>
-      <c r="Q114" t="n">
+      <c r="P114" t="n">
         <v>8813</v>
       </c>
-      <c r="R114" t="inlineStr">
+      <c r="Q114" t="inlineStr">
         <is>
           <t>Euphorbiaceae</t>
         </is>
       </c>
-      <c r="S114" t="inlineStr"/>
+      <c r="R114" t="inlineStr"/>
+      <c r="S114" t="inlineStr">
+        <is>
+          <t>Pseudosenefeldera</t>
+        </is>
+      </c>
       <c r="T114" t="inlineStr">
-        <is>
-          <t>Pseudosenefeldera</t>
-        </is>
-      </c>
-      <c r="U114" t="inlineStr">
         <is>
           <t>inclinata</t>
         </is>
@@ -7720,31 +7490,26 @@
         </is>
       </c>
       <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
       <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
-      <c r="P115" t="inlineStr"/>
-      <c r="Q115" t="n">
+      <c r="P115" t="n">
         <v>8813</v>
       </c>
-      <c r="R115" t="inlineStr">
+      <c r="Q115" t="inlineStr">
         <is>
           <t>Euphorbiaceae</t>
         </is>
       </c>
-      <c r="S115" t="inlineStr"/>
+      <c r="R115" t="inlineStr"/>
+      <c r="S115" t="inlineStr">
+        <is>
+          <t>Pseudosenefeldera</t>
+        </is>
+      </c>
       <c r="T115" t="inlineStr">
-        <is>
-          <t>Pseudosenefeldera</t>
-        </is>
-      </c>
-      <c r="U115" t="inlineStr">
         <is>
           <t>inclinata</t>
         </is>
@@ -7790,22 +7555,21 @@
       <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="O116" t="inlineStr"/>
-      <c r="P116" t="inlineStr"/>
-      <c r="Q116" t="n">
+      <c r="P116" t="n">
         <v>8814</v>
       </c>
-      <c r="R116" t="inlineStr">
+      <c r="Q116" t="inlineStr">
         <is>
           <t>Moraceae</t>
         </is>
       </c>
-      <c r="S116" t="inlineStr"/>
-      <c r="T116" t="inlineStr">
+      <c r="R116" t="inlineStr"/>
+      <c r="S116" t="inlineStr">
         <is>
           <t>Brosimum</t>
         </is>
       </c>
-      <c r="U116" t="inlineStr"/>
+      <c r="T116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" s="1" t="n">
@@ -7842,31 +7606,26 @@
         </is>
       </c>
       <c r="J117" t="inlineStr"/>
-      <c r="K117" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
       <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="O117" t="inlineStr"/>
-      <c r="P117" t="inlineStr"/>
-      <c r="Q117" t="n">
+      <c r="P117" t="n">
         <v>8814</v>
       </c>
-      <c r="R117" t="inlineStr">
+      <c r="Q117" t="inlineStr">
         <is>
           <t>Moraceae</t>
         </is>
       </c>
-      <c r="S117" t="inlineStr"/>
-      <c r="T117" t="inlineStr">
+      <c r="R117" t="inlineStr"/>
+      <c r="S117" t="inlineStr">
         <is>
           <t>Brosimum</t>
         </is>
       </c>
-      <c r="U117" t="inlineStr"/>
+      <c r="T117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" s="1" t="n">
@@ -7903,27 +7662,22 @@
         </is>
       </c>
       <c r="J118" t="inlineStr"/>
-      <c r="K118" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K118" t="inlineStr"/>
       <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="O118" t="inlineStr"/>
-      <c r="P118" t="inlineStr"/>
-      <c r="Q118" t="n">
+      <c r="P118" t="n">
         <v>8816</v>
       </c>
-      <c r="R118" t="inlineStr">
+      <c r="Q118" t="inlineStr">
         <is>
           <t>indet</t>
         </is>
       </c>
+      <c r="R118" t="inlineStr"/>
       <c r="S118" t="inlineStr"/>
       <c r="T118" t="inlineStr"/>
-      <c r="U118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" s="1" t="n">
@@ -7965,18 +7719,17 @@
       <c r="M119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
-      <c r="P119" t="inlineStr"/>
-      <c r="Q119" t="n">
+      <c r="P119" t="n">
         <v>8816</v>
       </c>
-      <c r="R119" t="inlineStr">
+      <c r="Q119" t="inlineStr">
         <is>
           <t>indet</t>
         </is>
       </c>
+      <c r="R119" t="inlineStr"/>
       <c r="S119" t="inlineStr"/>
       <c r="T119" t="inlineStr"/>
-      <c r="U119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" s="1" t="n">
@@ -8013,31 +7766,26 @@
         </is>
       </c>
       <c r="J120" t="inlineStr"/>
-      <c r="K120" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="O120" t="inlineStr"/>
-      <c r="P120" t="inlineStr"/>
-      <c r="Q120" t="n">
+      <c r="P120" t="n">
         <v>8819</v>
       </c>
-      <c r="R120" t="inlineStr">
+      <c r="Q120" t="inlineStr">
         <is>
           <t>Meliaceae</t>
         </is>
       </c>
-      <c r="S120" t="inlineStr"/>
-      <c r="T120" t="inlineStr">
+      <c r="R120" t="inlineStr"/>
+      <c r="S120" t="inlineStr">
         <is>
           <t>Guarea</t>
         </is>
       </c>
-      <c r="U120" t="inlineStr"/>
+      <c r="T120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" s="1" t="n">
@@ -8079,22 +7827,21 @@
       <c r="M121" t="inlineStr"/>
       <c r="N121" t="inlineStr"/>
       <c r="O121" t="inlineStr"/>
-      <c r="P121" t="inlineStr"/>
-      <c r="Q121" t="n">
+      <c r="P121" t="n">
         <v>8819</v>
       </c>
-      <c r="R121" t="inlineStr">
+      <c r="Q121" t="inlineStr">
         <is>
           <t>Meliaceae</t>
         </is>
       </c>
-      <c r="S121" t="inlineStr"/>
-      <c r="T121" t="inlineStr">
+      <c r="R121" t="inlineStr"/>
+      <c r="S121" t="inlineStr">
         <is>
           <t>Guarea</t>
         </is>
       </c>
-      <c r="U121" t="inlineStr"/>
+      <c r="T121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" s="1" t="n">
@@ -8131,27 +7878,22 @@
         </is>
       </c>
       <c r="J122" t="inlineStr"/>
-      <c r="K122" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr"/>
       <c r="N122" t="inlineStr"/>
       <c r="O122" t="inlineStr"/>
-      <c r="P122" t="inlineStr"/>
-      <c r="Q122" t="n">
+      <c r="P122" t="n">
         <v>8820</v>
       </c>
-      <c r="R122" t="inlineStr">
+      <c r="Q122" t="inlineStr">
         <is>
           <t>Clusiaceae</t>
         </is>
       </c>
+      <c r="R122" t="inlineStr"/>
       <c r="S122" t="inlineStr"/>
       <c r="T122" t="inlineStr"/>
-      <c r="U122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" s="1" t="n">
@@ -8193,18 +7935,17 @@
       <c r="M123" t="inlineStr"/>
       <c r="N123" t="inlineStr"/>
       <c r="O123" t="inlineStr"/>
-      <c r="P123" t="inlineStr"/>
-      <c r="Q123" t="n">
+      <c r="P123" t="n">
         <v>8820</v>
       </c>
-      <c r="R123" t="inlineStr">
+      <c r="Q123" t="inlineStr">
         <is>
           <t>Clusiaceae</t>
         </is>
       </c>
+      <c r="R123" t="inlineStr"/>
       <c r="S123" t="inlineStr"/>
       <c r="T123" t="inlineStr"/>
-      <c r="U123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" s="1" t="n">
@@ -8246,22 +7987,21 @@
       <c r="M124" t="inlineStr"/>
       <c r="N124" t="inlineStr"/>
       <c r="O124" t="inlineStr"/>
-      <c r="P124" t="inlineStr"/>
-      <c r="Q124" t="n">
+      <c r="P124" t="n">
         <v>8821</v>
       </c>
-      <c r="R124" t="inlineStr">
+      <c r="Q124" t="inlineStr">
         <is>
           <t>Myristicaceae</t>
         </is>
       </c>
-      <c r="S124" t="inlineStr"/>
-      <c r="T124" t="inlineStr">
+      <c r="R124" t="inlineStr"/>
+      <c r="S124" t="inlineStr">
         <is>
           <t>Compsoneura</t>
         </is>
       </c>
-      <c r="U124" t="inlineStr"/>
+      <c r="T124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" s="1" t="n">
@@ -8298,31 +8038,26 @@
         </is>
       </c>
       <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr"/>
       <c r="N125" t="inlineStr"/>
       <c r="O125" t="inlineStr"/>
-      <c r="P125" t="inlineStr"/>
-      <c r="Q125" t="n">
+      <c r="P125" t="n">
         <v>8821</v>
       </c>
-      <c r="R125" t="inlineStr">
+      <c r="Q125" t="inlineStr">
         <is>
           <t>Myristicaceae</t>
         </is>
       </c>
-      <c r="S125" t="inlineStr"/>
-      <c r="T125" t="inlineStr">
+      <c r="R125" t="inlineStr"/>
+      <c r="S125" t="inlineStr">
         <is>
           <t>Compsoneura</t>
         </is>
       </c>
-      <c r="U125" t="inlineStr"/>
+      <c r="T125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" s="1" t="n">
@@ -8364,18 +8099,17 @@
       <c r="M126" t="inlineStr"/>
       <c r="N126" t="inlineStr"/>
       <c r="O126" t="inlineStr"/>
-      <c r="P126" t="inlineStr"/>
-      <c r="Q126" t="n">
+      <c r="P126" t="n">
         <v>8822</v>
       </c>
-      <c r="R126" t="inlineStr">
+      <c r="Q126" t="inlineStr">
         <is>
           <t>Lauraceae</t>
         </is>
       </c>
+      <c r="R126" t="inlineStr"/>
       <c r="S126" t="inlineStr"/>
       <c r="T126" t="inlineStr"/>
-      <c r="U126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" s="1" t="n">
@@ -8412,27 +8146,22 @@
         </is>
       </c>
       <c r="J127" t="inlineStr"/>
-      <c r="K127" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
       <c r="M127" t="inlineStr"/>
       <c r="N127" t="inlineStr"/>
       <c r="O127" t="inlineStr"/>
-      <c r="P127" t="inlineStr"/>
-      <c r="Q127" t="n">
+      <c r="P127" t="n">
         <v>8822</v>
       </c>
-      <c r="R127" t="inlineStr">
+      <c r="Q127" t="inlineStr">
         <is>
           <t>Lauraceae</t>
         </is>
       </c>
+      <c r="R127" t="inlineStr"/>
       <c r="S127" t="inlineStr"/>
       <c r="T127" t="inlineStr"/>
-      <c r="U127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" s="1" t="n">
@@ -8474,22 +8203,21 @@
       <c r="M128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="O128" t="inlineStr"/>
-      <c r="P128" t="inlineStr"/>
-      <c r="Q128" t="n">
+      <c r="P128" t="n">
         <v>8825</v>
       </c>
-      <c r="R128" t="inlineStr">
+      <c r="Q128" t="inlineStr">
         <is>
           <t>Sapotaceae</t>
         </is>
       </c>
-      <c r="S128" t="inlineStr"/>
+      <c r="R128" t="inlineStr"/>
+      <c r="S128" t="inlineStr">
+        <is>
+          <t>Pouteria</t>
+        </is>
+      </c>
       <c r="T128" t="inlineStr">
-        <is>
-          <t>Pouteria</t>
-        </is>
-      </c>
-      <c r="U128" t="inlineStr">
         <is>
           <t>sp.2</t>
         </is>
@@ -8530,31 +8258,26 @@
         </is>
       </c>
       <c r="J129" t="inlineStr"/>
-      <c r="K129" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="M129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="O129" t="inlineStr"/>
-      <c r="P129" t="inlineStr"/>
-      <c r="Q129" t="n">
+      <c r="P129" t="n">
         <v>8825</v>
       </c>
-      <c r="R129" t="inlineStr">
+      <c r="Q129" t="inlineStr">
         <is>
           <t>Sapotaceae</t>
         </is>
       </c>
-      <c r="S129" t="inlineStr"/>
+      <c r="R129" t="inlineStr"/>
+      <c r="S129" t="inlineStr">
+        <is>
+          <t>Pouteria</t>
+        </is>
+      </c>
       <c r="T129" t="inlineStr">
-        <is>
-          <t>Pouteria</t>
-        </is>
-      </c>
-      <c r="U129" t="inlineStr">
         <is>
           <t>sp.2</t>
         </is>
@@ -8600,22 +8323,21 @@
       <c r="M130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="O130" t="inlineStr"/>
-      <c r="P130" t="inlineStr"/>
-      <c r="Q130" t="n">
+      <c r="P130" t="n">
         <v>8827</v>
       </c>
-      <c r="R130" t="inlineStr">
+      <c r="Q130" t="inlineStr">
         <is>
           <t>Sapotaceae</t>
         </is>
       </c>
-      <c r="S130" t="inlineStr"/>
+      <c r="R130" t="inlineStr"/>
+      <c r="S130" t="inlineStr">
+        <is>
+          <t>Sarcaulus</t>
+        </is>
+      </c>
       <c r="T130" t="inlineStr">
-        <is>
-          <t>Sarcaulus</t>
-        </is>
-      </c>
-      <c r="U130" t="inlineStr">
         <is>
           <t>brasiliensis</t>
         </is>
@@ -8656,31 +8378,26 @@
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
-      <c r="K131" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
       <c r="O131" t="inlineStr"/>
-      <c r="P131" t="inlineStr"/>
-      <c r="Q131" t="n">
+      <c r="P131" t="n">
         <v>8827</v>
       </c>
-      <c r="R131" t="inlineStr">
+      <c r="Q131" t="inlineStr">
         <is>
           <t>Sapotaceae</t>
         </is>
       </c>
-      <c r="S131" t="inlineStr"/>
+      <c r="R131" t="inlineStr"/>
+      <c r="S131" t="inlineStr">
+        <is>
+          <t>Sarcaulus</t>
+        </is>
+      </c>
       <c r="T131" t="inlineStr">
-        <is>
-          <t>Sarcaulus</t>
-        </is>
-      </c>
-      <c r="U131" t="inlineStr">
         <is>
           <t>brasiliensis</t>
         </is>
@@ -8721,31 +8438,26 @@
         </is>
       </c>
       <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
       <c r="M132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
       <c r="O132" t="inlineStr"/>
-      <c r="P132" t="inlineStr"/>
-      <c r="Q132" t="n">
+      <c r="P132" t="n">
         <v>8828</v>
       </c>
-      <c r="R132" t="inlineStr">
+      <c r="Q132" t="inlineStr">
         <is>
           <t>Fabaceae</t>
         </is>
       </c>
-      <c r="S132" t="inlineStr"/>
+      <c r="R132" t="inlineStr"/>
+      <c r="S132" t="inlineStr">
+        <is>
+          <t>Macrolobium</t>
+        </is>
+      </c>
       <c r="T132" t="inlineStr">
-        <is>
-          <t>Macrolobium</t>
-        </is>
-      </c>
-      <c r="U132" t="inlineStr">
         <is>
           <t>cf. ischnocalyx</t>
         </is>
@@ -8791,22 +8503,21 @@
       <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
       <c r="O133" t="inlineStr"/>
-      <c r="P133" t="inlineStr"/>
-      <c r="Q133" t="n">
+      <c r="P133" t="n">
         <v>8828</v>
       </c>
-      <c r="R133" t="inlineStr">
+      <c r="Q133" t="inlineStr">
         <is>
           <t>Fabaceae</t>
         </is>
       </c>
-      <c r="S133" t="inlineStr"/>
+      <c r="R133" t="inlineStr"/>
+      <c r="S133" t="inlineStr">
+        <is>
+          <t>Macrolobium</t>
+        </is>
+      </c>
       <c r="T133" t="inlineStr">
-        <is>
-          <t>Macrolobium</t>
-        </is>
-      </c>
-      <c r="U133" t="inlineStr">
         <is>
           <t>cf. ischnocalyx</t>
         </is>
@@ -8854,22 +8565,21 @@
       <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="O134" t="inlineStr"/>
-      <c r="P134" t="inlineStr"/>
-      <c r="Q134" t="n">
+      <c r="P134" t="n">
         <v>8829</v>
       </c>
-      <c r="R134" t="inlineStr">
+      <c r="Q134" t="inlineStr">
         <is>
           <t>Sapotaceae</t>
         </is>
       </c>
-      <c r="S134" t="inlineStr"/>
+      <c r="R134" t="inlineStr"/>
+      <c r="S134" t="inlineStr">
+        <is>
+          <t>Pouteria</t>
+        </is>
+      </c>
       <c r="T134" t="inlineStr">
-        <is>
-          <t>Pouteria</t>
-        </is>
-      </c>
-      <c r="U134" t="inlineStr">
         <is>
           <t>vernicosa</t>
         </is>
@@ -8913,22 +8623,21 @@
       <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="O135" t="inlineStr"/>
-      <c r="P135" t="inlineStr"/>
-      <c r="Q135" t="n">
+      <c r="P135" t="n">
         <v>8829</v>
       </c>
-      <c r="R135" t="inlineStr">
+      <c r="Q135" t="inlineStr">
         <is>
           <t>Sapotaceae</t>
         </is>
       </c>
-      <c r="S135" t="inlineStr"/>
+      <c r="R135" t="inlineStr"/>
+      <c r="S135" t="inlineStr">
+        <is>
+          <t>Pouteria</t>
+        </is>
+      </c>
       <c r="T135" t="inlineStr">
-        <is>
-          <t>Pouteria</t>
-        </is>
-      </c>
-      <c r="U135" t="inlineStr">
         <is>
           <t>vernicosa</t>
         </is>
@@ -8972,24 +8681,23 @@
       <c r="M136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
       <c r="O136" t="inlineStr"/>
-      <c r="P136" t="inlineStr"/>
-      <c r="Q136" t="n">
+      <c r="P136" t="n">
         <v>8830</v>
       </c>
-      <c r="R136" t="inlineStr">
+      <c r="Q136" t="inlineStr">
         <is>
           <t>Moraceae</t>
         </is>
       </c>
-      <c r="S136" t="n">
+      <c r="R136" t="n">
         <v>3265</v>
       </c>
+      <c r="S136" t="inlineStr">
+        <is>
+          <t>Pseudolmedia</t>
+        </is>
+      </c>
       <c r="T136" t="inlineStr">
-        <is>
-          <t>Pseudolmedia</t>
-        </is>
-      </c>
-      <c r="U136" t="inlineStr">
         <is>
           <t>laevis</t>
         </is>
@@ -9031,24 +8739,23 @@
       <c r="M137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
-      <c r="P137" t="inlineStr"/>
-      <c r="Q137" t="n">
+      <c r="P137" t="n">
         <v>8832</v>
       </c>
-      <c r="R137" t="inlineStr">
+      <c r="Q137" t="inlineStr">
         <is>
           <t>Violaceae</t>
         </is>
       </c>
-      <c r="S137" t="n">
+      <c r="R137" t="n">
         <v>3270</v>
       </c>
+      <c r="S137" t="inlineStr">
+        <is>
+          <t>Leonia</t>
+        </is>
+      </c>
       <c r="T137" t="inlineStr">
-        <is>
-          <t>Leonia</t>
-        </is>
-      </c>
-      <c r="U137" t="inlineStr">
         <is>
           <t>longifolium</t>
         </is>
@@ -9094,18 +8801,17 @@
       <c r="M138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="O138" t="inlineStr"/>
-      <c r="P138" t="inlineStr"/>
-      <c r="Q138" t="n">
+      <c r="P138" t="n">
         <v>8834</v>
       </c>
-      <c r="R138" t="inlineStr">
+      <c r="Q138" t="inlineStr">
         <is>
           <t>indet</t>
         </is>
       </c>
+      <c r="R138" t="inlineStr"/>
       <c r="S138" t="inlineStr"/>
       <c r="T138" t="inlineStr"/>
-      <c r="U138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" s="1" t="n">
@@ -9142,27 +8848,22 @@
         </is>
       </c>
       <c r="J139" t="inlineStr"/>
-      <c r="K139" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
       <c r="M139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="O139" t="inlineStr"/>
-      <c r="P139" t="inlineStr"/>
-      <c r="Q139" t="n">
+      <c r="P139" t="n">
         <v>8834</v>
       </c>
-      <c r="R139" t="inlineStr">
+      <c r="Q139" t="inlineStr">
         <is>
           <t>indet</t>
         </is>
       </c>
+      <c r="R139" t="inlineStr"/>
       <c r="S139" t="inlineStr"/>
       <c r="T139" t="inlineStr"/>
-      <c r="U139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" s="1" t="n">
@@ -9204,22 +8905,21 @@
       <c r="M140" t="inlineStr"/>
       <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
-      <c r="P140" t="inlineStr"/>
-      <c r="Q140" t="n">
+      <c r="P140" t="n">
         <v>8836</v>
       </c>
-      <c r="R140" t="inlineStr">
+      <c r="Q140" t="inlineStr">
         <is>
           <t>Siparunaceae</t>
         </is>
       </c>
-      <c r="S140" t="inlineStr"/>
+      <c r="R140" t="inlineStr"/>
+      <c r="S140" t="inlineStr">
+        <is>
+          <t>Siparuna</t>
+        </is>
+      </c>
       <c r="T140" t="inlineStr">
-        <is>
-          <t>Siparuna</t>
-        </is>
-      </c>
-      <c r="U140" t="inlineStr">
         <is>
           <t>sp.1</t>
         </is>
@@ -9260,31 +8960,26 @@
         </is>
       </c>
       <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
       <c r="M141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
       <c r="O141" t="inlineStr"/>
-      <c r="P141" t="inlineStr"/>
-      <c r="Q141" t="n">
+      <c r="P141" t="n">
         <v>8836</v>
       </c>
-      <c r="R141" t="inlineStr">
+      <c r="Q141" t="inlineStr">
         <is>
           <t>Siparunaceae</t>
         </is>
       </c>
-      <c r="S141" t="inlineStr"/>
+      <c r="R141" t="inlineStr"/>
+      <c r="S141" t="inlineStr">
+        <is>
+          <t>Siparuna</t>
+        </is>
+      </c>
       <c r="T141" t="inlineStr">
-        <is>
-          <t>Siparuna</t>
-        </is>
-      </c>
-      <c r="U141" t="inlineStr">
         <is>
           <t>sp.1</t>
         </is>
@@ -9321,43 +9016,42 @@
       <c r="J142" t="n">
         <v>2388</v>
       </c>
-      <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr">
+      <c r="K142" t="inlineStr">
         <is>
           <t>p74-8838</t>
         </is>
       </c>
+      <c r="L142" t="n">
+        <v>0.01506027773689399</v>
+      </c>
       <c r="M142" t="n">
-        <v>0.01506027773689399</v>
+        <v>0.4810743319827603</v>
       </c>
       <c r="N142" t="n">
-        <v>0.4810743319827603</v>
+        <v>0.25</v>
       </c>
       <c r="O142" t="n">
-        <v>0.25</v>
+        <v>-33.65</v>
       </c>
       <c r="P142" t="n">
-        <v>-33.65</v>
-      </c>
-      <c r="Q142" t="n">
         <v>8838</v>
       </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>Sapotaceae</t>
+        </is>
+      </c>
       <c r="R142" t="inlineStr">
         <is>
-          <t>Sapotaceae</t>
+          <t>same as 3244</t>
         </is>
       </c>
       <c r="S142" t="inlineStr">
         <is>
-          <t>same as 3244</t>
+          <t>Pouteria</t>
         </is>
       </c>
       <c r="T142" t="inlineStr">
-        <is>
-          <t>Pouteria</t>
-        </is>
-      </c>
-      <c r="U142" t="inlineStr">
         <is>
           <t>cuspidata</t>
         </is>
@@ -9401,24 +9095,23 @@
       <c r="M143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
       <c r="O143" t="inlineStr"/>
-      <c r="P143" t="inlineStr"/>
-      <c r="Q143" t="n">
+      <c r="P143" t="n">
         <v>8839</v>
       </c>
-      <c r="R143" t="inlineStr">
+      <c r="Q143" t="inlineStr">
         <is>
           <t>Salicaceae</t>
         </is>
       </c>
-      <c r="S143" t="n">
+      <c r="R143" t="n">
         <v>3280</v>
       </c>
+      <c r="S143" t="inlineStr">
+        <is>
+          <t>Tetrathylacium</t>
+        </is>
+      </c>
       <c r="T143" t="inlineStr">
-        <is>
-          <t>Tetrathylacium</t>
-        </is>
-      </c>
-      <c r="U143" t="inlineStr">
         <is>
           <t>macrophyllum</t>
         </is>
@@ -9466,24 +9159,23 @@
       <c r="M144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="O144" t="inlineStr"/>
-      <c r="P144" t="inlineStr"/>
-      <c r="Q144" t="n">
+      <c r="P144" t="n">
         <v>8839</v>
       </c>
-      <c r="R144" t="inlineStr">
+      <c r="Q144" t="inlineStr">
         <is>
           <t>Salicaceae</t>
         </is>
       </c>
-      <c r="S144" t="n">
+      <c r="R144" t="n">
         <v>3280</v>
       </c>
+      <c r="S144" t="inlineStr">
+        <is>
+          <t>Tetrathylacium</t>
+        </is>
+      </c>
       <c r="T144" t="inlineStr">
-        <is>
-          <t>Tetrathylacium</t>
-        </is>
-      </c>
-      <c r="U144" t="inlineStr">
         <is>
           <t>macrophyllum</t>
         </is>
@@ -9520,41 +9212,40 @@
       <c r="J145" t="n">
         <v>2389</v>
       </c>
-      <c r="K145" t="inlineStr"/>
-      <c r="L145" t="inlineStr">
+      <c r="K145" t="inlineStr">
         <is>
           <t>p74-8840</t>
         </is>
       </c>
+      <c r="L145" t="n">
+        <v>0.013054872322637</v>
+      </c>
       <c r="M145" t="n">
-        <v>0.013054872322637</v>
+        <v>0.4551252723799056</v>
       </c>
       <c r="N145" t="n">
-        <v>0.4551252723799056</v>
+        <v>-1.16</v>
       </c>
       <c r="O145" t="n">
-        <v>-1.16</v>
+        <v>-34.88</v>
       </c>
       <c r="P145" t="n">
-        <v>-34.88</v>
-      </c>
-      <c r="Q145" t="n">
         <v>8840</v>
       </c>
-      <c r="R145" t="inlineStr">
+      <c r="Q145" t="inlineStr">
         <is>
           <t>Sapotaceae</t>
         </is>
       </c>
-      <c r="S145" t="n">
+      <c r="R145" t="n">
         <v>3269</v>
       </c>
+      <c r="S145" t="inlineStr">
+        <is>
+          <t>Pouteria</t>
+        </is>
+      </c>
       <c r="T145" t="inlineStr">
-        <is>
-          <t>Pouteria</t>
-        </is>
-      </c>
-      <c r="U145" t="inlineStr">
         <is>
           <t>megaphylla</t>
         </is>
@@ -9602,24 +9293,23 @@
       <c r="M146" t="inlineStr"/>
       <c r="N146" t="inlineStr"/>
       <c r="O146" t="inlineStr"/>
-      <c r="P146" t="inlineStr"/>
-      <c r="Q146" t="n">
+      <c r="P146" t="n">
         <v>8840</v>
       </c>
-      <c r="R146" t="inlineStr">
+      <c r="Q146" t="inlineStr">
         <is>
           <t>Sapotaceae</t>
         </is>
       </c>
-      <c r="S146" t="n">
+      <c r="R146" t="n">
         <v>3269</v>
       </c>
+      <c r="S146" t="inlineStr">
+        <is>
+          <t>Pouteria</t>
+        </is>
+      </c>
       <c r="T146" t="inlineStr">
-        <is>
-          <t>Pouteria</t>
-        </is>
-      </c>
-      <c r="U146" t="inlineStr">
         <is>
           <t>megaphylla</t>
         </is>
@@ -9660,32 +9350,27 @@
         </is>
       </c>
       <c r="J147" t="inlineStr"/>
-      <c r="K147" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
       <c r="M147" t="inlineStr"/>
       <c r="N147" t="inlineStr"/>
       <c r="O147" t="inlineStr"/>
-      <c r="P147" t="inlineStr"/>
-      <c r="Q147" t="n">
+      <c r="P147" t="n">
         <v>8841</v>
       </c>
-      <c r="R147" t="inlineStr">
+      <c r="Q147" t="inlineStr">
         <is>
           <t>Myristicaceae</t>
         </is>
       </c>
-      <c r="S147" t="inlineStr"/>
-      <c r="T147" t="inlineStr">
+      <c r="R147" t="inlineStr"/>
+      <c r="S147" t="inlineStr">
         <is>
           <t xml:space="preserve">Osteophloeum 
 </t>
         </is>
       </c>
-      <c r="U147" t="inlineStr"/>
+      <c r="T147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" s="1" t="n">
@@ -9727,23 +9412,22 @@
       <c r="M148" t="inlineStr"/>
       <c r="N148" t="inlineStr"/>
       <c r="O148" t="inlineStr"/>
-      <c r="P148" t="inlineStr"/>
-      <c r="Q148" t="n">
+      <c r="P148" t="n">
         <v>8841</v>
       </c>
-      <c r="R148" t="inlineStr">
+      <c r="Q148" t="inlineStr">
         <is>
           <t>Myristicaceae</t>
         </is>
       </c>
-      <c r="S148" t="inlineStr"/>
-      <c r="T148" t="inlineStr">
+      <c r="R148" t="inlineStr"/>
+      <c r="S148" t="inlineStr">
         <is>
           <t xml:space="preserve">Osteophloeum 
 </t>
         </is>
       </c>
-      <c r="U148" t="inlineStr"/>
+      <c r="T148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" s="1" t="n">
@@ -9785,22 +9469,21 @@
       <c r="M149" t="inlineStr"/>
       <c r="N149" t="inlineStr"/>
       <c r="O149" t="inlineStr"/>
-      <c r="P149" t="inlineStr"/>
-      <c r="Q149" t="n">
+      <c r="P149" t="n">
         <v>8843</v>
       </c>
-      <c r="R149" t="inlineStr">
+      <c r="Q149" t="inlineStr">
         <is>
           <t>Annonaceae</t>
         </is>
       </c>
-      <c r="S149" t="inlineStr"/>
+      <c r="R149" t="inlineStr"/>
+      <c r="S149" t="inlineStr">
+        <is>
+          <t>Guatteria</t>
+        </is>
+      </c>
       <c r="T149" t="inlineStr">
-        <is>
-          <t>Guatteria</t>
-        </is>
-      </c>
-      <c r="U149" t="inlineStr">
         <is>
           <t>sp</t>
         </is>
@@ -9841,31 +9524,26 @@
         </is>
       </c>
       <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K150" t="inlineStr"/>
       <c r="L150" t="inlineStr"/>
       <c r="M150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
       <c r="O150" t="inlineStr"/>
-      <c r="P150" t="inlineStr"/>
-      <c r="Q150" t="n">
+      <c r="P150" t="n">
         <v>8843</v>
       </c>
-      <c r="R150" t="inlineStr">
+      <c r="Q150" t="inlineStr">
         <is>
           <t>Annonaceae</t>
         </is>
       </c>
-      <c r="S150" t="inlineStr"/>
+      <c r="R150" t="inlineStr"/>
+      <c r="S150" t="inlineStr">
+        <is>
+          <t>Guatteria</t>
+        </is>
+      </c>
       <c r="T150" t="inlineStr">
-        <is>
-          <t>Guatteria</t>
-        </is>
-      </c>
-      <c r="U150" t="inlineStr">
         <is>
           <t>sp</t>
         </is>
@@ -9906,31 +9584,26 @@
         </is>
       </c>
       <c r="J151" t="inlineStr"/>
-      <c r="K151" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K151" t="inlineStr"/>
       <c r="L151" t="inlineStr"/>
       <c r="M151" t="inlineStr"/>
       <c r="N151" t="inlineStr"/>
       <c r="O151" t="inlineStr"/>
-      <c r="P151" t="inlineStr"/>
-      <c r="Q151" t="n">
+      <c r="P151" t="n">
         <v>8848</v>
       </c>
-      <c r="R151" t="inlineStr">
+      <c r="Q151" t="inlineStr">
         <is>
           <t>Myristicaceae</t>
         </is>
       </c>
-      <c r="S151" t="inlineStr"/>
-      <c r="T151" t="inlineStr">
+      <c r="R151" t="inlineStr"/>
+      <c r="S151" t="inlineStr">
         <is>
           <t>Virola</t>
         </is>
       </c>
-      <c r="U151" t="inlineStr"/>
+      <c r="T151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" s="1" t="n">
@@ -9972,22 +9645,21 @@
       <c r="M152" t="inlineStr"/>
       <c r="N152" t="inlineStr"/>
       <c r="O152" t="inlineStr"/>
-      <c r="P152" t="inlineStr"/>
-      <c r="Q152" t="n">
+      <c r="P152" t="n">
         <v>8848</v>
       </c>
-      <c r="R152" t="inlineStr">
+      <c r="Q152" t="inlineStr">
         <is>
           <t>Myristicaceae</t>
         </is>
       </c>
-      <c r="S152" t="inlineStr"/>
-      <c r="T152" t="inlineStr">
+      <c r="R152" t="inlineStr"/>
+      <c r="S152" t="inlineStr">
         <is>
           <t>Virola</t>
         </is>
       </c>
-      <c r="U152" t="inlineStr"/>
+      <c r="T152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" s="1" t="n">
@@ -10020,41 +9692,40 @@
       <c r="J153" t="n">
         <v>2368</v>
       </c>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr">
+      <c r="K153" t="inlineStr">
         <is>
           <t>p74-8849</t>
         </is>
       </c>
+      <c r="L153" t="n">
+        <v>0.0157979699642389</v>
+      </c>
       <c r="M153" t="n">
-        <v>0.0157979699642389</v>
+        <v>0.4892875807439671</v>
       </c>
       <c r="N153" t="n">
-        <v>0.4892875807439671</v>
+        <v>0.44</v>
       </c>
       <c r="O153" t="n">
-        <v>0.44</v>
+        <v>-33.24</v>
       </c>
       <c r="P153" t="n">
-        <v>-33.24</v>
-      </c>
-      <c r="Q153" t="n">
         <v>8849</v>
       </c>
-      <c r="R153" t="inlineStr">
+      <c r="Q153" t="inlineStr">
         <is>
           <t>Calophyllaceae</t>
         </is>
       </c>
-      <c r="S153" t="n">
+      <c r="R153" t="n">
         <v>3163</v>
       </c>
+      <c r="S153" t="inlineStr">
+        <is>
+          <t>Marila</t>
+        </is>
+      </c>
       <c r="T153" t="inlineStr">
-        <is>
-          <t>Marila</t>
-        </is>
-      </c>
-      <c r="U153" t="inlineStr">
         <is>
           <t>grandiflora</t>
         </is>
@@ -10095,27 +9766,22 @@
         </is>
       </c>
       <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
       <c r="M154" t="inlineStr"/>
       <c r="N154" t="inlineStr"/>
       <c r="O154" t="inlineStr"/>
-      <c r="P154" t="inlineStr"/>
-      <c r="Q154" t="n">
+      <c r="P154" t="n">
         <v>8850</v>
       </c>
-      <c r="R154" t="inlineStr">
+      <c r="Q154" t="inlineStr">
         <is>
           <t>Rubiaceae</t>
         </is>
       </c>
+      <c r="R154" t="inlineStr"/>
       <c r="S154" t="inlineStr"/>
       <c r="T154" t="inlineStr"/>
-      <c r="U154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" s="1" t="n">
@@ -10157,18 +9823,17 @@
       <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="O155" t="inlineStr"/>
-      <c r="P155" t="inlineStr"/>
-      <c r="Q155" t="n">
+      <c r="P155" t="n">
         <v>8850</v>
       </c>
-      <c r="R155" t="inlineStr">
+      <c r="Q155" t="inlineStr">
         <is>
           <t>Rubiaceae</t>
         </is>
       </c>
+      <c r="R155" t="inlineStr"/>
       <c r="S155" t="inlineStr"/>
       <c r="T155" t="inlineStr"/>
-      <c r="U155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" s="1" t="n">
@@ -10201,41 +9866,40 @@
       <c r="J156" t="n">
         <v>2374</v>
       </c>
-      <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr">
+      <c r="K156" t="inlineStr">
         <is>
           <t>p74-8853</t>
         </is>
       </c>
+      <c r="L156" t="n">
+        <v>0.01315526705850149</v>
+      </c>
       <c r="M156" t="n">
-        <v>0.01315526705850149</v>
+        <v>0.4473774700942126</v>
       </c>
       <c r="N156" t="n">
-        <v>0.4473774700942126</v>
+        <v>-0.42</v>
       </c>
       <c r="O156" t="n">
-        <v>-0.42</v>
+        <v>-34.64</v>
       </c>
       <c r="P156" t="n">
-        <v>-34.64</v>
-      </c>
-      <c r="Q156" t="n">
         <v>8853</v>
       </c>
-      <c r="R156" t="inlineStr">
+      <c r="Q156" t="inlineStr">
         <is>
           <t>Myrtaceae</t>
         </is>
       </c>
-      <c r="S156" t="n">
+      <c r="R156" t="n">
         <v>3266</v>
       </c>
-      <c r="T156" t="inlineStr">
+      <c r="S156" t="inlineStr">
         <is>
           <t>Eugenia</t>
         </is>
       </c>
-      <c r="U156" t="inlineStr"/>
+      <c r="T156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" s="1" t="n">
@@ -10268,41 +9932,40 @@
       <c r="J157" t="n">
         <v>2375</v>
       </c>
-      <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr">
+      <c r="K157" t="inlineStr">
         <is>
           <t>p74-8854</t>
         </is>
       </c>
+      <c r="L157" t="n">
+        <v>0.02065846271337194</v>
+      </c>
       <c r="M157" t="n">
-        <v>0.02065846271337194</v>
+        <v>0.3932217774359631</v>
       </c>
       <c r="N157" t="n">
-        <v>0.3932217774359631</v>
+        <v>-0.3</v>
       </c>
       <c r="O157" t="n">
-        <v>-0.3</v>
+        <v>-31.32</v>
       </c>
       <c r="P157" t="n">
-        <v>-31.32</v>
-      </c>
-      <c r="Q157" t="n">
         <v>8854</v>
       </c>
-      <c r="R157" t="inlineStr">
+      <c r="Q157" t="inlineStr">
         <is>
           <t>Moraceae</t>
         </is>
       </c>
-      <c r="S157" t="n">
+      <c r="R157" t="n">
         <v>3268</v>
       </c>
+      <c r="S157" t="inlineStr">
+        <is>
+          <t>Sorocea</t>
+        </is>
+      </c>
       <c r="T157" t="inlineStr">
-        <is>
-          <t>Sorocea</t>
-        </is>
-      </c>
-      <c r="U157" t="inlineStr">
         <is>
           <t>pubivena</t>
         </is>
@@ -10350,24 +10013,23 @@
       <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="O158" t="inlineStr"/>
-      <c r="P158" t="inlineStr"/>
-      <c r="Q158" t="n">
+      <c r="P158" t="n">
         <v>8854</v>
       </c>
-      <c r="R158" t="inlineStr">
+      <c r="Q158" t="inlineStr">
         <is>
           <t>Moraceae</t>
         </is>
       </c>
-      <c r="S158" t="n">
+      <c r="R158" t="n">
         <v>3268</v>
       </c>
+      <c r="S158" t="inlineStr">
+        <is>
+          <t>Sorocea</t>
+        </is>
+      </c>
       <c r="T158" t="inlineStr">
-        <is>
-          <t>Sorocea</t>
-        </is>
-      </c>
-      <c r="U158" t="inlineStr">
         <is>
           <t>pubivena</t>
         </is>
@@ -10411,26 +10073,25 @@
       <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
       <c r="O159" t="inlineStr"/>
-      <c r="P159" t="inlineStr"/>
-      <c r="Q159" t="n">
+      <c r="P159" t="n">
         <v>8855</v>
       </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>Annonaceae</t>
+        </is>
+      </c>
       <c r="R159" t="inlineStr">
         <is>
-          <t>Annonaceae</t>
+          <t>same as 3262</t>
         </is>
       </c>
       <c r="S159" t="inlineStr">
         <is>
-          <t>same as 3262</t>
-        </is>
-      </c>
-      <c r="T159" t="inlineStr">
-        <is>
           <t>Guatteria</t>
         </is>
       </c>
-      <c r="U159" t="inlineStr"/>
+      <c r="T159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" s="1" t="n">
@@ -10474,26 +10135,25 @@
       <c r="M160" t="inlineStr"/>
       <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr"/>
-      <c r="P160" t="inlineStr"/>
-      <c r="Q160" t="n">
+      <c r="P160" t="n">
         <v>8855</v>
       </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>Annonaceae</t>
+        </is>
+      </c>
       <c r="R160" t="inlineStr">
         <is>
-          <t>Annonaceae</t>
+          <t>same as 3262</t>
         </is>
       </c>
       <c r="S160" t="inlineStr">
         <is>
-          <t>same as 3262</t>
-        </is>
-      </c>
-      <c r="T160" t="inlineStr">
-        <is>
           <t>Guatteria</t>
         </is>
       </c>
-      <c r="U160" t="inlineStr"/>
+      <c r="T160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" s="1" t="n">
@@ -10526,41 +10186,40 @@
       <c r="J161" t="n">
         <v>2382</v>
       </c>
-      <c r="K161" t="inlineStr"/>
-      <c r="L161" t="inlineStr">
+      <c r="K161" t="inlineStr">
         <is>
           <t>p74-8859</t>
         </is>
       </c>
+      <c r="L161" t="n">
+        <v>0.01519611827639625</v>
+      </c>
       <c r="M161" t="n">
-        <v>0.01519611827639625</v>
+        <v>0.3990582769402648</v>
       </c>
       <c r="N161" t="n">
-        <v>0.3990582769402648</v>
+        <v>0.5</v>
       </c>
       <c r="O161" t="n">
-        <v>0.5</v>
+        <v>-34.77</v>
       </c>
       <c r="P161" t="n">
-        <v>-34.77</v>
-      </c>
-      <c r="Q161" t="n">
         <v>8859</v>
       </c>
-      <c r="R161" t="inlineStr">
+      <c r="Q161" t="inlineStr">
         <is>
           <t>Moraceae</t>
         </is>
       </c>
-      <c r="S161" t="n">
+      <c r="R161" t="n">
         <v>3264</v>
       </c>
+      <c r="S161" t="inlineStr">
+        <is>
+          <t>Pseudolmedia</t>
+        </is>
+      </c>
       <c r="T161" t="inlineStr">
-        <is>
-          <t>Pseudolmedia</t>
-        </is>
-      </c>
-      <c r="U161" t="inlineStr">
         <is>
           <t>laevigata</t>
         </is>
@@ -10608,24 +10267,23 @@
       <c r="M162" t="inlineStr"/>
       <c r="N162" t="inlineStr"/>
       <c r="O162" t="inlineStr"/>
-      <c r="P162" t="inlineStr"/>
-      <c r="Q162" t="n">
+      <c r="P162" t="n">
         <v>8859</v>
       </c>
-      <c r="R162" t="inlineStr">
+      <c r="Q162" t="inlineStr">
         <is>
           <t>Moraceae</t>
         </is>
       </c>
-      <c r="S162" t="n">
+      <c r="R162" t="n">
         <v>3264</v>
       </c>
+      <c r="S162" t="inlineStr">
+        <is>
+          <t>Pseudolmedia</t>
+        </is>
+      </c>
       <c r="T162" t="inlineStr">
-        <is>
-          <t>Pseudolmedia</t>
-        </is>
-      </c>
-      <c r="U162" t="inlineStr">
         <is>
           <t>laevigata</t>
         </is>
@@ -10666,31 +10324,26 @@
         </is>
       </c>
       <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
       <c r="M163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
       <c r="O163" t="inlineStr"/>
-      <c r="P163" t="inlineStr"/>
-      <c r="Q163" t="n">
+      <c r="P163" t="n">
         <v>8861</v>
       </c>
-      <c r="R163" t="inlineStr">
+      <c r="Q163" t="inlineStr">
         <is>
           <t>Calophyllaceae</t>
         </is>
       </c>
-      <c r="S163" t="inlineStr"/>
-      <c r="T163" t="inlineStr">
+      <c r="R163" t="inlineStr"/>
+      <c r="S163" t="inlineStr">
         <is>
           <t>Marila</t>
         </is>
       </c>
-      <c r="U163" t="inlineStr"/>
+      <c r="T163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" s="1" t="n">
@@ -10732,22 +10385,21 @@
       <c r="M164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
       <c r="O164" t="inlineStr"/>
-      <c r="P164" t="inlineStr"/>
-      <c r="Q164" t="n">
+      <c r="P164" t="n">
         <v>8861</v>
       </c>
-      <c r="R164" t="inlineStr">
+      <c r="Q164" t="inlineStr">
         <is>
           <t>Calophyllaceae</t>
         </is>
       </c>
-      <c r="S164" t="inlineStr"/>
-      <c r="T164" t="inlineStr">
+      <c r="R164" t="inlineStr"/>
+      <c r="S164" t="inlineStr">
         <is>
           <t>Marila</t>
         </is>
       </c>
-      <c r="U164" t="inlineStr"/>
+      <c r="T164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" s="1" t="n">
@@ -10784,31 +10436,26 @@
         </is>
       </c>
       <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
       <c r="M165" t="inlineStr"/>
       <c r="N165" t="inlineStr"/>
       <c r="O165" t="inlineStr"/>
-      <c r="P165" t="inlineStr"/>
-      <c r="Q165" t="n">
+      <c r="P165" t="n">
         <v>8862</v>
       </c>
-      <c r="R165" t="inlineStr">
+      <c r="Q165" t="inlineStr">
         <is>
           <t>Myristicaceae</t>
         </is>
       </c>
-      <c r="S165" t="inlineStr"/>
+      <c r="R165" t="inlineStr"/>
+      <c r="S165" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Virola </t>
+        </is>
+      </c>
       <c r="T165" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Virola </t>
-        </is>
-      </c>
-      <c r="U165" t="inlineStr">
         <is>
           <t>multinervia</t>
         </is>
@@ -10854,22 +10501,21 @@
       <c r="M166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="O166" t="inlineStr"/>
-      <c r="P166" t="inlineStr"/>
-      <c r="Q166" t="n">
+      <c r="P166" t="n">
         <v>8862</v>
       </c>
-      <c r="R166" t="inlineStr">
+      <c r="Q166" t="inlineStr">
         <is>
           <t>Myristicaceae</t>
         </is>
       </c>
-      <c r="S166" t="inlineStr"/>
+      <c r="R166" t="inlineStr"/>
+      <c r="S166" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Virola </t>
+        </is>
+      </c>
       <c r="T166" t="inlineStr">
-        <is>
-          <t xml:space="preserve">Virola </t>
-        </is>
-      </c>
-      <c r="U166" t="inlineStr">
         <is>
           <t>multinervia</t>
         </is>
@@ -10906,41 +10552,40 @@
       <c r="J167" t="n">
         <v>2380</v>
       </c>
-      <c r="K167" t="inlineStr"/>
-      <c r="L167" t="inlineStr">
+      <c r="K167" t="inlineStr">
         <is>
           <t>p74-8863</t>
         </is>
       </c>
+      <c r="L167" t="n">
+        <v>0.01887504041753914</v>
+      </c>
       <c r="M167" t="n">
-        <v>0.01887504041753914</v>
+        <v>0.4521728216082592</v>
       </c>
       <c r="N167" t="n">
-        <v>0.4521728216082592</v>
+        <v>-0.82</v>
       </c>
       <c r="O167" t="n">
-        <v>-0.82</v>
+        <v>-34.43</v>
       </c>
       <c r="P167" t="n">
-        <v>-34.43</v>
-      </c>
-      <c r="Q167" t="n">
         <v>8863</v>
       </c>
-      <c r="R167" t="inlineStr">
+      <c r="Q167" t="inlineStr">
         <is>
           <t>Lauraceae</t>
         </is>
       </c>
-      <c r="S167" t="n">
+      <c r="R167" t="n">
         <v>3273</v>
       </c>
-      <c r="T167" t="inlineStr">
+      <c r="S167" t="inlineStr">
         <is>
           <t>Pleurothyrium</t>
         </is>
       </c>
-      <c r="U167" t="inlineStr"/>
+      <c r="T167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" s="1" t="n">
@@ -10979,33 +10624,28 @@
       <c r="J168" t="n">
         <v>2380</v>
       </c>
-      <c r="K168" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K168" t="inlineStr"/>
       <c r="L168" t="inlineStr"/>
       <c r="M168" t="inlineStr"/>
       <c r="N168" t="inlineStr"/>
       <c r="O168" t="inlineStr"/>
-      <c r="P168" t="inlineStr"/>
-      <c r="Q168" t="n">
+      <c r="P168" t="n">
         <v>8863</v>
       </c>
-      <c r="R168" t="inlineStr">
+      <c r="Q168" t="inlineStr">
         <is>
           <t>Lauraceae</t>
         </is>
       </c>
-      <c r="S168" t="n">
+      <c r="R168" t="n">
         <v>3273</v>
       </c>
-      <c r="T168" t="inlineStr">
+      <c r="S168" t="inlineStr">
         <is>
           <t>Pleurothyrium</t>
         </is>
       </c>
-      <c r="U168" t="inlineStr"/>
+      <c r="T168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" s="1" t="n">
@@ -11038,41 +10678,40 @@
       <c r="J169" t="n">
         <v>2380</v>
       </c>
-      <c r="K169" t="inlineStr"/>
-      <c r="L169" t="inlineStr">
+      <c r="K169" t="inlineStr">
         <is>
           <t>p74-8863</t>
         </is>
       </c>
+      <c r="L169" t="n">
+        <v>0.01887504041753914</v>
+      </c>
       <c r="M169" t="n">
-        <v>0.01887504041753914</v>
+        <v>0.4521728216082592</v>
       </c>
       <c r="N169" t="n">
-        <v>0.4521728216082592</v>
+        <v>-0.82</v>
       </c>
       <c r="O169" t="n">
-        <v>-0.82</v>
+        <v>-34.43</v>
       </c>
       <c r="P169" t="n">
-        <v>-34.43</v>
-      </c>
-      <c r="Q169" t="n">
         <v>8863</v>
       </c>
-      <c r="R169" t="inlineStr">
+      <c r="Q169" t="inlineStr">
         <is>
           <t>Lauraceae</t>
         </is>
       </c>
-      <c r="S169" t="n">
+      <c r="R169" t="n">
         <v>3273</v>
       </c>
-      <c r="T169" t="inlineStr">
+      <c r="S169" t="inlineStr">
         <is>
           <t>Pleurothyrium</t>
         </is>
       </c>
-      <c r="U169" t="inlineStr"/>
+      <c r="T169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" s="1" t="n">
@@ -11109,31 +10748,26 @@
         </is>
       </c>
       <c r="J170" t="inlineStr"/>
-      <c r="K170" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K170" t="inlineStr"/>
       <c r="L170" t="inlineStr"/>
       <c r="M170" t="inlineStr"/>
       <c r="N170" t="inlineStr"/>
       <c r="O170" t="inlineStr"/>
-      <c r="P170" t="inlineStr"/>
-      <c r="Q170" t="n">
+      <c r="P170" t="n">
         <v>8864</v>
       </c>
-      <c r="R170" t="inlineStr">
+      <c r="Q170" t="inlineStr">
         <is>
           <t>Moraceae</t>
         </is>
       </c>
-      <c r="S170" t="inlineStr"/>
-      <c r="T170" t="inlineStr">
+      <c r="R170" t="inlineStr"/>
+      <c r="S170" t="inlineStr">
         <is>
           <t>Perebea</t>
         </is>
       </c>
-      <c r="U170" t="inlineStr"/>
+      <c r="T170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" s="1" t="n">
@@ -11175,22 +10809,21 @@
       <c r="M171" t="inlineStr"/>
       <c r="N171" t="inlineStr"/>
       <c r="O171" t="inlineStr"/>
-      <c r="P171" t="inlineStr"/>
-      <c r="Q171" t="n">
+      <c r="P171" t="n">
         <v>8864</v>
       </c>
-      <c r="R171" t="inlineStr">
+      <c r="Q171" t="inlineStr">
         <is>
           <t>Moraceae</t>
         </is>
       </c>
-      <c r="S171" t="inlineStr"/>
-      <c r="T171" t="inlineStr">
+      <c r="R171" t="inlineStr"/>
+      <c r="S171" t="inlineStr">
         <is>
           <t>Perebea</t>
         </is>
       </c>
-      <c r="U171" t="inlineStr"/>
+      <c r="T171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" s="1" t="n">
@@ -11234,26 +10867,25 @@
       <c r="M172" t="inlineStr"/>
       <c r="N172" t="inlineStr"/>
       <c r="O172" t="inlineStr"/>
-      <c r="P172" t="inlineStr"/>
-      <c r="Q172" t="n">
+      <c r="P172" t="n">
         <v>8865</v>
       </c>
+      <c r="Q172" t="inlineStr">
+        <is>
+          <t>Violaceae</t>
+        </is>
+      </c>
       <c r="R172" t="inlineStr">
         <is>
-          <t>Violaceae</t>
+          <t>3928</t>
         </is>
       </c>
       <c r="S172" t="inlineStr">
         <is>
-          <t>3928</t>
+          <t>Leonia</t>
         </is>
       </c>
       <c r="T172" t="inlineStr">
-        <is>
-          <t>Leonia</t>
-        </is>
-      </c>
-      <c r="U172" t="inlineStr">
         <is>
           <t>glycycarpa</t>
         </is>
@@ -11290,43 +10922,42 @@
       <c r="J173" t="n">
         <v>2142</v>
       </c>
-      <c r="K173" t="inlineStr"/>
-      <c r="L173" t="inlineStr">
+      <c r="K173" t="inlineStr">
         <is>
           <t>p68-8867</t>
         </is>
       </c>
+      <c r="L173" t="n">
+        <v>0.020640948</v>
+      </c>
       <c r="M173" t="n">
-        <v>0.020640948</v>
+        <v>0.440605127</v>
       </c>
       <c r="N173" t="n">
-        <v>0.440605127</v>
+        <v>1.538858585858584</v>
       </c>
       <c r="O173" t="n">
-        <v>1.538858585858584</v>
+        <v>-34.17514612937434</v>
       </c>
       <c r="P173" t="n">
-        <v>-34.17514612937434</v>
-      </c>
-      <c r="Q173" t="n">
         <v>8867</v>
       </c>
+      <c r="Q173" t="inlineStr">
+        <is>
+          <t>Rhizophoraceae</t>
+        </is>
+      </c>
       <c r="R173" t="inlineStr">
         <is>
-          <t>Rhizophoraceae</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="S173" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>Cassipourea</t>
         </is>
       </c>
       <c r="T173" t="inlineStr">
-        <is>
-          <t>Cassipourea</t>
-        </is>
-      </c>
-      <c r="U173" t="inlineStr">
         <is>
           <t>guianensis</t>
         </is>
@@ -11374,26 +11005,25 @@
       <c r="M174" t="inlineStr"/>
       <c r="N174" t="inlineStr"/>
       <c r="O174" t="inlineStr"/>
-      <c r="P174" t="inlineStr"/>
-      <c r="Q174" t="n">
+      <c r="P174" t="n">
         <v>8867</v>
       </c>
+      <c r="Q174" t="inlineStr">
+        <is>
+          <t>Rhizophoraceae</t>
+        </is>
+      </c>
       <c r="R174" t="inlineStr">
         <is>
-          <t>Rhizophoraceae</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="S174" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>Cassipourea</t>
         </is>
       </c>
       <c r="T174" t="inlineStr">
-        <is>
-          <t>Cassipourea</t>
-        </is>
-      </c>
-      <c r="U174" t="inlineStr">
         <is>
           <t>guianensis</t>
         </is>
@@ -11430,43 +11060,42 @@
       <c r="J175" t="n">
         <v>2142</v>
       </c>
-      <c r="K175" t="inlineStr"/>
-      <c r="L175" t="inlineStr">
+      <c r="K175" t="inlineStr">
         <is>
           <t>p68-8867</t>
         </is>
       </c>
+      <c r="L175" t="n">
+        <v>0.020640948</v>
+      </c>
       <c r="M175" t="n">
-        <v>0.020640948</v>
+        <v>0.440605127</v>
       </c>
       <c r="N175" t="n">
-        <v>0.440605127</v>
+        <v>1.538858585858584</v>
       </c>
       <c r="O175" t="n">
-        <v>1.538858585858584</v>
+        <v>-34.17514612937434</v>
       </c>
       <c r="P175" t="n">
-        <v>-34.17514612937434</v>
-      </c>
-      <c r="Q175" t="n">
         <v>8867</v>
       </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>Rhizophoraceae</t>
+        </is>
+      </c>
       <c r="R175" t="inlineStr">
         <is>
-          <t>Rhizophoraceae</t>
+          <t>3925</t>
         </is>
       </c>
       <c r="S175" t="inlineStr">
         <is>
-          <t>3925</t>
+          <t>Cassipourea</t>
         </is>
       </c>
       <c r="T175" t="inlineStr">
-        <is>
-          <t>Cassipourea</t>
-        </is>
-      </c>
-      <c r="U175" t="inlineStr">
         <is>
           <t>guianensis</t>
         </is>
@@ -11510,26 +11139,25 @@
       <c r="M176" t="inlineStr"/>
       <c r="N176" t="inlineStr"/>
       <c r="O176" t="inlineStr"/>
-      <c r="P176" t="inlineStr"/>
-      <c r="Q176" t="n">
+      <c r="P176" t="n">
         <v>8869</v>
       </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>Sapotaceae</t>
+        </is>
+      </c>
       <c r="R176" t="inlineStr">
         <is>
-          <t>Sapotaceae</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="S176" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>Sarcaulus</t>
         </is>
       </c>
       <c r="T176" t="inlineStr">
-        <is>
-          <t>Sarcaulus</t>
-        </is>
-      </c>
-      <c r="U176" t="inlineStr">
         <is>
           <t>aff. oblatus</t>
         </is>
@@ -11577,26 +11205,25 @@
       <c r="M177" t="inlineStr"/>
       <c r="N177" t="inlineStr"/>
       <c r="O177" t="inlineStr"/>
-      <c r="P177" t="inlineStr"/>
-      <c r="Q177" t="n">
+      <c r="P177" t="n">
         <v>8869</v>
       </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>Sapotaceae</t>
+        </is>
+      </c>
       <c r="R177" t="inlineStr">
         <is>
-          <t>Sapotaceae</t>
+          <t>3924</t>
         </is>
       </c>
       <c r="S177" t="inlineStr">
         <is>
-          <t>3924</t>
+          <t>Sarcaulus</t>
         </is>
       </c>
       <c r="T177" t="inlineStr">
-        <is>
-          <t>Sarcaulus</t>
-        </is>
-      </c>
-      <c r="U177" t="inlineStr">
         <is>
           <t>aff. oblatus</t>
         </is>
@@ -11644,26 +11271,25 @@
       <c r="M178" t="inlineStr"/>
       <c r="N178" t="inlineStr"/>
       <c r="O178" t="inlineStr"/>
-      <c r="P178" t="inlineStr"/>
-      <c r="Q178" t="n">
+      <c r="P178" t="n">
         <v>8870</v>
       </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>Lauraceae</t>
+        </is>
+      </c>
       <c r="R178" t="inlineStr">
         <is>
-          <t>Lauraceae</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="S178" t="inlineStr">
         <is>
-          <t>3923</t>
-        </is>
-      </c>
-      <c r="T178" t="inlineStr">
-        <is>
           <t>Ocotea</t>
         </is>
       </c>
-      <c r="U178" t="inlineStr"/>
+      <c r="T178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" s="1" t="n">
@@ -11707,26 +11333,25 @@
       <c r="M179" t="inlineStr"/>
       <c r="N179" t="inlineStr"/>
       <c r="O179" t="inlineStr"/>
-      <c r="P179" t="inlineStr"/>
-      <c r="Q179" t="n">
+      <c r="P179" t="n">
         <v>8870</v>
       </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>Lauraceae</t>
+        </is>
+      </c>
       <c r="R179" t="inlineStr">
         <is>
-          <t>Lauraceae</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="S179" t="inlineStr">
         <is>
-          <t>3923</t>
-        </is>
-      </c>
-      <c r="T179" t="inlineStr">
-        <is>
           <t>Ocotea</t>
         </is>
       </c>
-      <c r="U179" t="inlineStr"/>
+      <c r="T179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" s="1" t="n">
@@ -11759,43 +11384,42 @@
       <c r="J180" t="n">
         <v>2139</v>
       </c>
-      <c r="K180" t="inlineStr"/>
-      <c r="L180" t="inlineStr">
+      <c r="K180" t="inlineStr">
         <is>
           <t>p68-8870</t>
         </is>
       </c>
+      <c r="L180" t="n">
+        <v>0.021749615</v>
+      </c>
       <c r="M180" t="n">
-        <v>0.021749615</v>
+        <v>0.495438619</v>
       </c>
       <c r="N180" t="n">
-        <v>0.495438619</v>
+        <v>-0.5456388888888914</v>
       </c>
       <c r="O180" t="n">
-        <v>-0.5456388888888914</v>
+        <v>-34.0256131495228</v>
       </c>
       <c r="P180" t="n">
-        <v>-34.0256131495228</v>
-      </c>
-      <c r="Q180" t="n">
         <v>8870</v>
       </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>Lauraceae</t>
+        </is>
+      </c>
       <c r="R180" t="inlineStr">
         <is>
-          <t>Lauraceae</t>
+          <t>3923</t>
         </is>
       </c>
       <c r="S180" t="inlineStr">
         <is>
-          <t>3923</t>
-        </is>
-      </c>
-      <c r="T180" t="inlineStr">
-        <is>
           <t>Ocotea</t>
         </is>
       </c>
-      <c r="U180" t="inlineStr"/>
+      <c r="T180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" s="1" t="n">
@@ -11837,22 +11461,21 @@
       <c r="M181" t="inlineStr"/>
       <c r="N181" t="inlineStr"/>
       <c r="O181" t="inlineStr"/>
-      <c r="P181" t="inlineStr"/>
-      <c r="Q181" t="n">
+      <c r="P181" t="n">
         <v>8872</v>
       </c>
-      <c r="R181" t="inlineStr">
+      <c r="Q181" t="inlineStr">
         <is>
           <t>Fabaceae</t>
         </is>
       </c>
-      <c r="S181" t="inlineStr"/>
+      <c r="R181" t="inlineStr"/>
+      <c r="S181" t="inlineStr">
+        <is>
+          <t>Macrolobium</t>
+        </is>
+      </c>
       <c r="T181" t="inlineStr">
-        <is>
-          <t>Macrolobium</t>
-        </is>
-      </c>
-      <c r="U181" t="inlineStr">
         <is>
           <t>cf. ischnocalyx</t>
         </is>
@@ -11893,31 +11516,26 @@
         </is>
       </c>
       <c r="J182" t="inlineStr"/>
-      <c r="K182" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K182" t="inlineStr"/>
       <c r="L182" t="inlineStr"/>
       <c r="M182" t="inlineStr"/>
       <c r="N182" t="inlineStr"/>
       <c r="O182" t="inlineStr"/>
-      <c r="P182" t="inlineStr"/>
-      <c r="Q182" t="n">
+      <c r="P182" t="n">
         <v>8872</v>
       </c>
-      <c r="R182" t="inlineStr">
+      <c r="Q182" t="inlineStr">
         <is>
           <t>Fabaceae</t>
         </is>
       </c>
-      <c r="S182" t="inlineStr"/>
+      <c r="R182" t="inlineStr"/>
+      <c r="S182" t="inlineStr">
+        <is>
+          <t>Macrolobium</t>
+        </is>
+      </c>
       <c r="T182" t="inlineStr">
-        <is>
-          <t>Macrolobium</t>
-        </is>
-      </c>
-      <c r="U182" t="inlineStr">
         <is>
           <t>cf. ischnocalyx</t>
         </is>
@@ -11963,22 +11581,21 @@
       <c r="M183" t="inlineStr"/>
       <c r="N183" t="inlineStr"/>
       <c r="O183" t="inlineStr"/>
-      <c r="P183" t="inlineStr"/>
-      <c r="Q183" t="n">
+      <c r="P183" t="n">
         <v>8874</v>
       </c>
-      <c r="R183" t="inlineStr">
+      <c r="Q183" t="inlineStr">
         <is>
           <t>Euphorbiaceae</t>
         </is>
       </c>
-      <c r="S183" t="inlineStr"/>
+      <c r="R183" t="inlineStr"/>
+      <c r="S183" t="inlineStr">
+        <is>
+          <t>Pseudosenefeldera</t>
+        </is>
+      </c>
       <c r="T183" t="inlineStr">
-        <is>
-          <t>Pseudosenefeldera</t>
-        </is>
-      </c>
-      <c r="U183" t="inlineStr">
         <is>
           <t>inclinata</t>
         </is>
@@ -12019,31 +11636,26 @@
         </is>
       </c>
       <c r="J184" t="inlineStr"/>
-      <c r="K184" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K184" t="inlineStr"/>
       <c r="L184" t="inlineStr"/>
       <c r="M184" t="inlineStr"/>
       <c r="N184" t="inlineStr"/>
       <c r="O184" t="inlineStr"/>
-      <c r="P184" t="inlineStr"/>
-      <c r="Q184" t="n">
+      <c r="P184" t="n">
         <v>8874</v>
       </c>
-      <c r="R184" t="inlineStr">
+      <c r="Q184" t="inlineStr">
         <is>
           <t>Euphorbiaceae</t>
         </is>
       </c>
-      <c r="S184" t="inlineStr"/>
+      <c r="R184" t="inlineStr"/>
+      <c r="S184" t="inlineStr">
+        <is>
+          <t>Pseudosenefeldera</t>
+        </is>
+      </c>
       <c r="T184" t="inlineStr">
-        <is>
-          <t>Pseudosenefeldera</t>
-        </is>
-      </c>
-      <c r="U184" t="inlineStr">
         <is>
           <t>inclinata</t>
         </is>
@@ -12080,43 +11692,42 @@
       <c r="J185" t="n">
         <v>2133</v>
       </c>
-      <c r="K185" t="inlineStr"/>
-      <c r="L185" t="inlineStr">
+      <c r="K185" t="inlineStr">
         <is>
           <t>p68-8876</t>
         </is>
       </c>
+      <c r="L185" t="n">
+        <v>0.017456195</v>
+      </c>
       <c r="M185" t="n">
-        <v>0.017456195</v>
+        <v>0.481396993</v>
       </c>
       <c r="N185" t="n">
-        <v>0.481396993</v>
+        <v>-0.6320429292929319</v>
       </c>
       <c r="O185" t="n">
-        <v>-0.6320429292929319</v>
+        <v>-34.2009276776246</v>
       </c>
       <c r="P185" t="n">
-        <v>-34.2009276776246</v>
-      </c>
-      <c r="Q185" t="n">
         <v>8876</v>
       </c>
+      <c r="Q185" t="inlineStr">
+        <is>
+          <t>Sapotaceae</t>
+        </is>
+      </c>
       <c r="R185" t="inlineStr">
         <is>
-          <t>Sapotaceae</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="S185" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>Pouteria</t>
         </is>
       </c>
       <c r="T185" t="inlineStr">
-        <is>
-          <t>Pouteria</t>
-        </is>
-      </c>
-      <c r="U185" t="inlineStr">
         <is>
           <t>torta</t>
         </is>
@@ -12164,26 +11775,25 @@
       <c r="M186" t="inlineStr"/>
       <c r="N186" t="inlineStr"/>
       <c r="O186" t="inlineStr"/>
-      <c r="P186" t="inlineStr"/>
-      <c r="Q186" t="n">
+      <c r="P186" t="n">
         <v>8876</v>
       </c>
+      <c r="Q186" t="inlineStr">
+        <is>
+          <t>Sapotaceae</t>
+        </is>
+      </c>
       <c r="R186" t="inlineStr">
         <is>
-          <t>Sapotaceae</t>
+          <t>3918</t>
         </is>
       </c>
       <c r="S186" t="inlineStr">
         <is>
-          <t>3918</t>
+          <t>Pouteria</t>
         </is>
       </c>
       <c r="T186" t="inlineStr">
-        <is>
-          <t>Pouteria</t>
-        </is>
-      </c>
-      <c r="U186" t="inlineStr">
         <is>
           <t>torta</t>
         </is>
@@ -12231,26 +11841,25 @@
       <c r="M187" t="inlineStr"/>
       <c r="N187" t="inlineStr"/>
       <c r="O187" t="inlineStr"/>
-      <c r="P187" t="inlineStr"/>
-      <c r="Q187" t="n">
+      <c r="P187" t="n">
         <v>8878</v>
       </c>
+      <c r="Q187" t="inlineStr">
+        <is>
+          <t>Rubiaceae</t>
+        </is>
+      </c>
       <c r="R187" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="S187" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>Duroia</t>
         </is>
       </c>
       <c r="T187" t="inlineStr">
-        <is>
-          <t>Duroia</t>
-        </is>
-      </c>
-      <c r="U187" t="inlineStr">
         <is>
           <t>hirsuta</t>
         </is>
@@ -12277,43 +11886,42 @@
       <c r="J188" t="n">
         <v>2136</v>
       </c>
-      <c r="K188" t="inlineStr"/>
-      <c r="L188" t="inlineStr">
+      <c r="K188" t="inlineStr">
         <is>
           <t>p68-8878</t>
         </is>
       </c>
+      <c r="L188" t="n">
+        <v>0.017277264</v>
+      </c>
       <c r="M188" t="n">
-        <v>0.017277264</v>
+        <v>0.437306213</v>
       </c>
       <c r="N188" t="n">
-        <v>0.437306213</v>
+        <v>1.571260101010099</v>
       </c>
       <c r="O188" t="n">
-        <v>1.571260101010099</v>
+        <v>-34.25249077412514</v>
       </c>
       <c r="P188" t="n">
-        <v>-34.25249077412514</v>
-      </c>
-      <c r="Q188" t="n">
         <v>8878</v>
       </c>
+      <c r="Q188" t="inlineStr">
+        <is>
+          <t>Rubiaceae</t>
+        </is>
+      </c>
       <c r="R188" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
+          <t>3920</t>
         </is>
       </c>
       <c r="S188" t="inlineStr">
         <is>
-          <t>3920</t>
+          <t>Duroia</t>
         </is>
       </c>
       <c r="T188" t="inlineStr">
-        <is>
-          <t>Duroia</t>
-        </is>
-      </c>
-      <c r="U188" t="inlineStr">
         <is>
           <t>hirsuta</t>
         </is>
@@ -12354,27 +11962,22 @@
         </is>
       </c>
       <c r="J189" t="inlineStr"/>
-      <c r="K189" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K189" t="inlineStr"/>
       <c r="L189" t="inlineStr"/>
       <c r="M189" t="inlineStr"/>
       <c r="N189" t="inlineStr"/>
       <c r="O189" t="inlineStr"/>
-      <c r="P189" t="inlineStr"/>
-      <c r="Q189" t="n">
+      <c r="P189" t="n">
         <v>8880</v>
       </c>
-      <c r="R189" t="inlineStr">
+      <c r="Q189" t="inlineStr">
         <is>
           <t>Rubiaceae</t>
         </is>
       </c>
+      <c r="R189" t="inlineStr"/>
       <c r="S189" t="inlineStr"/>
       <c r="T189" t="inlineStr"/>
-      <c r="U189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" s="1" t="n">
@@ -12416,18 +12019,17 @@
       <c r="M190" t="inlineStr"/>
       <c r="N190" t="inlineStr"/>
       <c r="O190" t="inlineStr"/>
-      <c r="P190" t="inlineStr"/>
-      <c r="Q190" t="n">
+      <c r="P190" t="n">
         <v>8880</v>
       </c>
-      <c r="R190" t="inlineStr">
+      <c r="Q190" t="inlineStr">
         <is>
           <t>Rubiaceae</t>
         </is>
       </c>
+      <c r="R190" t="inlineStr"/>
       <c r="S190" t="inlineStr"/>
       <c r="T190" t="inlineStr"/>
-      <c r="U190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" s="1" t="n">
@@ -12460,42 +12062,41 @@
       <c r="J191" t="n">
         <v>2155</v>
       </c>
-      <c r="K191" t="inlineStr"/>
-      <c r="L191" t="inlineStr">
+      <c r="K191" t="inlineStr">
         <is>
           <t>p68-8883</t>
         </is>
       </c>
+      <c r="L191" t="n">
+        <v>0.014952077</v>
+      </c>
       <c r="M191" t="n">
-        <v>0.014952077</v>
+        <v>0.406260288</v>
       </c>
       <c r="N191" t="n">
-        <v>0.406260288</v>
+        <v>2.392098484848483</v>
       </c>
       <c r="O191" t="n">
-        <v>2.392098484848483</v>
+        <v>-31.90121357370095</v>
       </c>
       <c r="P191" t="n">
-        <v>-31.90121357370095</v>
-      </c>
-      <c r="Q191" t="n">
         <v>8883</v>
       </c>
-      <c r="R191" t="inlineStr">
+      <c r="Q191" t="inlineStr">
         <is>
           <t>Melastomataceae</t>
         </is>
       </c>
-      <c r="S191">
+      <c r="R191">
         <f>3899</f>
         <v/>
       </c>
+      <c r="S191" t="inlineStr">
+        <is>
+          <t>Miconia</t>
+        </is>
+      </c>
       <c r="T191" t="inlineStr">
-        <is>
-          <t>Miconia</t>
-        </is>
-      </c>
-      <c r="U191" t="inlineStr">
         <is>
           <t>sp</t>
         </is>
@@ -12536,31 +12137,26 @@
         </is>
       </c>
       <c r="J192" t="inlineStr"/>
-      <c r="K192" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K192" t="inlineStr"/>
       <c r="L192" t="inlineStr"/>
       <c r="M192" t="inlineStr"/>
       <c r="N192" t="inlineStr"/>
       <c r="O192" t="inlineStr"/>
-      <c r="P192" t="inlineStr"/>
-      <c r="Q192" t="n">
+      <c r="P192" t="n">
         <v>8884</v>
       </c>
-      <c r="R192" t="inlineStr">
+      <c r="Q192" t="inlineStr">
         <is>
           <t>Fabaceae</t>
         </is>
       </c>
-      <c r="S192" t="inlineStr"/>
+      <c r="R192" t="inlineStr"/>
+      <c r="S192" t="inlineStr">
+        <is>
+          <t>Macrolobium</t>
+        </is>
+      </c>
       <c r="T192" t="inlineStr">
-        <is>
-          <t>Macrolobium</t>
-        </is>
-      </c>
-      <c r="U192" t="inlineStr">
         <is>
           <t>cf. ischnocalyx</t>
         </is>
@@ -12606,22 +12202,21 @@
       <c r="M193" t="inlineStr"/>
       <c r="N193" t="inlineStr"/>
       <c r="O193" t="inlineStr"/>
-      <c r="P193" t="inlineStr"/>
-      <c r="Q193" t="n">
+      <c r="P193" t="n">
         <v>8884</v>
       </c>
-      <c r="R193" t="inlineStr">
+      <c r="Q193" t="inlineStr">
         <is>
           <t>Fabaceae</t>
         </is>
       </c>
-      <c r="S193" t="inlineStr"/>
+      <c r="R193" t="inlineStr"/>
+      <c r="S193" t="inlineStr">
+        <is>
+          <t>Macrolobium</t>
+        </is>
+      </c>
       <c r="T193" t="inlineStr">
-        <is>
-          <t>Macrolobium</t>
-        </is>
-      </c>
-      <c r="U193" t="inlineStr">
         <is>
           <t>cf. ischnocalyx</t>
         </is>
@@ -12648,43 +12243,42 @@
       <c r="J194" t="n">
         <v>2154</v>
       </c>
-      <c r="K194" t="inlineStr"/>
-      <c r="L194" t="inlineStr">
+      <c r="K194" t="inlineStr">
         <is>
           <t>p68-8885</t>
         </is>
       </c>
+      <c r="L194" t="n">
+        <v>0.015294916</v>
+      </c>
       <c r="M194" t="n">
-        <v>0.015294916</v>
+        <v>0.488282508</v>
       </c>
       <c r="N194" t="n">
-        <v>0.488282508</v>
+        <v>0.8692272727272705</v>
       </c>
       <c r="O194" t="n">
-        <v>0.8692272727272705</v>
+        <v>-33.91217433722163</v>
       </c>
       <c r="P194" t="n">
-        <v>-33.91217433722163</v>
-      </c>
-      <c r="Q194" t="n">
         <v>8885</v>
       </c>
+      <c r="Q194" t="inlineStr">
+        <is>
+          <t>Apocynaceae</t>
+        </is>
+      </c>
       <c r="R194" t="inlineStr">
         <is>
-          <t>Apocynaceae</t>
+          <t>3921</t>
         </is>
       </c>
       <c r="S194" t="inlineStr">
         <is>
-          <t>3921</t>
+          <t>Aspidosperma</t>
         </is>
       </c>
       <c r="T194" t="inlineStr">
-        <is>
-          <t>Aspidosperma</t>
-        </is>
-      </c>
-      <c r="U194" t="inlineStr">
         <is>
           <t>aff. excelsum</t>
         </is>
@@ -12725,27 +12319,22 @@
         </is>
       </c>
       <c r="J195" t="inlineStr"/>
-      <c r="K195" t="inlineStr">
-        <is>
-          <t>jh</t>
-        </is>
-      </c>
+      <c r="K195" t="inlineStr"/>
       <c r="L195" t="inlineStr"/>
       <c r="M195" t="inlineStr"/>
       <c r="N195" t="inlineStr"/>
       <c r="O195" t="inlineStr"/>
-      <c r="P195" t="inlineStr"/>
-      <c r="Q195" t="n">
+      <c r="P195" t="n">
         <v>8886</v>
       </c>
-      <c r="R195" t="inlineStr">
+      <c r="Q195" t="inlineStr">
         <is>
           <t>Indet</t>
         </is>
       </c>
+      <c r="R195" t="inlineStr"/>
       <c r="S195" t="inlineStr"/>
       <c r="T195" t="inlineStr"/>
-      <c r="U195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" s="1" t="n">
@@ -12787,18 +12376,17 @@
       <c r="M196" t="inlineStr"/>
       <c r="N196" t="inlineStr"/>
       <c r="O196" t="inlineStr"/>
-      <c r="P196" t="inlineStr"/>
-      <c r="Q196" t="n">
+      <c r="P196" t="n">
         <v>8886</v>
       </c>
-      <c r="R196" t="inlineStr">
+      <c r="Q196" t="inlineStr">
         <is>
           <t>Indet</t>
         </is>
       </c>
+      <c r="R196" t="inlineStr"/>
       <c r="S196" t="inlineStr"/>
       <c r="T196" t="inlineStr"/>
-      <c r="U196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" s="1" t="n">
@@ -12842,26 +12430,25 @@
       <c r="M197" t="inlineStr"/>
       <c r="N197" t="inlineStr"/>
       <c r="O197" t="inlineStr"/>
-      <c r="P197" t="inlineStr"/>
-      <c r="Q197" t="n">
+      <c r="P197" t="n">
         <v>8888</v>
       </c>
+      <c r="Q197" t="inlineStr">
+        <is>
+          <t>Simaroubaceae</t>
+        </is>
+      </c>
       <c r="R197" t="inlineStr">
         <is>
-          <t>Simaroubaceae</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="S197" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>Simaba</t>
         </is>
       </c>
       <c r="T197" t="inlineStr">
-        <is>
-          <t>Simaba</t>
-        </is>
-      </c>
-      <c r="U197" t="inlineStr">
         <is>
           <t>polyphylla</t>
         </is>
@@ -12898,43 +12485,42 @@
       <c r="J198" t="n">
         <v>2148</v>
       </c>
-      <c r="K198" t="inlineStr"/>
-      <c r="L198" t="inlineStr">
+      <c r="K198" t="inlineStr">
         <is>
           <t>p68-8888</t>
         </is>
       </c>
+      <c r="L198" t="n">
+        <v>0.011420399</v>
+      </c>
       <c r="M198" t="n">
-        <v>0.011420399</v>
+        <v>0.430948024</v>
       </c>
       <c r="N198" t="n">
-        <v>0.430948024</v>
+        <v>2.435300505050503</v>
       </c>
       <c r="O198" t="n">
-        <v>2.435300505050503</v>
+        <v>-34.86093531283139</v>
       </c>
       <c r="P198" t="n">
-        <v>-34.86093531283139</v>
-      </c>
-      <c r="Q198" t="n">
         <v>8888</v>
       </c>
+      <c r="Q198" t="inlineStr">
+        <is>
+          <t>Simaroubaceae</t>
+        </is>
+      </c>
       <c r="R198" t="inlineStr">
         <is>
-          <t>Simaroubaceae</t>
+          <t>3929</t>
         </is>
       </c>
       <c r="S198" t="inlineStr">
         <is>
-          <t>3929</t>
+          <t>Simaba</t>
         </is>
       </c>
       <c r="T198" t="inlineStr">
-        <is>
-          <t>Simaba</t>
-        </is>
-      </c>
-      <c r="U198" t="inlineStr">
         <is>
           <t>polyphylla</t>
         </is>
@@ -12971,39 +12557,38 @@
       <c r="J199" t="n">
         <v>2147</v>
       </c>
-      <c r="K199" t="inlineStr"/>
-      <c r="L199" t="inlineStr">
+      <c r="K199" t="inlineStr">
         <is>
           <t>p68-8889</t>
         </is>
       </c>
+      <c r="L199" t="n">
+        <v>0.024841004</v>
+      </c>
       <c r="M199" t="n">
-        <v>0.024841004</v>
+        <v>0.404913041</v>
       </c>
       <c r="N199" t="n">
-        <v>0.404913041</v>
+        <v>1.312047979797978</v>
       </c>
       <c r="O199" t="n">
-        <v>1.312047979797978</v>
+        <v>-31.78777476139979</v>
       </c>
       <c r="P199" t="n">
-        <v>-31.78777476139979</v>
-      </c>
-      <c r="Q199" t="n">
         <v>8889</v>
       </c>
-      <c r="R199" t="inlineStr">
+      <c r="Q199" t="inlineStr">
         <is>
           <t>Euphorbiaceae</t>
         </is>
       </c>
-      <c r="S199" t="inlineStr"/>
+      <c r="R199" t="inlineStr"/>
+      <c r="S199" t="inlineStr">
+        <is>
+          <t>Pseudosenefeldera</t>
+        </is>
+      </c>
       <c r="T199" t="inlineStr">
-        <is>
-          <t>Pseudosenefeldera</t>
-        </is>
-      </c>
-      <c r="U199" t="inlineStr">
         <is>
           <t>inclinata</t>
         </is>
@@ -13040,43 +12625,42 @@
       <c r="J200" t="n">
         <v>2185</v>
       </c>
-      <c r="K200" t="inlineStr"/>
-      <c r="L200" t="inlineStr">
+      <c r="K200" t="inlineStr">
         <is>
           <t>p69-8891</t>
         </is>
       </c>
+      <c r="L200" t="n">
+        <v>0.02990649007833678</v>
+      </c>
       <c r="M200" t="n">
-        <v>0.02990649007833678</v>
+        <v>0.442290096180273</v>
       </c>
       <c r="N200" t="n">
-        <v>0.442290096180273</v>
+        <v>-0.03</v>
       </c>
       <c r="O200" t="n">
-        <v>-0.03</v>
+        <v>-35.22</v>
       </c>
       <c r="P200" t="n">
-        <v>-35.22</v>
-      </c>
-      <c r="Q200" t="n">
         <v>8891</v>
       </c>
+      <c r="Q200" t="inlineStr">
+        <is>
+          <t>Sapindaceae</t>
+        </is>
+      </c>
       <c r="R200" t="inlineStr">
         <is>
-          <t>Sapindaceae</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="S200" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>Allophylus</t>
         </is>
       </c>
       <c r="T200" t="inlineStr">
-        <is>
-          <t>Allophylus</t>
-        </is>
-      </c>
-      <c r="U200" t="inlineStr">
         <is>
           <t>punctatus</t>
         </is>
@@ -13124,26 +12708,25 @@
       <c r="M201" t="inlineStr"/>
       <c r="N201" t="inlineStr"/>
       <c r="O201" t="inlineStr"/>
-      <c r="P201" t="inlineStr"/>
-      <c r="Q201" t="n">
+      <c r="P201" t="n">
         <v>8891</v>
       </c>
+      <c r="Q201" t="inlineStr">
+        <is>
+          <t>Sapindaceae</t>
+        </is>
+      </c>
       <c r="R201" t="inlineStr">
         <is>
-          <t>Sapindaceae</t>
+          <t>3848</t>
         </is>
       </c>
       <c r="S201" t="inlineStr">
         <is>
-          <t>3848</t>
+          <t>Allophylus</t>
         </is>
       </c>
       <c r="T201" t="inlineStr">
-        <is>
-          <t>Allophylus</t>
-        </is>
-      </c>
-      <c r="U201" t="inlineStr">
         <is>
           <t>punctatus</t>
         </is>
@@ -13180,43 +12763,42 @@
       <c r="J202" t="n">
         <v>2184</v>
       </c>
-      <c r="K202" t="inlineStr"/>
-      <c r="L202" t="inlineStr">
+      <c r="K202" t="inlineStr">
         <is>
           <t>p69-8892</t>
         </is>
       </c>
+      <c r="L202" t="n">
+        <v>0.01810419616968846</v>
+      </c>
       <c r="M202" t="n">
-        <v>0.01810419616968846</v>
+        <v>0.4657246583502926</v>
       </c>
       <c r="N202" t="n">
-        <v>0.4657246583502926</v>
+        <v>2.56</v>
       </c>
       <c r="O202" t="n">
-        <v>2.56</v>
+        <v>-34.8</v>
       </c>
       <c r="P202" t="n">
-        <v>-34.8</v>
-      </c>
-      <c r="Q202" t="n">
         <v>8892</v>
       </c>
+      <c r="Q202" t="inlineStr">
+        <is>
+          <t>Rubiaceae</t>
+        </is>
+      </c>
       <c r="R202" t="inlineStr">
         <is>
-          <t>Rubiaceae</t>
+          <t>3847</t>
         </is>
       </c>
       <c r="S202" t="inlineStr">
         <is>
-          <t>3847</t>
+          <t>Pentagonia</t>
         </is>
       </c>
       <c r="T202" t="inlineStr">
-        <is>
-          <t>Pentagonia</t>
-        </is>
-      </c>
-      <c r="U202" t="inlineStr">
         <is>
           <t>amazonica</t>
         </is>
@@ -13264,26 +12846,25 @@
       <c r="M203" t="inlineStr"/>
       <c r="N203" t="inlineStr"/>
       <c r="O203" t="inlineStr"/>
-      <c r="P203" t="inlineStr"/>
-      <c r="Q203" t="n">
+      <c r="P203" t="n">
         <v>8893</v>
       </c>
+      <c r="Q203" t="inlineStr">
+        <is>
+          <t>Moraceae</t>
+        </is>
+      </c>
       <c r="R203" t="inlineStr">
         <is>
-          <t>Moraceae</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="S203" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>Pseudolmedia</t>
         </is>
       </c>
       <c r="T203" t="inlineStr">
-        <is>
-          <t>Pseudolmedia</t>
-        </is>
-      </c>
-      <c r="U203" t="inlineStr">
         <is>
           <t>macrophylla</t>
         </is>
@@ -13327,26 +12908,25 @@
       <c r="M204" t="inlineStr"/>
       <c r="N204" t="inlineStr"/>
       <c r="O204" t="inlineStr"/>
-      <c r="P204" t="inlineStr"/>
-      <c r="Q204" t="n">
+      <c r="P204" t="n">
         <v>8893</v>
       </c>
+      <c r="Q204" t="inlineStr">
+        <is>
+          <t>Moraceae</t>
+        </is>
+      </c>
       <c r="R204" t="inlineStr">
         <is>
-          <t>Moraceae</t>
+          <t>3855</t>
         </is>
       </c>
       <c r="S204" t="inlineStr">
         <is>
-          <t>3855</t>
+          <t>Pseudolmedia</t>
         </is>
       </c>
       <c r="T204" t="inlineStr">
-        <is>
-          <t>Pseudolmedia</t>
-        </is>
-      </c>
-      <c r="U204" t="inlineStr">
         <is>
           <t>macrophylla</t>
         </is>
@@ -13394,26 +12974,25 @@
       <c r="M205" t="inlineStr"/>
       <c r="N205" t="inlineStr"/>
       <c r="O205" t="inlineStr"/>
-      <c r="P205" t="inlineStr"/>
-      <c r="Q205" t="n">
+      <c r="P205" t="n">
         <v>8894</v>
       </c>
+      <c r="Q205" t="inlineStr">
+        <is>
+          <t>Moraceae</t>
+        </is>
+      </c>
       <c r="R205" t="inlineStr">
         <is>
-          <t>Moraceae</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="S205" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>Brosimum</t>
         </is>
       </c>
       <c r="T205" t="inlineStr">
-        <is>
-          <t>Brosimum</t>
-        </is>
-      </c>
-      <c r="U205" t="inlineStr">
         <is>
           <t>lactescens</t>
         </is>
@@ -13457,26 +13036,25 @@
       <c r="M206" t="inlineStr"/>
       <c r="N206" t="inlineStr"/>
       <c r="O206" t="inlineStr"/>
-      <c r="P206" t="inlineStr"/>
-      <c r="Q206" t="n">
+      <c r="P206" t="n">
         <v>8894</v>
       </c>
+      <c r="Q206" t="inlineStr">
+        <is>
+          <t>Moraceae</t>
+        </is>
+      </c>
       <c r="R206" t="inlineStr">
         <is>
-          <t>Moraceae</t>
+          <t>3853</t>
         </is>
       </c>
       <c r="S206" t="inlineStr">
         <is>
-          <t>3853</t>
+          <t>Brosimum</t>
         </is>
       </c>
       <c r="T206" t="inlineStr">
-        <is>
-          <t>Brosimum</t>
-        </is>
-      </c>
-      <c r="U206" t="inlineStr">
         <is>
           <t>lactescens</t>
         </is>
@@ -13513,43 +13091,42 @@
       <c r="J207" t="n">
         <v>2195</v>
       </c>
-      <c r="K207" t="inlineStr"/>
-      <c r="L207" t="inlineStr">
+      <c r="K207" t="inlineStr">
         <is>
           <t>p69-8895</t>
         </is>
       </c>
+      <c r="L207" t="n">
+        <v>0.02466862000311886</v>
+      </c>
       <c r="M207" t="n">
-        <v>0.02466862000311886</v>
+        <v>0.4874293332468896</v>
       </c>
       <c r="N207" t="n">
-        <v>0.4874293332468896</v>
+        <v>2.82</v>
       </c>
       <c r="O207" t="n">
-        <v>2.82</v>
+        <v>-36.94</v>
       </c>
       <c r="P207" t="n">
-        <v>-36.94</v>
-      </c>
-      <c r="Q207" t="n">
         <v>8895</v>
       </c>
+      <c r="Q207" t="inlineStr">
+        <is>
+          <t>Celastraceae</t>
+        </is>
+      </c>
       <c r="R207" t="inlineStr">
         <is>
-          <t>Celastraceae</t>
+          <t>3852</t>
         </is>
       </c>
       <c r="S207" t="inlineStr">
         <is>
-          <t>3852</t>
+          <t>Salacia</t>
         </is>
       </c>
       <c r="T207" t="inlineStr">
-        <is>
-          <t>Salacia</t>
-        </is>
-      </c>
-      <c r="U207" t="inlineStr">
         <is>
           <t>aff. cordata</t>
         </is>
@@ -13586,39 +13163,38 @@
       <c r="J208" t="n">
         <v>2191</v>
       </c>
-      <c r="K208" t="inlineStr"/>
-      <c r="L208" t="inlineStr">
+      <c r="K208" t="inlineStr">
         <is>
           <t>p69-8898</t>
         </is>
       </c>
+      <c r="L208" t="n">
+        <v>0.02685294930046833</v>
+      </c>
       <c r="M208" t="n">
-        <v>0.02685294930046833</v>
+        <v>0.4356585352943561</v>
       </c>
       <c r="N208" t="n">
-        <v>0.4356585352943561</v>
+        <v>0.66</v>
       </c>
       <c r="O208" t="n">
-        <v>0.66</v>
+        <v>-33.2</v>
       </c>
       <c r="P208" t="n">
-        <v>-33.2</v>
-      </c>
-      <c r="Q208" t="n">
         <v>8898</v>
       </c>
-      <c r="R208" t="inlineStr">
+      <c r="Q208" t="inlineStr">
         <is>
           <t>Euphorbiaceae</t>
         </is>
       </c>
-      <c r="S208" t="inlineStr"/>
+      <c r="R208" t="inlineStr"/>
+      <c r="S208" t="inlineStr">
+        <is>
+          <t>Pseudosenefeldera</t>
+        </is>
+      </c>
       <c r="T208" t="inlineStr">
-        <is>
-          <t>Pseudosenefeldera</t>
-        </is>
-      </c>
-      <c r="U208" t="inlineStr">
         <is>
           <t>inclinata</t>
         </is>
@@ -13662,26 +13238,25 @@
       <c r="M209" t="inlineStr"/>
       <c r="N209" t="inlineStr"/>
       <c r="O209" t="inlineStr"/>
-      <c r="P209" t="inlineStr"/>
-      <c r="Q209" t="n">
+      <c r="P209" t="n">
         <v>8899</v>
       </c>
+      <c r="Q209" t="inlineStr">
+        <is>
+          <t>Lacistemataceae</t>
+        </is>
+      </c>
       <c r="R209" t="inlineStr">
         <is>
-          <t>Lacistemataceae</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="S209" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>Lozania</t>
         </is>
       </c>
       <c r="T209" t="inlineStr">
-        <is>
-          <t>Lozania</t>
-        </is>
-      </c>
-      <c r="U209" t="inlineStr">
         <is>
           <t>klugii</t>
         </is>
@@ -13729,26 +13304,25 @@
       <c r="M210" t="inlineStr"/>
       <c r="N210" t="inlineStr"/>
       <c r="O210" t="inlineStr"/>
-      <c r="P210" t="inlineStr"/>
-      <c r="Q210" t="n">
+      <c r="P210" t="n">
         <v>8899</v>
       </c>
+      <c r="Q210" t="inlineStr">
+        <is>
+          <t>Lacistemataceae</t>
+        </is>
+      </c>
       <c r="R210" t="inlineStr">
         <is>
-          <t>Lacistemataceae</t>
+          <t>3850</t>
         </is>
       </c>
       <c r="S210" t="inlineStr">
         <is>
-          <t>3850</t>
+          <t>Lozania</t>
         </is>
       </c>
       <c r="T210" t="inlineStr">
-        <is>
-          <t>Lozania</t>
-        </is>
-      </c>
-      <c r="U210" t="inlineStr">
         <is>
           <t>klugii</t>
         </is>
@@ -13790,14 +13364,13 @@
       <c r="M211" t="inlineStr"/>
       <c r="N211" t="inlineStr"/>
       <c r="O211" t="inlineStr"/>
-      <c r="P211" t="inlineStr"/>
-      <c r="Q211" t="n">
+      <c r="P211" t="n">
         <v>9865</v>
       </c>
+      <c r="Q211" t="inlineStr"/>
       <c r="R211" t="inlineStr"/>
       <c r="S211" t="inlineStr"/>
       <c r="T211" t="inlineStr"/>
-      <c r="U211" t="inlineStr"/>
     </row>
     <row r="212">
       <c r="A212" s="1" t="n">
@@ -13842,23 +13415,22 @@
       <c r="N212" t="inlineStr"/>
       <c r="O212" t="inlineStr"/>
       <c r="P212" t="inlineStr"/>
-      <c r="Q212" t="inlineStr"/>
+      <c r="Q212" t="inlineStr">
+        <is>
+          <t>Euphorbiaceae</t>
+        </is>
+      </c>
       <c r="R212" t="inlineStr">
         <is>
-          <t>Euphorbiaceae</t>
+          <t>3839</t>
         </is>
       </c>
       <c r="S212" t="inlineStr">
         <is>
-          <t>3839</t>
+          <t>Pseudosenefeldera</t>
         </is>
       </c>
       <c r="T212" t="inlineStr">
-        <is>
-          <t>Pseudosenefeldera</t>
-        </is>
-      </c>
-      <c r="U212" t="inlineStr">
         <is>
           <t>inclinata</t>
         </is>
@@ -13907,23 +13479,22 @@
       <c r="N213" t="inlineStr"/>
       <c r="O213" t="inlineStr"/>
       <c r="P213" t="inlineStr"/>
-      <c r="Q213" t="inlineStr"/>
+      <c r="Q213" t="inlineStr">
+        <is>
+          <t>Opiliaceae</t>
+        </is>
+      </c>
       <c r="R213" t="inlineStr">
         <is>
-          <t>Opiliaceae</t>
+          <t>3919</t>
         </is>
       </c>
       <c r="S213" t="inlineStr">
         <is>
-          <t>3919</t>
+          <t>Agonandra</t>
         </is>
       </c>
       <c r="T213" t="inlineStr">
-        <is>
-          <t>Agonandra</t>
-        </is>
-      </c>
-      <c r="U213" t="inlineStr">
         <is>
           <t>peruviana</t>
         </is>
@@ -13972,21 +13543,20 @@
       <c r="N214" t="inlineStr"/>
       <c r="O214" t="inlineStr"/>
       <c r="P214" t="inlineStr"/>
-      <c r="Q214" t="inlineStr"/>
-      <c r="R214" t="inlineStr">
+      <c r="Q214" t="inlineStr">
         <is>
           <t>Salicaceae</t>
         </is>
       </c>
-      <c r="S214" t="n">
+      <c r="R214" t="n">
         <v>3875</v>
       </c>
+      <c r="S214" t="inlineStr">
+        <is>
+          <t>Laetia</t>
+        </is>
+      </c>
       <c r="T214" t="inlineStr">
-        <is>
-          <t>Laetia</t>
-        </is>
-      </c>
-      <c r="U214" t="inlineStr">
         <is>
           <t>procera</t>
         </is>
@@ -14035,21 +13605,20 @@
       <c r="N215" t="inlineStr"/>
       <c r="O215" t="inlineStr"/>
       <c r="P215" t="inlineStr"/>
-      <c r="Q215" t="inlineStr"/>
-      <c r="R215" t="inlineStr">
+      <c r="Q215" t="inlineStr">
         <is>
           <t>Myristicaceae</t>
         </is>
       </c>
-      <c r="S215" t="n">
+      <c r="R215" t="n">
         <v>3880</v>
       </c>
+      <c r="S215" t="inlineStr">
+        <is>
+          <t>Iryanthera</t>
+        </is>
+      </c>
       <c r="T215" t="inlineStr">
-        <is>
-          <t>Iryanthera</t>
-        </is>
-      </c>
-      <c r="U215" t="inlineStr">
         <is>
           <t>juruensis</t>
         </is>
@@ -14098,23 +13667,22 @@
       <c r="N216" t="inlineStr"/>
       <c r="O216" t="inlineStr"/>
       <c r="P216" t="inlineStr"/>
-      <c r="Q216" t="inlineStr"/>
+      <c r="Q216" t="inlineStr">
+        <is>
+          <t>Fabaceae</t>
+        </is>
+      </c>
       <c r="R216" t="inlineStr">
         <is>
-          <t>Fabaceae</t>
+          <t>3922</t>
         </is>
       </c>
       <c r="S216" t="inlineStr">
         <is>
-          <t>3922</t>
+          <t>Tachigali</t>
         </is>
       </c>
       <c r="T216" t="inlineStr">
-        <is>
-          <t>Tachigali</t>
-        </is>
-      </c>
-      <c r="U216" t="inlineStr">
         <is>
           <t>chrysophylla</t>
         </is>
@@ -14163,23 +13731,22 @@
       <c r="N217" t="inlineStr"/>
       <c r="O217" t="inlineStr"/>
       <c r="P217" t="inlineStr"/>
-      <c r="Q217" t="inlineStr"/>
+      <c r="Q217" t="inlineStr">
+        <is>
+          <t>Clusiaceae</t>
+        </is>
+      </c>
       <c r="R217" t="inlineStr">
         <is>
-          <t>Clusiaceae</t>
+          <t>3927</t>
         </is>
       </c>
       <c r="S217" t="inlineStr">
         <is>
-          <t>3927</t>
+          <t>Garcinia</t>
         </is>
       </c>
       <c r="T217" t="inlineStr">
-        <is>
-          <t>Garcinia</t>
-        </is>
-      </c>
-      <c r="U217" t="inlineStr">
         <is>
           <t>madruno</t>
         </is>
@@ -14228,23 +13795,22 @@
       <c r="N218" t="inlineStr"/>
       <c r="O218" t="inlineStr"/>
       <c r="P218" t="inlineStr"/>
-      <c r="Q218" t="inlineStr"/>
+      <c r="Q218" t="inlineStr">
+        <is>
+          <t>Lauraceae</t>
+        </is>
+      </c>
       <c r="R218" t="inlineStr">
         <is>
-          <t>Lauraceae</t>
+          <t>3854</t>
         </is>
       </c>
       <c r="S218" t="inlineStr">
         <is>
-          <t>3854</t>
+          <t>Ocotea</t>
         </is>
       </c>
       <c r="T218" t="inlineStr">
-        <is>
-          <t>Ocotea</t>
-        </is>
-      </c>
-      <c r="U218" t="inlineStr">
         <is>
           <t>aff. oblonga</t>
         </is>
@@ -14293,17 +13859,16 @@
       <c r="N219" t="inlineStr"/>
       <c r="O219" t="inlineStr"/>
       <c r="P219" t="inlineStr"/>
-      <c r="Q219" t="inlineStr"/>
-      <c r="R219" t="inlineStr">
+      <c r="Q219" t="inlineStr">
         <is>
           <t>Moraceae</t>
         </is>
       </c>
-      <c r="S219" t="n">
+      <c r="R219" t="n">
         <v>3900</v>
       </c>
+      <c r="S219" t="inlineStr"/>
       <c r="T219" t="inlineStr"/>
-      <c r="U219" t="inlineStr"/>
     </row>
     <row r="220">
       <c r="A220" s="1" t="n">
@@ -14348,21 +13913,20 @@
       <c r="N220" t="inlineStr"/>
       <c r="O220" t="inlineStr"/>
       <c r="P220" t="inlineStr"/>
-      <c r="Q220" t="inlineStr"/>
-      <c r="R220" t="inlineStr">
+      <c r="Q220" t="inlineStr">
         <is>
           <t>Myristicaceae</t>
         </is>
       </c>
-      <c r="S220" t="n">
+      <c r="R220" t="n">
         <v>3212</v>
       </c>
+      <c r="S220" t="inlineStr">
+        <is>
+          <t>Compsoneura</t>
+        </is>
+      </c>
       <c r="T220" t="inlineStr">
-        <is>
-          <t>Compsoneura</t>
-        </is>
-      </c>
-      <c r="U220" t="inlineStr">
         <is>
           <t>aff sprucei</t>
         </is>
@@ -14411,21 +13975,20 @@
       <c r="N221" t="inlineStr"/>
       <c r="O221" t="inlineStr"/>
       <c r="P221" t="inlineStr"/>
-      <c r="Q221" t="inlineStr"/>
-      <c r="R221" t="inlineStr">
+      <c r="Q221" t="inlineStr">
         <is>
           <t>Myristicaceae</t>
         </is>
       </c>
-      <c r="S221" t="n">
+      <c r="R221" t="n">
         <v>3212</v>
       </c>
+      <c r="S221" t="inlineStr">
+        <is>
+          <t>Compsoneura</t>
+        </is>
+      </c>
       <c r="T221" t="inlineStr">
-        <is>
-          <t>Compsoneura</t>
-        </is>
-      </c>
-      <c r="U221" t="inlineStr">
         <is>
           <t>aff sprucei</t>
         </is>
@@ -14474,21 +14037,20 @@
       <c r="N222" t="inlineStr"/>
       <c r="O222" t="inlineStr"/>
       <c r="P222" t="inlineStr"/>
-      <c r="Q222" t="inlineStr"/>
-      <c r="R222" t="inlineStr">
+      <c r="Q222" t="inlineStr">
         <is>
           <t>Euphorbiaceae</t>
         </is>
       </c>
-      <c r="S222" t="n">
+      <c r="R222" t="n">
         <v>3215</v>
       </c>
+      <c r="S222" t="inlineStr">
+        <is>
+          <t>Mabea</t>
+        </is>
+      </c>
       <c r="T222" t="inlineStr">
-        <is>
-          <t>Mabea</t>
-        </is>
-      </c>
-      <c r="U222" t="inlineStr">
         <is>
           <t>klugii</t>
         </is>
@@ -14537,17 +14099,16 @@
       <c r="N223" t="inlineStr"/>
       <c r="O223" t="inlineStr"/>
       <c r="P223" t="inlineStr"/>
-      <c r="Q223" t="inlineStr"/>
-      <c r="R223" t="inlineStr">
+      <c r="Q223" t="inlineStr">
         <is>
           <t>Moraceae</t>
         </is>
       </c>
-      <c r="S223" t="n">
+      <c r="R223" t="n">
         <v>3900</v>
       </c>
+      <c r="S223" t="inlineStr"/>
       <c r="T223" t="inlineStr"/>
-      <c r="U223" t="inlineStr"/>
     </row>
     <row r="224">
       <c r="A224" s="1" t="n">
@@ -14592,21 +14153,20 @@
       <c r="N224" t="inlineStr"/>
       <c r="O224" t="inlineStr"/>
       <c r="P224" t="inlineStr"/>
-      <c r="Q224" t="inlineStr"/>
-      <c r="R224" t="inlineStr">
+      <c r="Q224" t="inlineStr">
         <is>
           <t>Violaceae</t>
         </is>
       </c>
-      <c r="S224" t="n">
+      <c r="R224" t="n">
         <v>3901</v>
       </c>
+      <c r="S224" t="inlineStr">
+        <is>
+          <t>Fusispermum</t>
+        </is>
+      </c>
       <c r="T224" t="inlineStr">
-        <is>
-          <t>Fusispermum</t>
-        </is>
-      </c>
-      <c r="U224" t="inlineStr">
         <is>
           <t>laxiflorum</t>
         </is>
